--- a/NGO_Project_MNE_Dataset_2000.xlsx
+++ b/NGO_Project_MNE_Dataset_2000.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8008" uniqueCount="2018">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8808" uniqueCount="2218">
   <si>
     <t>Household_ID</t>
   </si>
@@ -6071,6 +6071,606 @@
   </si>
   <si>
     <t>HH-3000</t>
+  </si>
+  <si>
+    <t>HH-3001</t>
+  </si>
+  <si>
+    <t>HH-3002</t>
+  </si>
+  <si>
+    <t>HH-3003</t>
+  </si>
+  <si>
+    <t>HH-3004</t>
+  </si>
+  <si>
+    <t>HH-3005</t>
+  </si>
+  <si>
+    <t>HH-3006</t>
+  </si>
+  <si>
+    <t>HH-3007</t>
+  </si>
+  <si>
+    <t>HH-3008</t>
+  </si>
+  <si>
+    <t>HH-3009</t>
+  </si>
+  <si>
+    <t>HH-3010</t>
+  </si>
+  <si>
+    <t>HH-3011</t>
+  </si>
+  <si>
+    <t>HH-3012</t>
+  </si>
+  <si>
+    <t>HH-3013</t>
+  </si>
+  <si>
+    <t>HH-3014</t>
+  </si>
+  <si>
+    <t>HH-3015</t>
+  </si>
+  <si>
+    <t>HH-3016</t>
+  </si>
+  <si>
+    <t>HH-3017</t>
+  </si>
+  <si>
+    <t>HH-3018</t>
+  </si>
+  <si>
+    <t>HH-3019</t>
+  </si>
+  <si>
+    <t>HH-3020</t>
+  </si>
+  <si>
+    <t>HH-3021</t>
+  </si>
+  <si>
+    <t>HH-3022</t>
+  </si>
+  <si>
+    <t>HH-3023</t>
+  </si>
+  <si>
+    <t>HH-3024</t>
+  </si>
+  <si>
+    <t>HH-3025</t>
+  </si>
+  <si>
+    <t>HH-3026</t>
+  </si>
+  <si>
+    <t>HH-3027</t>
+  </si>
+  <si>
+    <t>HH-3028</t>
+  </si>
+  <si>
+    <t>HH-3029</t>
+  </si>
+  <si>
+    <t>HH-3030</t>
+  </si>
+  <si>
+    <t>HH-3031</t>
+  </si>
+  <si>
+    <t>HH-3032</t>
+  </si>
+  <si>
+    <t>HH-3033</t>
+  </si>
+  <si>
+    <t>HH-3034</t>
+  </si>
+  <si>
+    <t>HH-3035</t>
+  </si>
+  <si>
+    <t>HH-3036</t>
+  </si>
+  <si>
+    <t>HH-3037</t>
+  </si>
+  <si>
+    <t>HH-3038</t>
+  </si>
+  <si>
+    <t>HH-3039</t>
+  </si>
+  <si>
+    <t>HH-3040</t>
+  </si>
+  <si>
+    <t>HH-3041</t>
+  </si>
+  <si>
+    <t>HH-3042</t>
+  </si>
+  <si>
+    <t>HH-3043</t>
+  </si>
+  <si>
+    <t>HH-3044</t>
+  </si>
+  <si>
+    <t>HH-3045</t>
+  </si>
+  <si>
+    <t>HH-3046</t>
+  </si>
+  <si>
+    <t>HH-3047</t>
+  </si>
+  <si>
+    <t>HH-3048</t>
+  </si>
+  <si>
+    <t>HH-3049</t>
+  </si>
+  <si>
+    <t>HH-3050</t>
+  </si>
+  <si>
+    <t>HH-3051</t>
+  </si>
+  <si>
+    <t>HH-3052</t>
+  </si>
+  <si>
+    <t>HH-3053</t>
+  </si>
+  <si>
+    <t>HH-3054</t>
+  </si>
+  <si>
+    <t>HH-3055</t>
+  </si>
+  <si>
+    <t>HH-3056</t>
+  </si>
+  <si>
+    <t>HH-3057</t>
+  </si>
+  <si>
+    <t>HH-3058</t>
+  </si>
+  <si>
+    <t>HH-3059</t>
+  </si>
+  <si>
+    <t>HH-3060</t>
+  </si>
+  <si>
+    <t>HH-3061</t>
+  </si>
+  <si>
+    <t>HH-3062</t>
+  </si>
+  <si>
+    <t>HH-3063</t>
+  </si>
+  <si>
+    <t>HH-3064</t>
+  </si>
+  <si>
+    <t>HH-3065</t>
+  </si>
+  <si>
+    <t>HH-3066</t>
+  </si>
+  <si>
+    <t>HH-3067</t>
+  </si>
+  <si>
+    <t>HH-3068</t>
+  </si>
+  <si>
+    <t>HH-3069</t>
+  </si>
+  <si>
+    <t>HH-3070</t>
+  </si>
+  <si>
+    <t>HH-3071</t>
+  </si>
+  <si>
+    <t>HH-3072</t>
+  </si>
+  <si>
+    <t>HH-3073</t>
+  </si>
+  <si>
+    <t>HH-3074</t>
+  </si>
+  <si>
+    <t>HH-3075</t>
+  </si>
+  <si>
+    <t>HH-3076</t>
+  </si>
+  <si>
+    <t>HH-3077</t>
+  </si>
+  <si>
+    <t>HH-3078</t>
+  </si>
+  <si>
+    <t>HH-3079</t>
+  </si>
+  <si>
+    <t>HH-3080</t>
+  </si>
+  <si>
+    <t>HH-3081</t>
+  </si>
+  <si>
+    <t>HH-3082</t>
+  </si>
+  <si>
+    <t>HH-3083</t>
+  </si>
+  <si>
+    <t>HH-3084</t>
+  </si>
+  <si>
+    <t>HH-3085</t>
+  </si>
+  <si>
+    <t>HH-3086</t>
+  </si>
+  <si>
+    <t>HH-3087</t>
+  </si>
+  <si>
+    <t>HH-3088</t>
+  </si>
+  <si>
+    <t>HH-3089</t>
+  </si>
+  <si>
+    <t>HH-3090</t>
+  </si>
+  <si>
+    <t>HH-3091</t>
+  </si>
+  <si>
+    <t>HH-3092</t>
+  </si>
+  <si>
+    <t>HH-3093</t>
+  </si>
+  <si>
+    <t>HH-3094</t>
+  </si>
+  <si>
+    <t>HH-3095</t>
+  </si>
+  <si>
+    <t>HH-3096</t>
+  </si>
+  <si>
+    <t>HH-3097</t>
+  </si>
+  <si>
+    <t>HH-3098</t>
+  </si>
+  <si>
+    <t>HH-3099</t>
+  </si>
+  <si>
+    <t>HH-3100</t>
+  </si>
+  <si>
+    <t>HH-3101</t>
+  </si>
+  <si>
+    <t>HH-3102</t>
+  </si>
+  <si>
+    <t>HH-3103</t>
+  </si>
+  <si>
+    <t>HH-3104</t>
+  </si>
+  <si>
+    <t>HH-3105</t>
+  </si>
+  <si>
+    <t>HH-3106</t>
+  </si>
+  <si>
+    <t>HH-3107</t>
+  </si>
+  <si>
+    <t>HH-3108</t>
+  </si>
+  <si>
+    <t>HH-3109</t>
+  </si>
+  <si>
+    <t>HH-3110</t>
+  </si>
+  <si>
+    <t>HH-3111</t>
+  </si>
+  <si>
+    <t>HH-3112</t>
+  </si>
+  <si>
+    <t>HH-3113</t>
+  </si>
+  <si>
+    <t>HH-3114</t>
+  </si>
+  <si>
+    <t>HH-3115</t>
+  </si>
+  <si>
+    <t>HH-3116</t>
+  </si>
+  <si>
+    <t>HH-3117</t>
+  </si>
+  <si>
+    <t>HH-3118</t>
+  </si>
+  <si>
+    <t>HH-3119</t>
+  </si>
+  <si>
+    <t>HH-3120</t>
+  </si>
+  <si>
+    <t>HH-3121</t>
+  </si>
+  <si>
+    <t>HH-3122</t>
+  </si>
+  <si>
+    <t>HH-3123</t>
+  </si>
+  <si>
+    <t>HH-3124</t>
+  </si>
+  <si>
+    <t>HH-3125</t>
+  </si>
+  <si>
+    <t>HH-3126</t>
+  </si>
+  <si>
+    <t>HH-3127</t>
+  </si>
+  <si>
+    <t>HH-3128</t>
+  </si>
+  <si>
+    <t>HH-3129</t>
+  </si>
+  <si>
+    <t>HH-3130</t>
+  </si>
+  <si>
+    <t>HH-3131</t>
+  </si>
+  <si>
+    <t>HH-3132</t>
+  </si>
+  <si>
+    <t>HH-3133</t>
+  </si>
+  <si>
+    <t>HH-3134</t>
+  </si>
+  <si>
+    <t>HH-3135</t>
+  </si>
+  <si>
+    <t>HH-3136</t>
+  </si>
+  <si>
+    <t>HH-3137</t>
+  </si>
+  <si>
+    <t>HH-3138</t>
+  </si>
+  <si>
+    <t>HH-3139</t>
+  </si>
+  <si>
+    <t>HH-3140</t>
+  </si>
+  <si>
+    <t>HH-3141</t>
+  </si>
+  <si>
+    <t>HH-3142</t>
+  </si>
+  <si>
+    <t>HH-3143</t>
+  </si>
+  <si>
+    <t>HH-3144</t>
+  </si>
+  <si>
+    <t>HH-3145</t>
+  </si>
+  <si>
+    <t>HH-3146</t>
+  </si>
+  <si>
+    <t>HH-3147</t>
+  </si>
+  <si>
+    <t>HH-3148</t>
+  </si>
+  <si>
+    <t>HH-3149</t>
+  </si>
+  <si>
+    <t>HH-3150</t>
+  </si>
+  <si>
+    <t>HH-3151</t>
+  </si>
+  <si>
+    <t>HH-3152</t>
+  </si>
+  <si>
+    <t>HH-3153</t>
+  </si>
+  <si>
+    <t>HH-3154</t>
+  </si>
+  <si>
+    <t>HH-3155</t>
+  </si>
+  <si>
+    <t>HH-3156</t>
+  </si>
+  <si>
+    <t>HH-3157</t>
+  </si>
+  <si>
+    <t>HH-3158</t>
+  </si>
+  <si>
+    <t>HH-3159</t>
+  </si>
+  <si>
+    <t>HH-3160</t>
+  </si>
+  <si>
+    <t>HH-3161</t>
+  </si>
+  <si>
+    <t>HH-3162</t>
+  </si>
+  <si>
+    <t>HH-3163</t>
+  </si>
+  <si>
+    <t>HH-3164</t>
+  </si>
+  <si>
+    <t>HH-3165</t>
+  </si>
+  <si>
+    <t>HH-3166</t>
+  </si>
+  <si>
+    <t>HH-3167</t>
+  </si>
+  <si>
+    <t>HH-3168</t>
+  </si>
+  <si>
+    <t>HH-3169</t>
+  </si>
+  <si>
+    <t>HH-3170</t>
+  </si>
+  <si>
+    <t>HH-3171</t>
+  </si>
+  <si>
+    <t>HH-3172</t>
+  </si>
+  <si>
+    <t>HH-3173</t>
+  </si>
+  <si>
+    <t>HH-3174</t>
+  </si>
+  <si>
+    <t>HH-3175</t>
+  </si>
+  <si>
+    <t>HH-3176</t>
+  </si>
+  <si>
+    <t>HH-3177</t>
+  </si>
+  <si>
+    <t>HH-3178</t>
+  </si>
+  <si>
+    <t>HH-3179</t>
+  </si>
+  <si>
+    <t>HH-3180</t>
+  </si>
+  <si>
+    <t>HH-3181</t>
+  </si>
+  <si>
+    <t>HH-3182</t>
+  </si>
+  <si>
+    <t>HH-3183</t>
+  </si>
+  <si>
+    <t>HH-3184</t>
+  </si>
+  <si>
+    <t>HH-3185</t>
+  </si>
+  <si>
+    <t>HH-3186</t>
+  </si>
+  <si>
+    <t>HH-3187</t>
+  </si>
+  <si>
+    <t>HH-3188</t>
+  </si>
+  <si>
+    <t>HH-3189</t>
+  </si>
+  <si>
+    <t>HH-3190</t>
+  </si>
+  <si>
+    <t>HH-3191</t>
+  </si>
+  <si>
+    <t>HH-3192</t>
+  </si>
+  <si>
+    <t>HH-3193</t>
+  </si>
+  <si>
+    <t>HH-3194</t>
+  </si>
+  <si>
+    <t>HH-3195</t>
+  </si>
+  <si>
+    <t>HH-3196</t>
+  </si>
+  <si>
+    <t>HH-3197</t>
+  </si>
+  <si>
+    <t>HH-3198</t>
+  </si>
+  <si>
+    <t>HH-3199</t>
+  </si>
+  <si>
+    <t>HH-3200</t>
   </si>
 </sst>
 </file>
@@ -6114,11 +6714,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -6414,7 +7015,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H2001"/>
+  <dimension ref="A1:H2201"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.85546875" style="2" customWidth="1"/>
@@ -58454,6 +59055,5206 @@
         <v>5</v>
       </c>
     </row>
+    <row r="2002" spans="1:8">
+      <c r="A2002" s="2" t="s">
+        <v>2018</v>
+      </c>
+      <c r="B2002" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2002" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2002" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2002" s="2">
+        <v>5572</v>
+      </c>
+      <c r="F2002" s="2">
+        <v>7</v>
+      </c>
+      <c r="G2002" s="2">
+        <v>13014</v>
+      </c>
+      <c r="H2002" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2003" spans="1:8">
+      <c r="A2003" s="3" t="s">
+        <v>2019</v>
+      </c>
+      <c r="B2003" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2003" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2003" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2003" s="3">
+        <v>8492</v>
+      </c>
+      <c r="F2003" s="3">
+        <v>7</v>
+      </c>
+      <c r="G2003" s="3">
+        <v>15321</v>
+      </c>
+      <c r="H2003" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2004" spans="1:8">
+      <c r="A2004" s="3" t="s">
+        <v>2020</v>
+      </c>
+      <c r="B2004" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2004" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2004" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2004" s="3">
+        <v>8490</v>
+      </c>
+      <c r="F2004" s="3">
+        <v>10</v>
+      </c>
+      <c r="G2004" s="3">
+        <v>18201</v>
+      </c>
+      <c r="H2004" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2005" spans="1:8">
+      <c r="A2005" s="3" t="s">
+        <v>2021</v>
+      </c>
+      <c r="B2005" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2005" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2005" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2005" s="3">
+        <v>8483</v>
+      </c>
+      <c r="F2005" s="3">
+        <v>0</v>
+      </c>
+      <c r="G2005" s="3">
+        <v>12194</v>
+      </c>
+      <c r="H2005" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2006" spans="1:8">
+      <c r="A2006" s="3" t="s">
+        <v>2022</v>
+      </c>
+      <c r="B2006" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2006" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2006" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2006" s="3">
+        <v>8458</v>
+      </c>
+      <c r="F2006" s="3">
+        <v>0</v>
+      </c>
+      <c r="G2006" s="3">
+        <v>10485</v>
+      </c>
+      <c r="H2006" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2007" spans="1:8">
+      <c r="A2007" s="3" t="s">
+        <v>2023</v>
+      </c>
+      <c r="B2007" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2007" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2007" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2007" s="3">
+        <v>8446</v>
+      </c>
+      <c r="F2007" s="3">
+        <v>9</v>
+      </c>
+      <c r="G2007" s="3">
+        <v>16694</v>
+      </c>
+      <c r="H2007" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2008" spans="1:8">
+      <c r="A2008" s="3" t="s">
+        <v>2024</v>
+      </c>
+      <c r="B2008" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2008" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2008" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2008" s="3">
+        <v>8435</v>
+      </c>
+      <c r="F2008" s="3">
+        <v>0</v>
+      </c>
+      <c r="G2008" s="3">
+        <v>10405</v>
+      </c>
+      <c r="H2008" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2009" spans="1:8">
+      <c r="A2009" s="3" t="s">
+        <v>2025</v>
+      </c>
+      <c r="B2009" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2009" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2009" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2009" s="3">
+        <v>8435</v>
+      </c>
+      <c r="F2009" s="3">
+        <v>6</v>
+      </c>
+      <c r="G2009" s="3">
+        <v>13565</v>
+      </c>
+      <c r="H2009" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2010" spans="1:8">
+      <c r="A2010" s="3" t="s">
+        <v>2026</v>
+      </c>
+      <c r="B2010" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2010" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2010" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2010" s="3">
+        <v>8433</v>
+      </c>
+      <c r="F2010" s="3">
+        <v>4</v>
+      </c>
+      <c r="G2010" s="3">
+        <v>13758</v>
+      </c>
+      <c r="H2010" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2011" spans="1:8">
+      <c r="A2011" s="3" t="s">
+        <v>2027</v>
+      </c>
+      <c r="B2011" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2011" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2011" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2011" s="3">
+        <v>8421</v>
+      </c>
+      <c r="F2011" s="3">
+        <v>9</v>
+      </c>
+      <c r="G2011" s="3">
+        <v>15482</v>
+      </c>
+      <c r="H2011" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2012" spans="1:8">
+      <c r="A2012" s="3" t="s">
+        <v>2028</v>
+      </c>
+      <c r="B2012" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2012" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2012" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2012" s="3">
+        <v>8406</v>
+      </c>
+      <c r="F2012" s="3">
+        <v>6</v>
+      </c>
+      <c r="G2012" s="3">
+        <v>14678</v>
+      </c>
+      <c r="H2012" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2013" spans="1:8">
+      <c r="A2013" s="3" t="s">
+        <v>2029</v>
+      </c>
+      <c r="B2013" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2013" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2013" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2013" s="3">
+        <v>8402</v>
+      </c>
+      <c r="F2013" s="3">
+        <v>5</v>
+      </c>
+      <c r="G2013" s="3">
+        <v>12681</v>
+      </c>
+      <c r="H2013" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2014" spans="1:8">
+      <c r="A2014" s="3" t="s">
+        <v>2030</v>
+      </c>
+      <c r="B2014" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2014" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2014" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2014" s="3">
+        <v>8402</v>
+      </c>
+      <c r="F2014" s="3">
+        <v>3</v>
+      </c>
+      <c r="G2014" s="3">
+        <v>12447</v>
+      </c>
+      <c r="H2014" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2015" spans="1:8">
+      <c r="A2015" s="3" t="s">
+        <v>2031</v>
+      </c>
+      <c r="B2015" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2015" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2015" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2015" s="3">
+        <v>8381</v>
+      </c>
+      <c r="F2015" s="3">
+        <v>9</v>
+      </c>
+      <c r="G2015" s="3">
+        <v>17045</v>
+      </c>
+      <c r="H2015" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2016" spans="1:8">
+      <c r="A2016" s="3" t="s">
+        <v>2032</v>
+      </c>
+      <c r="B2016" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2016" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2016" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2016" s="3">
+        <v>8372</v>
+      </c>
+      <c r="F2016" s="3">
+        <v>3</v>
+      </c>
+      <c r="G2016" s="3">
+        <v>11685</v>
+      </c>
+      <c r="H2016" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2017" spans="1:8">
+      <c r="A2017" s="3" t="s">
+        <v>2033</v>
+      </c>
+      <c r="B2017" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2017" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2017" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2017" s="3">
+        <v>8371</v>
+      </c>
+      <c r="F2017" s="3">
+        <v>7</v>
+      </c>
+      <c r="G2017" s="3">
+        <v>16523</v>
+      </c>
+      <c r="H2017" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2018" spans="1:8">
+      <c r="A2018" s="3" t="s">
+        <v>2034</v>
+      </c>
+      <c r="B2018" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2018" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2018" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2018" s="3">
+        <v>8366</v>
+      </c>
+      <c r="F2018" s="3">
+        <v>0</v>
+      </c>
+      <c r="G2018" s="3">
+        <v>10666</v>
+      </c>
+      <c r="H2018" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2019" spans="1:8">
+      <c r="A2019" s="3" t="s">
+        <v>2035</v>
+      </c>
+      <c r="B2019" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2019" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2019" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2019" s="3">
+        <v>8362</v>
+      </c>
+      <c r="F2019" s="3">
+        <v>10</v>
+      </c>
+      <c r="G2019" s="3">
+        <v>17901</v>
+      </c>
+      <c r="H2019" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2020" spans="1:8">
+      <c r="A2020" s="3" t="s">
+        <v>2036</v>
+      </c>
+      <c r="B2020" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2020" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2020" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2020" s="3">
+        <v>8354</v>
+      </c>
+      <c r="F2020" s="3">
+        <v>2</v>
+      </c>
+      <c r="G2020" s="3">
+        <v>13221</v>
+      </c>
+      <c r="H2020" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2021" spans="1:8">
+      <c r="A2021" s="3" t="s">
+        <v>2037</v>
+      </c>
+      <c r="B2021" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2021" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2021" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2021" s="3">
+        <v>8345</v>
+      </c>
+      <c r="F2021" s="3">
+        <v>4</v>
+      </c>
+      <c r="G2021" s="3">
+        <v>13774</v>
+      </c>
+      <c r="H2021" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2022" spans="1:8">
+      <c r="A2022" s="3" t="s">
+        <v>2038</v>
+      </c>
+      <c r="B2022" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2022" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2022" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2022" s="3">
+        <v>8320</v>
+      </c>
+      <c r="F2022" s="3">
+        <v>4</v>
+      </c>
+      <c r="G2022" s="3">
+        <v>12589</v>
+      </c>
+      <c r="H2022" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2023" spans="1:8">
+      <c r="A2023" s="3" t="s">
+        <v>2039</v>
+      </c>
+      <c r="B2023" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2023" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2023" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2023" s="3">
+        <v>8309</v>
+      </c>
+      <c r="F2023" s="3">
+        <v>10</v>
+      </c>
+      <c r="G2023" s="3">
+        <v>16361</v>
+      </c>
+      <c r="H2023" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2024" spans="1:8">
+      <c r="A2024" s="3" t="s">
+        <v>2040</v>
+      </c>
+      <c r="B2024" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2024" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2024" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2024" s="3">
+        <v>8302</v>
+      </c>
+      <c r="F2024" s="3">
+        <v>8</v>
+      </c>
+      <c r="G2024" s="3">
+        <v>16689</v>
+      </c>
+      <c r="H2024" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2025" spans="1:8">
+      <c r="A2025" s="3" t="s">
+        <v>2041</v>
+      </c>
+      <c r="B2025" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2025" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2025" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2025" s="3">
+        <v>8293</v>
+      </c>
+      <c r="F2025" s="3">
+        <v>5</v>
+      </c>
+      <c r="G2025" s="3">
+        <v>12740</v>
+      </c>
+      <c r="H2025" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2026" spans="1:8">
+      <c r="A2026" s="3" t="s">
+        <v>2042</v>
+      </c>
+      <c r="B2026" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2026" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2026" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2026" s="3">
+        <v>8293</v>
+      </c>
+      <c r="F2026" s="3">
+        <v>9</v>
+      </c>
+      <c r="G2026" s="3">
+        <v>15097</v>
+      </c>
+      <c r="H2026" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2027" spans="1:8">
+      <c r="A2027" s="3" t="s">
+        <v>2043</v>
+      </c>
+      <c r="B2027" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2027" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2027" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2027" s="3">
+        <v>8287</v>
+      </c>
+      <c r="F2027" s="3">
+        <v>1</v>
+      </c>
+      <c r="G2027" s="3">
+        <v>10634</v>
+      </c>
+      <c r="H2027" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2028" spans="1:8">
+      <c r="A2028" s="3" t="s">
+        <v>2044</v>
+      </c>
+      <c r="B2028" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2028" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2028" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2028" s="3">
+        <v>8272</v>
+      </c>
+      <c r="F2028" s="3">
+        <v>6</v>
+      </c>
+      <c r="G2028" s="3">
+        <v>13735</v>
+      </c>
+      <c r="H2028" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2029" spans="1:8">
+      <c r="A2029" s="3" t="s">
+        <v>2045</v>
+      </c>
+      <c r="B2029" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2029" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2029" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2029" s="3">
+        <v>8264</v>
+      </c>
+      <c r="F2029" s="3">
+        <v>6</v>
+      </c>
+      <c r="G2029" s="3">
+        <v>14845</v>
+      </c>
+      <c r="H2029" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2030" spans="1:8">
+      <c r="A2030" s="3" t="s">
+        <v>2046</v>
+      </c>
+      <c r="B2030" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2030" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2030" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2030" s="3">
+        <v>8235</v>
+      </c>
+      <c r="F2030" s="3">
+        <v>6</v>
+      </c>
+      <c r="G2030" s="3">
+        <v>14798</v>
+      </c>
+      <c r="H2030" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2031" spans="1:8">
+      <c r="A2031" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="B2031" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2031" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2031" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2031" s="3">
+        <v>8234</v>
+      </c>
+      <c r="F2031" s="3">
+        <v>1</v>
+      </c>
+      <c r="G2031" s="3">
+        <v>12603</v>
+      </c>
+      <c r="H2031" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2032" spans="1:8">
+      <c r="A2032" s="3" t="s">
+        <v>2048</v>
+      </c>
+      <c r="B2032" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2032" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2032" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2032" s="3">
+        <v>8232</v>
+      </c>
+      <c r="F2032" s="3">
+        <v>8</v>
+      </c>
+      <c r="G2032" s="3">
+        <v>15141</v>
+      </c>
+      <c r="H2032" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2033" spans="1:8">
+      <c r="A2033" s="3" t="s">
+        <v>2049</v>
+      </c>
+      <c r="B2033" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2033" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2033" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2033" s="3">
+        <v>8222</v>
+      </c>
+      <c r="F2033" s="3">
+        <v>3</v>
+      </c>
+      <c r="G2033" s="3">
+        <v>13853</v>
+      </c>
+      <c r="H2033" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2034" spans="1:8">
+      <c r="A2034" s="3" t="s">
+        <v>2050</v>
+      </c>
+      <c r="B2034" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2034" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2034" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2034" s="3">
+        <v>8198</v>
+      </c>
+      <c r="F2034" s="3">
+        <v>4</v>
+      </c>
+      <c r="G2034" s="3">
+        <v>13535</v>
+      </c>
+      <c r="H2034" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2035" spans="1:8">
+      <c r="A2035" s="3" t="s">
+        <v>2051</v>
+      </c>
+      <c r="B2035" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2035" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2035" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2035" s="3">
+        <v>8195</v>
+      </c>
+      <c r="F2035" s="3">
+        <v>6</v>
+      </c>
+      <c r="G2035" s="3">
+        <v>14408</v>
+      </c>
+      <c r="H2035" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2036" spans="1:8">
+      <c r="A2036" s="3" t="s">
+        <v>2052</v>
+      </c>
+      <c r="B2036" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2036" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2036" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2036" s="3">
+        <v>8175</v>
+      </c>
+      <c r="F2036" s="3">
+        <v>3</v>
+      </c>
+      <c r="G2036" s="3">
+        <v>10986</v>
+      </c>
+      <c r="H2036" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2037" spans="1:8">
+      <c r="A2037" s="3" t="s">
+        <v>2053</v>
+      </c>
+      <c r="B2037" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2037" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2037" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2037" s="3">
+        <v>8166</v>
+      </c>
+      <c r="F2037" s="3">
+        <v>9</v>
+      </c>
+      <c r="G2037" s="3">
+        <v>14657</v>
+      </c>
+      <c r="H2037" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2038" spans="1:8">
+      <c r="A2038" s="3" t="s">
+        <v>2054</v>
+      </c>
+      <c r="B2038" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2038" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2038" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2038" s="3">
+        <v>8163</v>
+      </c>
+      <c r="F2038" s="3">
+        <v>5</v>
+      </c>
+      <c r="G2038" s="3">
+        <v>13238</v>
+      </c>
+      <c r="H2038" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2039" spans="1:8">
+      <c r="A2039" s="3" t="s">
+        <v>2055</v>
+      </c>
+      <c r="B2039" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2039" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2039" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2039" s="3">
+        <v>8157</v>
+      </c>
+      <c r="F2039" s="3">
+        <v>0</v>
+      </c>
+      <c r="G2039" s="3">
+        <v>11274</v>
+      </c>
+      <c r="H2039" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2040" spans="1:8">
+      <c r="A2040" s="3" t="s">
+        <v>2056</v>
+      </c>
+      <c r="B2040" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2040" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2040" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2040" s="3">
+        <v>8137</v>
+      </c>
+      <c r="F2040" s="3">
+        <v>3</v>
+      </c>
+      <c r="G2040" s="3">
+        <v>12614</v>
+      </c>
+      <c r="H2040" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2041" spans="1:8">
+      <c r="A2041" s="3" t="s">
+        <v>2057</v>
+      </c>
+      <c r="B2041" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2041" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2041" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2041" s="3">
+        <v>8113</v>
+      </c>
+      <c r="F2041" s="3">
+        <v>6</v>
+      </c>
+      <c r="G2041" s="3">
+        <v>13256</v>
+      </c>
+      <c r="H2041" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2042" spans="1:8">
+      <c r="A2042" s="3" t="s">
+        <v>2058</v>
+      </c>
+      <c r="B2042" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2042" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2042" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2042" s="3">
+        <v>8076</v>
+      </c>
+      <c r="F2042" s="3">
+        <v>4</v>
+      </c>
+      <c r="G2042" s="3">
+        <v>11964</v>
+      </c>
+      <c r="H2042" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2043" spans="1:8">
+      <c r="A2043" s="3" t="s">
+        <v>2059</v>
+      </c>
+      <c r="B2043" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2043" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2043" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2043" s="3">
+        <v>8076</v>
+      </c>
+      <c r="F2043" s="3">
+        <v>6</v>
+      </c>
+      <c r="G2043" s="3">
+        <v>14750</v>
+      </c>
+      <c r="H2043" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2044" spans="1:8">
+      <c r="A2044" s="3" t="s">
+        <v>2060</v>
+      </c>
+      <c r="B2044" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2044" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2044" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2044" s="3">
+        <v>8071</v>
+      </c>
+      <c r="F2044" s="3">
+        <v>8</v>
+      </c>
+      <c r="G2044" s="3">
+        <v>16091</v>
+      </c>
+      <c r="H2044" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2045" spans="1:8">
+      <c r="A2045" s="3" t="s">
+        <v>2061</v>
+      </c>
+      <c r="B2045" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2045" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2045" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2045" s="3">
+        <v>8037</v>
+      </c>
+      <c r="F2045" s="3">
+        <v>5</v>
+      </c>
+      <c r="G2045" s="3">
+        <v>13601</v>
+      </c>
+      <c r="H2045" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2046" spans="1:8">
+      <c r="A2046" s="3" t="s">
+        <v>2062</v>
+      </c>
+      <c r="B2046" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2046" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2046" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2046" s="3">
+        <v>8032</v>
+      </c>
+      <c r="F2046" s="3">
+        <v>3</v>
+      </c>
+      <c r="G2046" s="3">
+        <v>11291</v>
+      </c>
+      <c r="H2046" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2047" spans="1:8">
+      <c r="A2047" s="3" t="s">
+        <v>2063</v>
+      </c>
+      <c r="B2047" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2047" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2047" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2047" s="3">
+        <v>8020</v>
+      </c>
+      <c r="F2047" s="3">
+        <v>3</v>
+      </c>
+      <c r="G2047" s="3">
+        <v>12899</v>
+      </c>
+      <c r="H2047" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2048" spans="1:8">
+      <c r="A2048" s="3" t="s">
+        <v>2064</v>
+      </c>
+      <c r="B2048" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2048" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2048" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2048" s="3">
+        <v>8009</v>
+      </c>
+      <c r="F2048" s="3">
+        <v>0</v>
+      </c>
+      <c r="G2048" s="3">
+        <v>9818</v>
+      </c>
+      <c r="H2048" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2049" spans="1:8">
+      <c r="A2049" s="3" t="s">
+        <v>2065</v>
+      </c>
+      <c r="B2049" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2049" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2049" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2049" s="3">
+        <v>7999</v>
+      </c>
+      <c r="F2049" s="3">
+        <v>1</v>
+      </c>
+      <c r="G2049" s="3">
+        <v>11219</v>
+      </c>
+      <c r="H2049" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2050" spans="1:8">
+      <c r="A2050" s="3" t="s">
+        <v>2066</v>
+      </c>
+      <c r="B2050" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2050" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2050" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2050" s="3">
+        <v>7985</v>
+      </c>
+      <c r="F2050" s="3">
+        <v>0</v>
+      </c>
+      <c r="G2050" s="3">
+        <v>10174</v>
+      </c>
+      <c r="H2050" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2051" spans="1:8">
+      <c r="A2051" s="3" t="s">
+        <v>2067</v>
+      </c>
+      <c r="B2051" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2051" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2051" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2051" s="3">
+        <v>7973</v>
+      </c>
+      <c r="F2051" s="3">
+        <v>3</v>
+      </c>
+      <c r="G2051" s="3">
+        <v>13398</v>
+      </c>
+      <c r="H2051" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2052" spans="1:8">
+      <c r="A2052" s="3" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B2052" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2052" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2052" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2052" s="3">
+        <v>7969</v>
+      </c>
+      <c r="F2052" s="3">
+        <v>10</v>
+      </c>
+      <c r="G2052" s="3">
+        <v>16532</v>
+      </c>
+      <c r="H2052" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2053" spans="1:8">
+      <c r="A2053" s="3" t="s">
+        <v>2069</v>
+      </c>
+      <c r="B2053" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2053" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2053" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2053" s="3">
+        <v>7969</v>
+      </c>
+      <c r="F2053" s="3">
+        <v>10</v>
+      </c>
+      <c r="G2053" s="3">
+        <v>16713</v>
+      </c>
+      <c r="H2053" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2054" spans="1:8">
+      <c r="A2054" s="3" t="s">
+        <v>2070</v>
+      </c>
+      <c r="B2054" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2054" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2054" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2054" s="3">
+        <v>7961</v>
+      </c>
+      <c r="F2054" s="3">
+        <v>9</v>
+      </c>
+      <c r="G2054" s="3">
+        <v>16543</v>
+      </c>
+      <c r="H2054" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2055" spans="1:8">
+      <c r="A2055" s="3" t="s">
+        <v>2071</v>
+      </c>
+      <c r="B2055" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2055" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2055" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2055" s="3">
+        <v>7951</v>
+      </c>
+      <c r="F2055" s="3">
+        <v>8</v>
+      </c>
+      <c r="G2055" s="3">
+        <v>15397</v>
+      </c>
+      <c r="H2055" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2056" spans="1:8">
+      <c r="A2056" s="3" t="s">
+        <v>2072</v>
+      </c>
+      <c r="B2056" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2056" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2056" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2056" s="3">
+        <v>7945</v>
+      </c>
+      <c r="F2056" s="3">
+        <v>5</v>
+      </c>
+      <c r="G2056" s="3">
+        <v>13552</v>
+      </c>
+      <c r="H2056" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2057" spans="1:8">
+      <c r="A2057" s="3" t="s">
+        <v>2073</v>
+      </c>
+      <c r="B2057" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2057" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2057" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2057" s="3">
+        <v>7932</v>
+      </c>
+      <c r="F2057" s="3">
+        <v>6</v>
+      </c>
+      <c r="G2057" s="3">
+        <v>14477</v>
+      </c>
+      <c r="H2057" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2058" spans="1:8">
+      <c r="A2058" s="3" t="s">
+        <v>2074</v>
+      </c>
+      <c r="B2058" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2058" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2058" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2058" s="3">
+        <v>7906</v>
+      </c>
+      <c r="F2058" s="3">
+        <v>5</v>
+      </c>
+      <c r="G2058" s="3">
+        <v>12650</v>
+      </c>
+      <c r="H2058" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2059" spans="1:8">
+      <c r="A2059" s="3" t="s">
+        <v>2075</v>
+      </c>
+      <c r="B2059" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2059" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2059" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2059" s="3">
+        <v>7883</v>
+      </c>
+      <c r="F2059" s="3">
+        <v>9</v>
+      </c>
+      <c r="G2059" s="3">
+        <v>15914</v>
+      </c>
+      <c r="H2059" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2060" spans="1:8">
+      <c r="A2060" s="3" t="s">
+        <v>2076</v>
+      </c>
+      <c r="B2060" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2060" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2060" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2060" s="3">
+        <v>7875</v>
+      </c>
+      <c r="F2060" s="3">
+        <v>1</v>
+      </c>
+      <c r="G2060" s="3">
+        <v>10748</v>
+      </c>
+      <c r="H2060" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2061" spans="1:8">
+      <c r="A2061" s="3" t="s">
+        <v>2077</v>
+      </c>
+      <c r="B2061" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2061" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2061" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2061" s="3">
+        <v>7865</v>
+      </c>
+      <c r="F2061" s="3">
+        <v>1</v>
+      </c>
+      <c r="G2061" s="3">
+        <v>11823</v>
+      </c>
+      <c r="H2061" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2062" spans="1:8">
+      <c r="A2062" s="3" t="s">
+        <v>2078</v>
+      </c>
+      <c r="B2062" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2062" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2062" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2062" s="3">
+        <v>7863</v>
+      </c>
+      <c r="F2062" s="3">
+        <v>10</v>
+      </c>
+      <c r="G2062" s="3">
+        <v>15643</v>
+      </c>
+      <c r="H2062" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2063" spans="1:8">
+      <c r="A2063" s="3" t="s">
+        <v>2079</v>
+      </c>
+      <c r="B2063" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2063" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2063" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2063" s="3">
+        <v>7832</v>
+      </c>
+      <c r="F2063" s="3">
+        <v>8</v>
+      </c>
+      <c r="G2063" s="3">
+        <v>14637</v>
+      </c>
+      <c r="H2063" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2064" spans="1:8">
+      <c r="A2064" s="3" t="s">
+        <v>2080</v>
+      </c>
+      <c r="B2064" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2064" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2064" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2064" s="3">
+        <v>7815</v>
+      </c>
+      <c r="F2064" s="3">
+        <v>9</v>
+      </c>
+      <c r="G2064" s="3">
+        <v>15298</v>
+      </c>
+      <c r="H2064" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2065" spans="1:8">
+      <c r="A2065" s="3" t="s">
+        <v>2081</v>
+      </c>
+      <c r="B2065" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2065" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2065" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2065" s="3">
+        <v>7814</v>
+      </c>
+      <c r="F2065" s="3">
+        <v>6</v>
+      </c>
+      <c r="G2065" s="3">
+        <v>15158</v>
+      </c>
+      <c r="H2065" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2066" spans="1:8">
+      <c r="A2066" s="3" t="s">
+        <v>2082</v>
+      </c>
+      <c r="B2066" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2066" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2066" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2066" s="3">
+        <v>7786</v>
+      </c>
+      <c r="F2066" s="3">
+        <v>3</v>
+      </c>
+      <c r="G2066" s="3">
+        <v>13483</v>
+      </c>
+      <c r="H2066" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2067" spans="1:8">
+      <c r="A2067" s="3" t="s">
+        <v>2083</v>
+      </c>
+      <c r="B2067" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2067" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2067" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2067" s="3">
+        <v>7783</v>
+      </c>
+      <c r="F2067" s="3">
+        <v>6</v>
+      </c>
+      <c r="G2067" s="3">
+        <v>14058</v>
+      </c>
+      <c r="H2067" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2068" spans="1:8">
+      <c r="A2068" s="3" t="s">
+        <v>2084</v>
+      </c>
+      <c r="B2068" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2068" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2068" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2068" s="3">
+        <v>7764</v>
+      </c>
+      <c r="F2068" s="3">
+        <v>2</v>
+      </c>
+      <c r="G2068" s="3">
+        <v>11901</v>
+      </c>
+      <c r="H2068" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2069" spans="1:8">
+      <c r="A2069" s="3" t="s">
+        <v>2085</v>
+      </c>
+      <c r="B2069" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2069" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2069" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2069" s="3">
+        <v>7740</v>
+      </c>
+      <c r="F2069" s="3">
+        <v>6</v>
+      </c>
+      <c r="G2069" s="3">
+        <v>12945</v>
+      </c>
+      <c r="H2069" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2070" spans="1:8">
+      <c r="A2070" s="3" t="s">
+        <v>2086</v>
+      </c>
+      <c r="B2070" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2070" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2070" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2070" s="3">
+        <v>7737</v>
+      </c>
+      <c r="F2070" s="3">
+        <v>1</v>
+      </c>
+      <c r="G2070" s="3">
+        <v>12057</v>
+      </c>
+      <c r="H2070" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2071" spans="1:8">
+      <c r="A2071" s="3" t="s">
+        <v>2087</v>
+      </c>
+      <c r="B2071" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2071" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2071" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2071" s="3">
+        <v>7734</v>
+      </c>
+      <c r="F2071" s="3">
+        <v>9</v>
+      </c>
+      <c r="G2071" s="3">
+        <v>14725</v>
+      </c>
+      <c r="H2071" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2072" spans="1:8">
+      <c r="A2072" s="3" t="s">
+        <v>2088</v>
+      </c>
+      <c r="B2072" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2072" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2072" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2072" s="3">
+        <v>7720</v>
+      </c>
+      <c r="F2072" s="3">
+        <v>6</v>
+      </c>
+      <c r="G2072" s="3">
+        <v>15259</v>
+      </c>
+      <c r="H2072" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2073" spans="1:8">
+      <c r="A2073" s="3" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B2073" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2073" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2073" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2073" s="3">
+        <v>7718</v>
+      </c>
+      <c r="F2073" s="3">
+        <v>9</v>
+      </c>
+      <c r="G2073" s="3">
+        <v>14228</v>
+      </c>
+      <c r="H2073" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2074" spans="1:8">
+      <c r="A2074" s="3" t="s">
+        <v>2090</v>
+      </c>
+      <c r="B2074" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2074" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2074" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2074" s="3">
+        <v>7696</v>
+      </c>
+      <c r="F2074" s="3">
+        <v>4</v>
+      </c>
+      <c r="G2074" s="3">
+        <v>12663</v>
+      </c>
+      <c r="H2074" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2075" spans="1:8">
+      <c r="A2075" s="3" t="s">
+        <v>2091</v>
+      </c>
+      <c r="B2075" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2075" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2075" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2075" s="3">
+        <v>7688</v>
+      </c>
+      <c r="F2075" s="3">
+        <v>5</v>
+      </c>
+      <c r="G2075" s="3">
+        <v>11761</v>
+      </c>
+      <c r="H2075" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2076" spans="1:8">
+      <c r="A2076" s="3" t="s">
+        <v>2092</v>
+      </c>
+      <c r="B2076" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2076" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2076" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2076" s="3">
+        <v>7675</v>
+      </c>
+      <c r="F2076" s="3">
+        <v>6</v>
+      </c>
+      <c r="G2076" s="3">
+        <v>14977</v>
+      </c>
+      <c r="H2076" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2077" spans="1:8">
+      <c r="A2077" s="3" t="s">
+        <v>2093</v>
+      </c>
+      <c r="B2077" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2077" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2077" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2077" s="3">
+        <v>7673</v>
+      </c>
+      <c r="F2077" s="3">
+        <v>3</v>
+      </c>
+      <c r="G2077" s="3">
+        <v>12352</v>
+      </c>
+      <c r="H2077" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2078" spans="1:8">
+      <c r="A2078" s="3" t="s">
+        <v>2094</v>
+      </c>
+      <c r="B2078" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2078" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2078" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2078" s="3">
+        <v>7672</v>
+      </c>
+      <c r="F2078" s="3">
+        <v>0</v>
+      </c>
+      <c r="G2078" s="3">
+        <v>10057</v>
+      </c>
+      <c r="H2078" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2079" spans="1:8">
+      <c r="A2079" s="3" t="s">
+        <v>2095</v>
+      </c>
+      <c r="B2079" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2079" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2079" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2079" s="3">
+        <v>7670</v>
+      </c>
+      <c r="F2079" s="3">
+        <v>2</v>
+      </c>
+      <c r="G2079" s="3">
+        <v>10857</v>
+      </c>
+      <c r="H2079" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2080" spans="1:8">
+      <c r="A2080" s="3" t="s">
+        <v>2096</v>
+      </c>
+      <c r="B2080" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2080" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2080" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2080" s="3">
+        <v>7664</v>
+      </c>
+      <c r="F2080" s="3">
+        <v>5</v>
+      </c>
+      <c r="G2080" s="3">
+        <v>13542</v>
+      </c>
+      <c r="H2080" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2081" spans="1:8">
+      <c r="A2081" s="3" t="s">
+        <v>2097</v>
+      </c>
+      <c r="B2081" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2081" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2081" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2081" s="3">
+        <v>7634</v>
+      </c>
+      <c r="F2081" s="3">
+        <v>9</v>
+      </c>
+      <c r="G2081" s="3">
+        <v>15995</v>
+      </c>
+      <c r="H2081" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2082" spans="1:8">
+      <c r="A2082" s="3" t="s">
+        <v>2098</v>
+      </c>
+      <c r="B2082" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2082" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2082" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2082" s="3">
+        <v>7597</v>
+      </c>
+      <c r="F2082" s="3">
+        <v>1</v>
+      </c>
+      <c r="G2082" s="3">
+        <v>10593</v>
+      </c>
+      <c r="H2082" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2083" spans="1:8">
+      <c r="A2083" s="3" t="s">
+        <v>2099</v>
+      </c>
+      <c r="B2083" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2083" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2083" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2083" s="3">
+        <v>7566</v>
+      </c>
+      <c r="F2083" s="3">
+        <v>7</v>
+      </c>
+      <c r="G2083" s="3">
+        <v>14833</v>
+      </c>
+      <c r="H2083" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2084" spans="1:8">
+      <c r="A2084" s="3" t="s">
+        <v>2100</v>
+      </c>
+      <c r="B2084" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2084" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2084" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2084" s="3">
+        <v>7548</v>
+      </c>
+      <c r="F2084" s="3">
+        <v>4</v>
+      </c>
+      <c r="G2084" s="3">
+        <v>13697</v>
+      </c>
+      <c r="H2084" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2085" spans="1:8">
+      <c r="A2085" s="3" t="s">
+        <v>2101</v>
+      </c>
+      <c r="B2085" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2085" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2085" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2085" s="3">
+        <v>7538</v>
+      </c>
+      <c r="F2085" s="3">
+        <v>6</v>
+      </c>
+      <c r="G2085" s="3">
+        <v>14336</v>
+      </c>
+      <c r="H2085" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2086" spans="1:8">
+      <c r="A2086" s="3" t="s">
+        <v>2102</v>
+      </c>
+      <c r="B2086" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2086" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2086" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2086" s="3">
+        <v>7531</v>
+      </c>
+      <c r="F2086" s="3">
+        <v>1</v>
+      </c>
+      <c r="G2086" s="3">
+        <v>10480</v>
+      </c>
+      <c r="H2086" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2087" spans="1:8">
+      <c r="A2087" s="3" t="s">
+        <v>2103</v>
+      </c>
+      <c r="B2087" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2087" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2087" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2087" s="3">
+        <v>7523</v>
+      </c>
+      <c r="F2087" s="3">
+        <v>5</v>
+      </c>
+      <c r="G2087" s="3">
+        <v>13409</v>
+      </c>
+      <c r="H2087" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2088" spans="1:8">
+      <c r="A2088" s="3" t="s">
+        <v>2104</v>
+      </c>
+      <c r="B2088" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2088" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2088" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2088" s="3">
+        <v>7518</v>
+      </c>
+      <c r="F2088" s="3">
+        <v>8</v>
+      </c>
+      <c r="G2088" s="3">
+        <v>14258</v>
+      </c>
+      <c r="H2088" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2089" spans="1:8">
+      <c r="A2089" s="3" t="s">
+        <v>2105</v>
+      </c>
+      <c r="B2089" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2089" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2089" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2089" s="3">
+        <v>7516</v>
+      </c>
+      <c r="F2089" s="3">
+        <v>0</v>
+      </c>
+      <c r="G2089" s="3">
+        <v>11262</v>
+      </c>
+      <c r="H2089" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2090" spans="1:8">
+      <c r="A2090" s="3" t="s">
+        <v>2106</v>
+      </c>
+      <c r="B2090" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2090" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2090" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2090" s="3">
+        <v>7515</v>
+      </c>
+      <c r="F2090" s="3">
+        <v>9</v>
+      </c>
+      <c r="G2090" s="3">
+        <v>15312</v>
+      </c>
+      <c r="H2090" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2091" spans="1:8">
+      <c r="A2091" s="3" t="s">
+        <v>2107</v>
+      </c>
+      <c r="B2091" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2091" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2091" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2091" s="3">
+        <v>7513</v>
+      </c>
+      <c r="F2091" s="3">
+        <v>9</v>
+      </c>
+      <c r="G2091" s="3">
+        <v>14532</v>
+      </c>
+      <c r="H2091" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2092" spans="1:8">
+      <c r="A2092" s="3" t="s">
+        <v>2108</v>
+      </c>
+      <c r="B2092" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2092" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2092" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2092" s="3">
+        <v>7491</v>
+      </c>
+      <c r="F2092" s="3">
+        <v>6</v>
+      </c>
+      <c r="G2092" s="3">
+        <v>14143</v>
+      </c>
+      <c r="H2092" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2093" spans="1:8">
+      <c r="A2093" s="3" t="s">
+        <v>2109</v>
+      </c>
+      <c r="B2093" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2093" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2093" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2093" s="3">
+        <v>7491</v>
+      </c>
+      <c r="F2093" s="3">
+        <v>3</v>
+      </c>
+      <c r="G2093" s="3">
+        <v>11816</v>
+      </c>
+      <c r="H2093" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2094" spans="1:8">
+      <c r="A2094" s="3" t="s">
+        <v>2110</v>
+      </c>
+      <c r="B2094" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2094" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2094" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2094" s="3">
+        <v>7428</v>
+      </c>
+      <c r="F2094" s="3">
+        <v>8</v>
+      </c>
+      <c r="G2094" s="3">
+        <v>14820</v>
+      </c>
+      <c r="H2094" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2095" spans="1:8">
+      <c r="A2095" s="3" t="s">
+        <v>2111</v>
+      </c>
+      <c r="B2095" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2095" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2095" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2095" s="3">
+        <v>7408</v>
+      </c>
+      <c r="F2095" s="3">
+        <v>10</v>
+      </c>
+      <c r="G2095" s="3">
+        <v>15029</v>
+      </c>
+      <c r="H2095" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2096" spans="1:8">
+      <c r="A2096" s="3" t="s">
+        <v>2112</v>
+      </c>
+      <c r="B2096" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2096" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2096" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2096" s="3">
+        <v>7382</v>
+      </c>
+      <c r="F2096" s="3">
+        <v>8</v>
+      </c>
+      <c r="G2096" s="3">
+        <v>14361</v>
+      </c>
+      <c r="H2096" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2097" spans="1:8">
+      <c r="A2097" s="3" t="s">
+        <v>2113</v>
+      </c>
+      <c r="B2097" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2097" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2097" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2097" s="3">
+        <v>7373</v>
+      </c>
+      <c r="F2097" s="3">
+        <v>9</v>
+      </c>
+      <c r="G2097" s="3">
+        <v>16155</v>
+      </c>
+      <c r="H2097" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2098" spans="1:8">
+      <c r="A2098" s="3" t="s">
+        <v>2114</v>
+      </c>
+      <c r="B2098" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2098" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2098" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2098" s="3">
+        <v>7368</v>
+      </c>
+      <c r="F2098" s="3">
+        <v>8</v>
+      </c>
+      <c r="G2098" s="3">
+        <v>14704</v>
+      </c>
+      <c r="H2098" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2099" spans="1:8">
+      <c r="A2099" s="3" t="s">
+        <v>2115</v>
+      </c>
+      <c r="B2099" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2099" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2099" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2099" s="3">
+        <v>7361</v>
+      </c>
+      <c r="F2099" s="3">
+        <v>10</v>
+      </c>
+      <c r="G2099" s="3">
+        <v>15920</v>
+      </c>
+      <c r="H2099" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2100" spans="1:8">
+      <c r="A2100" s="3" t="s">
+        <v>2116</v>
+      </c>
+      <c r="B2100" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2100" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2100" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2100" s="3">
+        <v>7342</v>
+      </c>
+      <c r="F2100" s="3">
+        <v>10</v>
+      </c>
+      <c r="G2100" s="3">
+        <v>16753</v>
+      </c>
+      <c r="H2100" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2101" spans="1:8">
+      <c r="A2101" s="3" t="s">
+        <v>2117</v>
+      </c>
+      <c r="B2101" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2101" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2101" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2101" s="3">
+        <v>7326</v>
+      </c>
+      <c r="F2101" s="3">
+        <v>1</v>
+      </c>
+      <c r="G2101" s="3">
+        <v>11346</v>
+      </c>
+      <c r="H2101" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2102" spans="1:8">
+      <c r="A2102" s="3" t="s">
+        <v>2118</v>
+      </c>
+      <c r="B2102" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2102" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2102" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2102" s="3">
+        <v>7324</v>
+      </c>
+      <c r="F2102" s="3">
+        <v>4</v>
+      </c>
+      <c r="G2102" s="3">
+        <v>11302</v>
+      </c>
+      <c r="H2102" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2103" spans="1:8">
+      <c r="A2103" s="3" t="s">
+        <v>2119</v>
+      </c>
+      <c r="B2103" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2103" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2103" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2103" s="3">
+        <v>7308</v>
+      </c>
+      <c r="F2103" s="3">
+        <v>5</v>
+      </c>
+      <c r="G2103" s="3">
+        <v>12968</v>
+      </c>
+      <c r="H2103" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2104" spans="1:8">
+      <c r="A2104" s="3" t="s">
+        <v>2120</v>
+      </c>
+      <c r="B2104" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2104" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2104" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2104" s="3">
+        <v>7293</v>
+      </c>
+      <c r="F2104" s="3">
+        <v>1</v>
+      </c>
+      <c r="G2104" s="3">
+        <v>10293</v>
+      </c>
+      <c r="H2104" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2105" spans="1:8">
+      <c r="A2105" s="3" t="s">
+        <v>2121</v>
+      </c>
+      <c r="B2105" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2105" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2105" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2105" s="3">
+        <v>7291</v>
+      </c>
+      <c r="F2105" s="3">
+        <v>1</v>
+      </c>
+      <c r="G2105" s="3">
+        <v>9587</v>
+      </c>
+      <c r="H2105" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2106" spans="1:8">
+      <c r="A2106" s="3" t="s">
+        <v>2122</v>
+      </c>
+      <c r="B2106" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2106" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2106" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2106" s="3">
+        <v>7287</v>
+      </c>
+      <c r="F2106" s="3">
+        <v>0</v>
+      </c>
+      <c r="G2106" s="3">
+        <v>9870</v>
+      </c>
+      <c r="H2106" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2107" spans="1:8">
+      <c r="A2107" s="3" t="s">
+        <v>2123</v>
+      </c>
+      <c r="B2107" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2107" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2107" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2107" s="3">
+        <v>7284</v>
+      </c>
+      <c r="F2107" s="3">
+        <v>7</v>
+      </c>
+      <c r="G2107" s="3">
+        <v>14740</v>
+      </c>
+      <c r="H2107" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2108" spans="1:8">
+      <c r="A2108" s="3" t="s">
+        <v>2124</v>
+      </c>
+      <c r="B2108" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2108" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2108" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2108" s="3">
+        <v>7263</v>
+      </c>
+      <c r="F2108" s="3">
+        <v>2</v>
+      </c>
+      <c r="G2108" s="3">
+        <v>12408</v>
+      </c>
+      <c r="H2108" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2109" spans="1:8">
+      <c r="A2109" s="3" t="s">
+        <v>2125</v>
+      </c>
+      <c r="B2109" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2109" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2109" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2109" s="3">
+        <v>7253</v>
+      </c>
+      <c r="F2109" s="3">
+        <v>4</v>
+      </c>
+      <c r="G2109" s="3">
+        <v>13319</v>
+      </c>
+      <c r="H2109" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2110" spans="1:8">
+      <c r="A2110" s="3" t="s">
+        <v>2126</v>
+      </c>
+      <c r="B2110" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2110" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2110" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2110" s="3">
+        <v>7247</v>
+      </c>
+      <c r="F2110" s="3">
+        <v>9</v>
+      </c>
+      <c r="G2110" s="3">
+        <v>14680</v>
+      </c>
+      <c r="H2110" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2111" spans="1:8">
+      <c r="A2111" s="3" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B2111" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2111" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2111" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2111" s="3">
+        <v>7201</v>
+      </c>
+      <c r="F2111" s="3">
+        <v>9</v>
+      </c>
+      <c r="G2111" s="3">
+        <v>15772</v>
+      </c>
+      <c r="H2111" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2112" spans="1:8">
+      <c r="A2112" s="3" t="s">
+        <v>2128</v>
+      </c>
+      <c r="B2112" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2112" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2112" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2112" s="3">
+        <v>7192</v>
+      </c>
+      <c r="F2112" s="3">
+        <v>10</v>
+      </c>
+      <c r="G2112" s="3">
+        <v>14600</v>
+      </c>
+      <c r="H2112" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2113" spans="1:8">
+      <c r="A2113" s="3" t="s">
+        <v>2129</v>
+      </c>
+      <c r="B2113" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2113" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2113" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2113" s="3">
+        <v>7185</v>
+      </c>
+      <c r="F2113" s="3">
+        <v>6</v>
+      </c>
+      <c r="G2113" s="3">
+        <v>11880</v>
+      </c>
+      <c r="H2113" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2114" spans="1:8">
+      <c r="A2114" s="3" t="s">
+        <v>2130</v>
+      </c>
+      <c r="B2114" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2114" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2114" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2114" s="3">
+        <v>7142</v>
+      </c>
+      <c r="F2114" s="3">
+        <v>9</v>
+      </c>
+      <c r="G2114" s="3">
+        <v>16522</v>
+      </c>
+      <c r="H2114" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2115" spans="1:8">
+      <c r="A2115" s="3" t="s">
+        <v>2131</v>
+      </c>
+      <c r="B2115" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2115" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2115" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2115" s="3">
+        <v>7083</v>
+      </c>
+      <c r="F2115" s="3">
+        <v>10</v>
+      </c>
+      <c r="G2115" s="3">
+        <v>15829</v>
+      </c>
+      <c r="H2115" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2116" spans="1:8">
+      <c r="A2116" s="3" t="s">
+        <v>2132</v>
+      </c>
+      <c r="B2116" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2116" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2116" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2116" s="3">
+        <v>7083</v>
+      </c>
+      <c r="F2116" s="3">
+        <v>7</v>
+      </c>
+      <c r="G2116" s="3">
+        <v>15051</v>
+      </c>
+      <c r="H2116" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2117" spans="1:8">
+      <c r="A2117" s="3" t="s">
+        <v>2133</v>
+      </c>
+      <c r="B2117" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2117" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2117" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2117" s="3">
+        <v>7083</v>
+      </c>
+      <c r="F2117" s="3">
+        <v>1</v>
+      </c>
+      <c r="G2117" s="3">
+        <v>8816</v>
+      </c>
+      <c r="H2117" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2118" spans="1:8">
+      <c r="A2118" s="3" t="s">
+        <v>2134</v>
+      </c>
+      <c r="B2118" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2118" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2118" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2118" s="3">
+        <v>7078</v>
+      </c>
+      <c r="F2118" s="3">
+        <v>7</v>
+      </c>
+      <c r="G2118" s="3">
+        <v>12410</v>
+      </c>
+      <c r="H2118" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2119" spans="1:8">
+      <c r="A2119" s="3" t="s">
+        <v>2135</v>
+      </c>
+      <c r="B2119" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2119" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2119" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2119" s="3">
+        <v>7075</v>
+      </c>
+      <c r="F2119" s="3">
+        <v>8</v>
+      </c>
+      <c r="G2119" s="3">
+        <v>13210</v>
+      </c>
+      <c r="H2119" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2120" spans="1:8">
+      <c r="A2120" s="3" t="s">
+        <v>2136</v>
+      </c>
+      <c r="B2120" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2120" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2120" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2120" s="3">
+        <v>7066</v>
+      </c>
+      <c r="F2120" s="3">
+        <v>8</v>
+      </c>
+      <c r="G2120" s="3">
+        <v>14348</v>
+      </c>
+      <c r="H2120" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2121" spans="1:8">
+      <c r="A2121" s="3" t="s">
+        <v>2137</v>
+      </c>
+      <c r="B2121" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2121" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2121" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2121" s="3">
+        <v>7062</v>
+      </c>
+      <c r="F2121" s="3">
+        <v>9</v>
+      </c>
+      <c r="G2121" s="3">
+        <v>16199</v>
+      </c>
+      <c r="H2121" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2122" spans="1:8">
+      <c r="A2122" s="3" t="s">
+        <v>2138</v>
+      </c>
+      <c r="B2122" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2122" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2122" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2122" s="3">
+        <v>7057</v>
+      </c>
+      <c r="F2122" s="3">
+        <v>4</v>
+      </c>
+      <c r="G2122" s="3">
+        <v>12669</v>
+      </c>
+      <c r="H2122" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2123" spans="1:8">
+      <c r="A2123" s="3" t="s">
+        <v>2139</v>
+      </c>
+      <c r="B2123" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2123" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2123" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2123" s="3">
+        <v>7052</v>
+      </c>
+      <c r="F2123" s="3">
+        <v>4</v>
+      </c>
+      <c r="G2123" s="3">
+        <v>11401</v>
+      </c>
+      <c r="H2123" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2124" spans="1:8">
+      <c r="A2124" s="3" t="s">
+        <v>2140</v>
+      </c>
+      <c r="B2124" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2124" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2124" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2124" s="3">
+        <v>7047</v>
+      </c>
+      <c r="F2124" s="3">
+        <v>7</v>
+      </c>
+      <c r="G2124" s="3">
+        <v>13716</v>
+      </c>
+      <c r="H2124" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2125" spans="1:8">
+      <c r="A2125" s="3" t="s">
+        <v>2141</v>
+      </c>
+      <c r="B2125" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2125" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2125" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2125" s="3">
+        <v>7010</v>
+      </c>
+      <c r="F2125" s="3">
+        <v>0</v>
+      </c>
+      <c r="G2125" s="3">
+        <v>8313</v>
+      </c>
+      <c r="H2125" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2126" spans="1:8">
+      <c r="A2126" s="3" t="s">
+        <v>2142</v>
+      </c>
+      <c r="B2126" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2126" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2126" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2126" s="3">
+        <v>6985</v>
+      </c>
+      <c r="F2126" s="3">
+        <v>9</v>
+      </c>
+      <c r="G2126" s="3">
+        <v>14590</v>
+      </c>
+      <c r="H2126" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2127" spans="1:8">
+      <c r="A2127" s="3" t="s">
+        <v>2143</v>
+      </c>
+      <c r="B2127" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2127" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2127" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2127" s="3">
+        <v>6971</v>
+      </c>
+      <c r="F2127" s="3">
+        <v>2</v>
+      </c>
+      <c r="G2127" s="3">
+        <v>10648</v>
+      </c>
+      <c r="H2127" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2128" spans="1:8">
+      <c r="A2128" s="3" t="s">
+        <v>2144</v>
+      </c>
+      <c r="B2128" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2128" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2128" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2128" s="3">
+        <v>6962</v>
+      </c>
+      <c r="F2128" s="3">
+        <v>9</v>
+      </c>
+      <c r="G2128" s="3">
+        <v>14062</v>
+      </c>
+      <c r="H2128" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2129" spans="1:8">
+      <c r="A2129" s="3" t="s">
+        <v>2145</v>
+      </c>
+      <c r="B2129" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2129" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2129" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2129" s="3">
+        <v>6956</v>
+      </c>
+      <c r="F2129" s="3">
+        <v>6</v>
+      </c>
+      <c r="G2129" s="3">
+        <v>12278</v>
+      </c>
+      <c r="H2129" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2130" spans="1:8">
+      <c r="A2130" s="3" t="s">
+        <v>2146</v>
+      </c>
+      <c r="B2130" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2130" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2130" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2130" s="3">
+        <v>6939</v>
+      </c>
+      <c r="F2130" s="3">
+        <v>5</v>
+      </c>
+      <c r="G2130" s="3">
+        <v>12450</v>
+      </c>
+      <c r="H2130" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2131" spans="1:8">
+      <c r="A2131" s="3" t="s">
+        <v>2147</v>
+      </c>
+      <c r="B2131" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2131" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2131" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2131" s="3">
+        <v>6933</v>
+      </c>
+      <c r="F2131" s="3">
+        <v>8</v>
+      </c>
+      <c r="G2131" s="3">
+        <v>13292</v>
+      </c>
+      <c r="H2131" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2132" spans="1:8">
+      <c r="A2132" s="3" t="s">
+        <v>2148</v>
+      </c>
+      <c r="B2132" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2132" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2132" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2132" s="3">
+        <v>6916</v>
+      </c>
+      <c r="F2132" s="3">
+        <v>1</v>
+      </c>
+      <c r="G2132" s="3">
+        <v>11260</v>
+      </c>
+      <c r="H2132" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2133" spans="1:8">
+      <c r="A2133" s="3" t="s">
+        <v>2149</v>
+      </c>
+      <c r="B2133" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2133" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2133" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2133" s="3">
+        <v>6880</v>
+      </c>
+      <c r="F2133" s="3">
+        <v>6</v>
+      </c>
+      <c r="G2133" s="3">
+        <v>12463</v>
+      </c>
+      <c r="H2133" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2134" spans="1:8">
+      <c r="A2134" s="3" t="s">
+        <v>2150</v>
+      </c>
+      <c r="B2134" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2134" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2134" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2134" s="3">
+        <v>6869</v>
+      </c>
+      <c r="F2134" s="3">
+        <v>7</v>
+      </c>
+      <c r="G2134" s="3">
+        <v>14284</v>
+      </c>
+      <c r="H2134" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2135" spans="1:8">
+      <c r="A2135" s="3" t="s">
+        <v>2151</v>
+      </c>
+      <c r="B2135" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2135" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2135" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2135" s="3">
+        <v>6868</v>
+      </c>
+      <c r="F2135" s="3">
+        <v>1</v>
+      </c>
+      <c r="G2135" s="3">
+        <v>10576</v>
+      </c>
+      <c r="H2135" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2136" spans="1:8">
+      <c r="A2136" s="3" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B2136" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2136" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2136" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2136" s="3">
+        <v>6860</v>
+      </c>
+      <c r="F2136" s="3">
+        <v>8</v>
+      </c>
+      <c r="G2136" s="3">
+        <v>13729</v>
+      </c>
+      <c r="H2136" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2137" spans="1:8">
+      <c r="A2137" s="3" t="s">
+        <v>2153</v>
+      </c>
+      <c r="B2137" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2137" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2137" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2137" s="3">
+        <v>6857</v>
+      </c>
+      <c r="F2137" s="3">
+        <v>9</v>
+      </c>
+      <c r="G2137" s="3">
+        <v>14708</v>
+      </c>
+      <c r="H2137" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2138" spans="1:8">
+      <c r="A2138" s="3" t="s">
+        <v>2154</v>
+      </c>
+      <c r="B2138" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2138" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2138" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2138" s="3">
+        <v>6857</v>
+      </c>
+      <c r="F2138" s="3">
+        <v>3</v>
+      </c>
+      <c r="G2138" s="3">
+        <v>10726</v>
+      </c>
+      <c r="H2138" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2139" spans="1:8">
+      <c r="A2139" s="3" t="s">
+        <v>2155</v>
+      </c>
+      <c r="B2139" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2139" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2139" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2139" s="3">
+        <v>6838</v>
+      </c>
+      <c r="F2139" s="3">
+        <v>1</v>
+      </c>
+      <c r="G2139" s="3">
+        <v>8912</v>
+      </c>
+      <c r="H2139" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2140" spans="1:8">
+      <c r="A2140" s="3" t="s">
+        <v>2156</v>
+      </c>
+      <c r="B2140" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2140" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2140" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2140" s="3">
+        <v>6838</v>
+      </c>
+      <c r="F2140" s="3">
+        <v>2</v>
+      </c>
+      <c r="G2140" s="3">
+        <v>9222</v>
+      </c>
+      <c r="H2140" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2141" spans="1:8">
+      <c r="A2141" s="3" t="s">
+        <v>2157</v>
+      </c>
+      <c r="B2141" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2141" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2141" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2141" s="3">
+        <v>6835</v>
+      </c>
+      <c r="F2141" s="3">
+        <v>9</v>
+      </c>
+      <c r="G2141" s="3">
+        <v>15709</v>
+      </c>
+      <c r="H2141" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2142" spans="1:8">
+      <c r="A2142" s="3" t="s">
+        <v>2158</v>
+      </c>
+      <c r="B2142" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2142" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2142" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2142" s="3">
+        <v>6825</v>
+      </c>
+      <c r="F2142" s="3">
+        <v>7</v>
+      </c>
+      <c r="G2142" s="3">
+        <v>14468</v>
+      </c>
+      <c r="H2142" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2143" spans="1:8">
+      <c r="A2143" s="3" t="s">
+        <v>2159</v>
+      </c>
+      <c r="B2143" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2143" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2143" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2143" s="3">
+        <v>6812</v>
+      </c>
+      <c r="F2143" s="3">
+        <v>2</v>
+      </c>
+      <c r="G2143" s="3">
+        <v>10321</v>
+      </c>
+      <c r="H2143" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2144" spans="1:8">
+      <c r="A2144" s="3" t="s">
+        <v>2160</v>
+      </c>
+      <c r="B2144" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2144" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2144" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2144" s="3">
+        <v>6794</v>
+      </c>
+      <c r="F2144" s="3">
+        <v>9</v>
+      </c>
+      <c r="G2144" s="3">
+        <v>14291</v>
+      </c>
+      <c r="H2144" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2145" spans="1:8">
+      <c r="A2145" s="3" t="s">
+        <v>2161</v>
+      </c>
+      <c r="B2145" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2145" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2145" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2145" s="3">
+        <v>6784</v>
+      </c>
+      <c r="F2145" s="3">
+        <v>5</v>
+      </c>
+      <c r="G2145" s="3">
+        <v>13675</v>
+      </c>
+      <c r="H2145" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2146" spans="1:8">
+      <c r="A2146" s="3" t="s">
+        <v>2162</v>
+      </c>
+      <c r="B2146" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2146" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2146" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2146" s="3">
+        <v>6762</v>
+      </c>
+      <c r="F2146" s="3">
+        <v>2</v>
+      </c>
+      <c r="G2146" s="3">
+        <v>10632</v>
+      </c>
+      <c r="H2146" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2147" spans="1:8">
+      <c r="A2147" s="3" t="s">
+        <v>2163</v>
+      </c>
+      <c r="B2147" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2147" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2147" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2147" s="3">
+        <v>6737</v>
+      </c>
+      <c r="F2147" s="3">
+        <v>10</v>
+      </c>
+      <c r="G2147" s="3">
+        <v>14601</v>
+      </c>
+      <c r="H2147" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2148" spans="1:8">
+      <c r="A2148" s="3" t="s">
+        <v>2164</v>
+      </c>
+      <c r="B2148" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2148" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2148" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2148" s="3">
+        <v>6735</v>
+      </c>
+      <c r="F2148" s="3">
+        <v>5</v>
+      </c>
+      <c r="G2148" s="3">
+        <v>13401</v>
+      </c>
+      <c r="H2148" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2149" spans="1:8">
+      <c r="A2149" s="3" t="s">
+        <v>2165</v>
+      </c>
+      <c r="B2149" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2149" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2149" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2149" s="3">
+        <v>6731</v>
+      </c>
+      <c r="F2149" s="3">
+        <v>4</v>
+      </c>
+      <c r="G2149" s="3">
+        <v>11616</v>
+      </c>
+      <c r="H2149" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2150" spans="1:8">
+      <c r="A2150" s="3" t="s">
+        <v>2166</v>
+      </c>
+      <c r="B2150" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2150" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2150" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2150" s="3">
+        <v>6711</v>
+      </c>
+      <c r="F2150" s="3">
+        <v>5</v>
+      </c>
+      <c r="G2150" s="3">
+        <v>10866</v>
+      </c>
+      <c r="H2150" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2151" spans="1:8">
+      <c r="A2151" s="3" t="s">
+        <v>2167</v>
+      </c>
+      <c r="B2151" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2151" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2151" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2151" s="3">
+        <v>6707</v>
+      </c>
+      <c r="F2151" s="3">
+        <v>9</v>
+      </c>
+      <c r="G2151" s="3">
+        <v>14143</v>
+      </c>
+      <c r="H2151" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2152" spans="1:8">
+      <c r="A2152" s="3" t="s">
+        <v>2168</v>
+      </c>
+      <c r="B2152" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2152" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2152" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2152" s="3">
+        <v>6705</v>
+      </c>
+      <c r="F2152" s="3">
+        <v>8</v>
+      </c>
+      <c r="G2152" s="3">
+        <v>13344</v>
+      </c>
+      <c r="H2152" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2153" spans="1:8">
+      <c r="A2153" s="3" t="s">
+        <v>2169</v>
+      </c>
+      <c r="B2153" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2153" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2153" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2153" s="3">
+        <v>6700</v>
+      </c>
+      <c r="F2153" s="3">
+        <v>9</v>
+      </c>
+      <c r="G2153" s="3">
+        <v>15395</v>
+      </c>
+      <c r="H2153" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2154" spans="1:8">
+      <c r="A2154" s="3" t="s">
+        <v>2170</v>
+      </c>
+      <c r="B2154" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2154" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2154" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2154" s="3">
+        <v>6689</v>
+      </c>
+      <c r="F2154" s="3">
+        <v>5</v>
+      </c>
+      <c r="G2154" s="3">
+        <v>13282</v>
+      </c>
+      <c r="H2154" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2155" spans="1:8">
+      <c r="A2155" s="3" t="s">
+        <v>2171</v>
+      </c>
+      <c r="B2155" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2155" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2155" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2155" s="3">
+        <v>6668</v>
+      </c>
+      <c r="F2155" s="3">
+        <v>5</v>
+      </c>
+      <c r="G2155" s="3">
+        <v>12948</v>
+      </c>
+      <c r="H2155" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2156" spans="1:8">
+      <c r="A2156" s="3" t="s">
+        <v>2172</v>
+      </c>
+      <c r="B2156" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2156" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2156" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2156" s="3">
+        <v>6658</v>
+      </c>
+      <c r="F2156" s="3">
+        <v>6</v>
+      </c>
+      <c r="G2156" s="3">
+        <v>12206</v>
+      </c>
+      <c r="H2156" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2157" spans="1:8">
+      <c r="A2157" s="3" t="s">
+        <v>2173</v>
+      </c>
+      <c r="B2157" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2157" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2157" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2157" s="3">
+        <v>6652</v>
+      </c>
+      <c r="F2157" s="3">
+        <v>8</v>
+      </c>
+      <c r="G2157" s="3">
+        <v>12518</v>
+      </c>
+      <c r="H2157" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2158" spans="1:8">
+      <c r="A2158" s="3" t="s">
+        <v>2174</v>
+      </c>
+      <c r="B2158" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2158" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2158" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2158" s="3">
+        <v>6636</v>
+      </c>
+      <c r="F2158" s="3">
+        <v>4</v>
+      </c>
+      <c r="G2158" s="3">
+        <v>10143</v>
+      </c>
+      <c r="H2158" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2159" spans="1:8">
+      <c r="A2159" s="3" t="s">
+        <v>2175</v>
+      </c>
+      <c r="B2159" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2159" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2159" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2159" s="3">
+        <v>6624</v>
+      </c>
+      <c r="F2159" s="3">
+        <v>9</v>
+      </c>
+      <c r="G2159" s="3">
+        <v>14520</v>
+      </c>
+      <c r="H2159" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2160" spans="1:8">
+      <c r="A2160" s="3" t="s">
+        <v>2176</v>
+      </c>
+      <c r="B2160" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2160" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2160" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2160" s="3">
+        <v>6623</v>
+      </c>
+      <c r="F2160" s="3">
+        <v>9</v>
+      </c>
+      <c r="G2160" s="3">
+        <v>14533</v>
+      </c>
+      <c r="H2160" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2161" spans="1:8">
+      <c r="A2161" s="3" t="s">
+        <v>2177</v>
+      </c>
+      <c r="B2161" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2161" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2161" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2161" s="3">
+        <v>6605</v>
+      </c>
+      <c r="F2161" s="3">
+        <v>2</v>
+      </c>
+      <c r="G2161" s="3">
+        <v>9948</v>
+      </c>
+      <c r="H2161" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2162" spans="1:8">
+      <c r="A2162" s="3" t="s">
+        <v>2178</v>
+      </c>
+      <c r="B2162" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2162" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2162" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2162" s="3">
+        <v>6571</v>
+      </c>
+      <c r="F2162" s="3">
+        <v>10</v>
+      </c>
+      <c r="G2162" s="3">
+        <v>16416</v>
+      </c>
+      <c r="H2162" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2163" spans="1:8">
+      <c r="A2163" s="3" t="s">
+        <v>2179</v>
+      </c>
+      <c r="B2163" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2163" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2163" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2163" s="3">
+        <v>6558</v>
+      </c>
+      <c r="F2163" s="3">
+        <v>10</v>
+      </c>
+      <c r="G2163" s="3">
+        <v>16107</v>
+      </c>
+      <c r="H2163" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2164" spans="1:8">
+      <c r="A2164" s="3" t="s">
+        <v>2180</v>
+      </c>
+      <c r="B2164" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2164" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2164" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2164" s="3">
+        <v>6513</v>
+      </c>
+      <c r="F2164" s="3">
+        <v>4</v>
+      </c>
+      <c r="G2164" s="3">
+        <v>10670</v>
+      </c>
+      <c r="H2164" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2165" spans="1:8">
+      <c r="A2165" s="3" t="s">
+        <v>2181</v>
+      </c>
+      <c r="B2165" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2165" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2165" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2165" s="3">
+        <v>6510</v>
+      </c>
+      <c r="F2165" s="3">
+        <v>0</v>
+      </c>
+      <c r="G2165" s="3">
+        <v>7627</v>
+      </c>
+      <c r="H2165" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2166" spans="1:8">
+      <c r="A2166" s="3" t="s">
+        <v>2182</v>
+      </c>
+      <c r="B2166" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2166" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2166" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2166" s="3">
+        <v>6502</v>
+      </c>
+      <c r="F2166" s="3">
+        <v>10</v>
+      </c>
+      <c r="G2166" s="3">
+        <v>13817</v>
+      </c>
+      <c r="H2166" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2167" spans="1:8">
+      <c r="A2167" s="3" t="s">
+        <v>2183</v>
+      </c>
+      <c r="B2167" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2167" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2167" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2167" s="3">
+        <v>6494</v>
+      </c>
+      <c r="F2167" s="3">
+        <v>4</v>
+      </c>
+      <c r="G2167" s="3">
+        <v>12442</v>
+      </c>
+      <c r="H2167" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2168" spans="1:8">
+      <c r="A2168" s="3" t="s">
+        <v>2184</v>
+      </c>
+      <c r="B2168" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2168" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2168" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2168" s="3">
+        <v>6469</v>
+      </c>
+      <c r="F2168" s="3">
+        <v>8</v>
+      </c>
+      <c r="G2168" s="3">
+        <v>14904</v>
+      </c>
+      <c r="H2168" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2169" spans="1:8">
+      <c r="A2169" s="3" t="s">
+        <v>2185</v>
+      </c>
+      <c r="B2169" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2169" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2169" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2169" s="3">
+        <v>6443</v>
+      </c>
+      <c r="F2169" s="3">
+        <v>7</v>
+      </c>
+      <c r="G2169" s="3">
+        <v>12029</v>
+      </c>
+      <c r="H2169" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2170" spans="1:8">
+      <c r="A2170" s="3" t="s">
+        <v>2186</v>
+      </c>
+      <c r="B2170" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2170" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2170" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2170" s="3">
+        <v>6437</v>
+      </c>
+      <c r="F2170" s="3">
+        <v>2</v>
+      </c>
+      <c r="G2170" s="3">
+        <v>9998</v>
+      </c>
+      <c r="H2170" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2171" spans="1:8">
+      <c r="A2171" s="3" t="s">
+        <v>2187</v>
+      </c>
+      <c r="B2171" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2171" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2171" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2171" s="3">
+        <v>6429</v>
+      </c>
+      <c r="F2171" s="3">
+        <v>1</v>
+      </c>
+      <c r="G2171" s="3">
+        <v>10032</v>
+      </c>
+      <c r="H2171" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2172" spans="1:8">
+      <c r="A2172" s="3" t="s">
+        <v>2188</v>
+      </c>
+      <c r="B2172" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2172" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2172" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2172" s="3">
+        <v>6379</v>
+      </c>
+      <c r="F2172" s="3">
+        <v>2</v>
+      </c>
+      <c r="G2172" s="3">
+        <v>10823</v>
+      </c>
+      <c r="H2172" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2173" spans="1:8">
+      <c r="A2173" s="3" t="s">
+        <v>2189</v>
+      </c>
+      <c r="B2173" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2173" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2173" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2173" s="3">
+        <v>6370</v>
+      </c>
+      <c r="F2173" s="3">
+        <v>7</v>
+      </c>
+      <c r="G2173" s="3">
+        <v>12508</v>
+      </c>
+      <c r="H2173" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2174" spans="1:8">
+      <c r="A2174" s="3" t="s">
+        <v>2190</v>
+      </c>
+      <c r="B2174" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2174" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2174" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2174" s="3">
+        <v>6367</v>
+      </c>
+      <c r="F2174" s="3">
+        <v>9</v>
+      </c>
+      <c r="G2174" s="3">
+        <v>13780</v>
+      </c>
+      <c r="H2174" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2175" spans="1:8">
+      <c r="A2175" s="3" t="s">
+        <v>2191</v>
+      </c>
+      <c r="B2175" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2175" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2175" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2175" s="3">
+        <v>6327</v>
+      </c>
+      <c r="F2175" s="3">
+        <v>8</v>
+      </c>
+      <c r="G2175" s="3">
+        <v>14962</v>
+      </c>
+      <c r="H2175" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2176" spans="1:8">
+      <c r="A2176" s="3" t="s">
+        <v>2192</v>
+      </c>
+      <c r="B2176" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2176" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2176" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2176" s="3">
+        <v>6311</v>
+      </c>
+      <c r="F2176" s="3">
+        <v>0</v>
+      </c>
+      <c r="G2176" s="3">
+        <v>8014</v>
+      </c>
+      <c r="H2176" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2177" spans="1:8">
+      <c r="A2177" s="3" t="s">
+        <v>2193</v>
+      </c>
+      <c r="B2177" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2177" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2177" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2177" s="3">
+        <v>6300</v>
+      </c>
+      <c r="F2177" s="3">
+        <v>5</v>
+      </c>
+      <c r="G2177" s="3">
+        <v>10975</v>
+      </c>
+      <c r="H2177" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2178" spans="1:8">
+      <c r="A2178" s="3" t="s">
+        <v>2194</v>
+      </c>
+      <c r="B2178" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2178" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2178" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2178" s="3">
+        <v>6277</v>
+      </c>
+      <c r="F2178" s="3">
+        <v>7</v>
+      </c>
+      <c r="G2178" s="3">
+        <v>13158</v>
+      </c>
+      <c r="H2178" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2179" spans="1:8">
+      <c r="A2179" s="3" t="s">
+        <v>2195</v>
+      </c>
+      <c r="B2179" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2179" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2179" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2179" s="3">
+        <v>6276</v>
+      </c>
+      <c r="F2179" s="3">
+        <v>5</v>
+      </c>
+      <c r="G2179" s="3">
+        <v>10347</v>
+      </c>
+      <c r="H2179" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2180" spans="1:8">
+      <c r="A2180" s="3" t="s">
+        <v>2196</v>
+      </c>
+      <c r="B2180" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2180" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2180" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2180" s="3">
+        <v>6273</v>
+      </c>
+      <c r="F2180" s="3">
+        <v>5</v>
+      </c>
+      <c r="G2180" s="3">
+        <v>10871</v>
+      </c>
+      <c r="H2180" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2181" spans="1:8">
+      <c r="A2181" s="3" t="s">
+        <v>2197</v>
+      </c>
+      <c r="B2181" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2181" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2181" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2181" s="3">
+        <v>6266</v>
+      </c>
+      <c r="F2181" s="3">
+        <v>8</v>
+      </c>
+      <c r="G2181" s="3">
+        <v>14413</v>
+      </c>
+      <c r="H2181" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2182" spans="1:8">
+      <c r="A2182" s="3" t="s">
+        <v>2198</v>
+      </c>
+      <c r="B2182" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2182" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2182" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2182" s="3">
+        <v>6262</v>
+      </c>
+      <c r="F2182" s="3">
+        <v>3</v>
+      </c>
+      <c r="G2182" s="3">
+        <v>11108</v>
+      </c>
+      <c r="H2182" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2183" spans="1:8">
+      <c r="A2183" s="3" t="s">
+        <v>2199</v>
+      </c>
+      <c r="B2183" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2183" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2183" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2183" s="3">
+        <v>6198</v>
+      </c>
+      <c r="F2183" s="3">
+        <v>1</v>
+      </c>
+      <c r="G2183" s="3">
+        <v>9539</v>
+      </c>
+      <c r="H2183" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2184" spans="1:8">
+      <c r="A2184" s="3" t="s">
+        <v>2200</v>
+      </c>
+      <c r="B2184" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2184" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2184" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2184" s="3">
+        <v>6196</v>
+      </c>
+      <c r="F2184" s="3">
+        <v>2</v>
+      </c>
+      <c r="G2184" s="3">
+        <v>8917</v>
+      </c>
+      <c r="H2184" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2185" spans="1:8">
+      <c r="A2185" s="3" t="s">
+        <v>2201</v>
+      </c>
+      <c r="B2185" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2185" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2185" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2185" s="3">
+        <v>6194</v>
+      </c>
+      <c r="F2185" s="3">
+        <v>2</v>
+      </c>
+      <c r="G2185" s="3">
+        <v>9895</v>
+      </c>
+      <c r="H2185" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2186" spans="1:8">
+      <c r="A2186" s="3" t="s">
+        <v>2202</v>
+      </c>
+      <c r="B2186" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2186" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2186" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2186" s="3">
+        <v>6187</v>
+      </c>
+      <c r="F2186" s="3">
+        <v>8</v>
+      </c>
+      <c r="G2186" s="3">
+        <v>12445</v>
+      </c>
+      <c r="H2186" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2187" spans="1:8">
+      <c r="A2187" s="3" t="s">
+        <v>2203</v>
+      </c>
+      <c r="B2187" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2187" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2187" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2187" s="3">
+        <v>6166</v>
+      </c>
+      <c r="F2187" s="3">
+        <v>3</v>
+      </c>
+      <c r="G2187" s="3">
+        <v>9617</v>
+      </c>
+      <c r="H2187" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2188" spans="1:8">
+      <c r="A2188" s="3" t="s">
+        <v>2204</v>
+      </c>
+      <c r="B2188" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2188" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2188" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2188" s="3">
+        <v>6166</v>
+      </c>
+      <c r="F2188" s="3">
+        <v>8</v>
+      </c>
+      <c r="G2188" s="3">
+        <v>13107</v>
+      </c>
+      <c r="H2188" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2189" spans="1:8">
+      <c r="A2189" s="3" t="s">
+        <v>2205</v>
+      </c>
+      <c r="B2189" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2189" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2189" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2189" s="3">
+        <v>6163</v>
+      </c>
+      <c r="F2189" s="3">
+        <v>6</v>
+      </c>
+      <c r="G2189" s="3">
+        <v>11596</v>
+      </c>
+      <c r="H2189" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2190" spans="1:8">
+      <c r="A2190" s="3" t="s">
+        <v>2206</v>
+      </c>
+      <c r="B2190" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2190" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2190" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2190" s="3">
+        <v>6149</v>
+      </c>
+      <c r="F2190" s="3">
+        <v>7</v>
+      </c>
+      <c r="G2190" s="3">
+        <v>13612</v>
+      </c>
+      <c r="H2190" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2191" spans="1:8">
+      <c r="A2191" s="3" t="s">
+        <v>2207</v>
+      </c>
+      <c r="B2191" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2191" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2191" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2191" s="3">
+        <v>6134</v>
+      </c>
+      <c r="F2191" s="3">
+        <v>3</v>
+      </c>
+      <c r="G2191" s="3">
+        <v>9720</v>
+      </c>
+      <c r="H2191" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2192" spans="1:8">
+      <c r="A2192" s="3" t="s">
+        <v>2208</v>
+      </c>
+      <c r="B2192" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2192" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2192" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2192" s="3">
+        <v>6116</v>
+      </c>
+      <c r="F2192" s="3">
+        <v>0</v>
+      </c>
+      <c r="G2192" s="3">
+        <v>9985</v>
+      </c>
+      <c r="H2192" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2193" spans="1:8">
+      <c r="A2193" s="3" t="s">
+        <v>2209</v>
+      </c>
+      <c r="B2193" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2193" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2193" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2193" s="3">
+        <v>6113</v>
+      </c>
+      <c r="F2193" s="3">
+        <v>1</v>
+      </c>
+      <c r="G2193" s="3">
+        <v>8131</v>
+      </c>
+      <c r="H2193" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2194" spans="1:8">
+      <c r="A2194" s="3" t="s">
+        <v>2210</v>
+      </c>
+      <c r="B2194" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2194" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2194" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2194" s="3">
+        <v>6096</v>
+      </c>
+      <c r="F2194" s="3">
+        <v>7</v>
+      </c>
+      <c r="G2194" s="3">
+        <v>14005</v>
+      </c>
+      <c r="H2194" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2195" spans="1:8">
+      <c r="A2195" s="3" t="s">
+        <v>2211</v>
+      </c>
+      <c r="B2195" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2195" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2195" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2195" s="3">
+        <v>6076</v>
+      </c>
+      <c r="F2195" s="3">
+        <v>10</v>
+      </c>
+      <c r="G2195" s="3">
+        <v>15001</v>
+      </c>
+      <c r="H2195" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2196" spans="1:8">
+      <c r="A2196" s="3" t="s">
+        <v>2212</v>
+      </c>
+      <c r="B2196" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2196" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2196" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2196" s="3">
+        <v>6073</v>
+      </c>
+      <c r="F2196" s="3">
+        <v>1</v>
+      </c>
+      <c r="G2196" s="3">
+        <v>9317</v>
+      </c>
+      <c r="H2196" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2197" spans="1:8">
+      <c r="A2197" s="3" t="s">
+        <v>2213</v>
+      </c>
+      <c r="B2197" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2197" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2197" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2197" s="3">
+        <v>6064</v>
+      </c>
+      <c r="F2197" s="3">
+        <v>5</v>
+      </c>
+      <c r="G2197" s="3">
+        <v>12092</v>
+      </c>
+      <c r="H2197" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2198" spans="1:8">
+      <c r="A2198" s="3" t="s">
+        <v>2214</v>
+      </c>
+      <c r="B2198" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2198" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2198" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2198" s="3">
+        <v>6047</v>
+      </c>
+      <c r="F2198" s="3">
+        <v>0</v>
+      </c>
+      <c r="G2198" s="3">
+        <v>10040</v>
+      </c>
+      <c r="H2198" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2199" spans="1:8">
+      <c r="A2199" s="3" t="s">
+        <v>2215</v>
+      </c>
+      <c r="B2199" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2199" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2199" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2199" s="3">
+        <v>6040</v>
+      </c>
+      <c r="F2199" s="3">
+        <v>10</v>
+      </c>
+      <c r="G2199" s="3">
+        <v>14324</v>
+      </c>
+      <c r="H2199" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2200" spans="1:8">
+      <c r="A2200" s="3" t="s">
+        <v>2216</v>
+      </c>
+      <c r="B2200" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2200" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2200" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2200" s="3">
+        <v>6024</v>
+      </c>
+      <c r="F2200" s="3">
+        <v>4</v>
+      </c>
+      <c r="G2200" s="3">
+        <v>11486</v>
+      </c>
+      <c r="H2200" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2201" spans="1:8">
+      <c r="A2201" s="3" t="s">
+        <v>2217</v>
+      </c>
+      <c r="B2201" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2201" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2201" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2201" s="3">
+        <v>5998</v>
+      </c>
+      <c r="F2201" s="3">
+        <v>9</v>
+      </c>
+      <c r="G2201" s="3">
+        <v>13649</v>
+      </c>
+      <c r="H2201" s="3">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/NGO_Project_MNE_Dataset_2000.xlsx
+++ b/NGO_Project_MNE_Dataset_2000.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$2001</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8808" uniqueCount="2218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8008" uniqueCount="2018">
   <si>
     <t>Household_ID</t>
   </si>
@@ -6071,606 +6071,6 @@
   </si>
   <si>
     <t>HH-3000</t>
-  </si>
-  <si>
-    <t>HH-3001</t>
-  </si>
-  <si>
-    <t>HH-3002</t>
-  </si>
-  <si>
-    <t>HH-3003</t>
-  </si>
-  <si>
-    <t>HH-3004</t>
-  </si>
-  <si>
-    <t>HH-3005</t>
-  </si>
-  <si>
-    <t>HH-3006</t>
-  </si>
-  <si>
-    <t>HH-3007</t>
-  </si>
-  <si>
-    <t>HH-3008</t>
-  </si>
-  <si>
-    <t>HH-3009</t>
-  </si>
-  <si>
-    <t>HH-3010</t>
-  </si>
-  <si>
-    <t>HH-3011</t>
-  </si>
-  <si>
-    <t>HH-3012</t>
-  </si>
-  <si>
-    <t>HH-3013</t>
-  </si>
-  <si>
-    <t>HH-3014</t>
-  </si>
-  <si>
-    <t>HH-3015</t>
-  </si>
-  <si>
-    <t>HH-3016</t>
-  </si>
-  <si>
-    <t>HH-3017</t>
-  </si>
-  <si>
-    <t>HH-3018</t>
-  </si>
-  <si>
-    <t>HH-3019</t>
-  </si>
-  <si>
-    <t>HH-3020</t>
-  </si>
-  <si>
-    <t>HH-3021</t>
-  </si>
-  <si>
-    <t>HH-3022</t>
-  </si>
-  <si>
-    <t>HH-3023</t>
-  </si>
-  <si>
-    <t>HH-3024</t>
-  </si>
-  <si>
-    <t>HH-3025</t>
-  </si>
-  <si>
-    <t>HH-3026</t>
-  </si>
-  <si>
-    <t>HH-3027</t>
-  </si>
-  <si>
-    <t>HH-3028</t>
-  </si>
-  <si>
-    <t>HH-3029</t>
-  </si>
-  <si>
-    <t>HH-3030</t>
-  </si>
-  <si>
-    <t>HH-3031</t>
-  </si>
-  <si>
-    <t>HH-3032</t>
-  </si>
-  <si>
-    <t>HH-3033</t>
-  </si>
-  <si>
-    <t>HH-3034</t>
-  </si>
-  <si>
-    <t>HH-3035</t>
-  </si>
-  <si>
-    <t>HH-3036</t>
-  </si>
-  <si>
-    <t>HH-3037</t>
-  </si>
-  <si>
-    <t>HH-3038</t>
-  </si>
-  <si>
-    <t>HH-3039</t>
-  </si>
-  <si>
-    <t>HH-3040</t>
-  </si>
-  <si>
-    <t>HH-3041</t>
-  </si>
-  <si>
-    <t>HH-3042</t>
-  </si>
-  <si>
-    <t>HH-3043</t>
-  </si>
-  <si>
-    <t>HH-3044</t>
-  </si>
-  <si>
-    <t>HH-3045</t>
-  </si>
-  <si>
-    <t>HH-3046</t>
-  </si>
-  <si>
-    <t>HH-3047</t>
-  </si>
-  <si>
-    <t>HH-3048</t>
-  </si>
-  <si>
-    <t>HH-3049</t>
-  </si>
-  <si>
-    <t>HH-3050</t>
-  </si>
-  <si>
-    <t>HH-3051</t>
-  </si>
-  <si>
-    <t>HH-3052</t>
-  </si>
-  <si>
-    <t>HH-3053</t>
-  </si>
-  <si>
-    <t>HH-3054</t>
-  </si>
-  <si>
-    <t>HH-3055</t>
-  </si>
-  <si>
-    <t>HH-3056</t>
-  </si>
-  <si>
-    <t>HH-3057</t>
-  </si>
-  <si>
-    <t>HH-3058</t>
-  </si>
-  <si>
-    <t>HH-3059</t>
-  </si>
-  <si>
-    <t>HH-3060</t>
-  </si>
-  <si>
-    <t>HH-3061</t>
-  </si>
-  <si>
-    <t>HH-3062</t>
-  </si>
-  <si>
-    <t>HH-3063</t>
-  </si>
-  <si>
-    <t>HH-3064</t>
-  </si>
-  <si>
-    <t>HH-3065</t>
-  </si>
-  <si>
-    <t>HH-3066</t>
-  </si>
-  <si>
-    <t>HH-3067</t>
-  </si>
-  <si>
-    <t>HH-3068</t>
-  </si>
-  <si>
-    <t>HH-3069</t>
-  </si>
-  <si>
-    <t>HH-3070</t>
-  </si>
-  <si>
-    <t>HH-3071</t>
-  </si>
-  <si>
-    <t>HH-3072</t>
-  </si>
-  <si>
-    <t>HH-3073</t>
-  </si>
-  <si>
-    <t>HH-3074</t>
-  </si>
-  <si>
-    <t>HH-3075</t>
-  </si>
-  <si>
-    <t>HH-3076</t>
-  </si>
-  <si>
-    <t>HH-3077</t>
-  </si>
-  <si>
-    <t>HH-3078</t>
-  </si>
-  <si>
-    <t>HH-3079</t>
-  </si>
-  <si>
-    <t>HH-3080</t>
-  </si>
-  <si>
-    <t>HH-3081</t>
-  </si>
-  <si>
-    <t>HH-3082</t>
-  </si>
-  <si>
-    <t>HH-3083</t>
-  </si>
-  <si>
-    <t>HH-3084</t>
-  </si>
-  <si>
-    <t>HH-3085</t>
-  </si>
-  <si>
-    <t>HH-3086</t>
-  </si>
-  <si>
-    <t>HH-3087</t>
-  </si>
-  <si>
-    <t>HH-3088</t>
-  </si>
-  <si>
-    <t>HH-3089</t>
-  </si>
-  <si>
-    <t>HH-3090</t>
-  </si>
-  <si>
-    <t>HH-3091</t>
-  </si>
-  <si>
-    <t>HH-3092</t>
-  </si>
-  <si>
-    <t>HH-3093</t>
-  </si>
-  <si>
-    <t>HH-3094</t>
-  </si>
-  <si>
-    <t>HH-3095</t>
-  </si>
-  <si>
-    <t>HH-3096</t>
-  </si>
-  <si>
-    <t>HH-3097</t>
-  </si>
-  <si>
-    <t>HH-3098</t>
-  </si>
-  <si>
-    <t>HH-3099</t>
-  </si>
-  <si>
-    <t>HH-3100</t>
-  </si>
-  <si>
-    <t>HH-3101</t>
-  </si>
-  <si>
-    <t>HH-3102</t>
-  </si>
-  <si>
-    <t>HH-3103</t>
-  </si>
-  <si>
-    <t>HH-3104</t>
-  </si>
-  <si>
-    <t>HH-3105</t>
-  </si>
-  <si>
-    <t>HH-3106</t>
-  </si>
-  <si>
-    <t>HH-3107</t>
-  </si>
-  <si>
-    <t>HH-3108</t>
-  </si>
-  <si>
-    <t>HH-3109</t>
-  </si>
-  <si>
-    <t>HH-3110</t>
-  </si>
-  <si>
-    <t>HH-3111</t>
-  </si>
-  <si>
-    <t>HH-3112</t>
-  </si>
-  <si>
-    <t>HH-3113</t>
-  </si>
-  <si>
-    <t>HH-3114</t>
-  </si>
-  <si>
-    <t>HH-3115</t>
-  </si>
-  <si>
-    <t>HH-3116</t>
-  </si>
-  <si>
-    <t>HH-3117</t>
-  </si>
-  <si>
-    <t>HH-3118</t>
-  </si>
-  <si>
-    <t>HH-3119</t>
-  </si>
-  <si>
-    <t>HH-3120</t>
-  </si>
-  <si>
-    <t>HH-3121</t>
-  </si>
-  <si>
-    <t>HH-3122</t>
-  </si>
-  <si>
-    <t>HH-3123</t>
-  </si>
-  <si>
-    <t>HH-3124</t>
-  </si>
-  <si>
-    <t>HH-3125</t>
-  </si>
-  <si>
-    <t>HH-3126</t>
-  </si>
-  <si>
-    <t>HH-3127</t>
-  </si>
-  <si>
-    <t>HH-3128</t>
-  </si>
-  <si>
-    <t>HH-3129</t>
-  </si>
-  <si>
-    <t>HH-3130</t>
-  </si>
-  <si>
-    <t>HH-3131</t>
-  </si>
-  <si>
-    <t>HH-3132</t>
-  </si>
-  <si>
-    <t>HH-3133</t>
-  </si>
-  <si>
-    <t>HH-3134</t>
-  </si>
-  <si>
-    <t>HH-3135</t>
-  </si>
-  <si>
-    <t>HH-3136</t>
-  </si>
-  <si>
-    <t>HH-3137</t>
-  </si>
-  <si>
-    <t>HH-3138</t>
-  </si>
-  <si>
-    <t>HH-3139</t>
-  </si>
-  <si>
-    <t>HH-3140</t>
-  </si>
-  <si>
-    <t>HH-3141</t>
-  </si>
-  <si>
-    <t>HH-3142</t>
-  </si>
-  <si>
-    <t>HH-3143</t>
-  </si>
-  <si>
-    <t>HH-3144</t>
-  </si>
-  <si>
-    <t>HH-3145</t>
-  </si>
-  <si>
-    <t>HH-3146</t>
-  </si>
-  <si>
-    <t>HH-3147</t>
-  </si>
-  <si>
-    <t>HH-3148</t>
-  </si>
-  <si>
-    <t>HH-3149</t>
-  </si>
-  <si>
-    <t>HH-3150</t>
-  </si>
-  <si>
-    <t>HH-3151</t>
-  </si>
-  <si>
-    <t>HH-3152</t>
-  </si>
-  <si>
-    <t>HH-3153</t>
-  </si>
-  <si>
-    <t>HH-3154</t>
-  </si>
-  <si>
-    <t>HH-3155</t>
-  </si>
-  <si>
-    <t>HH-3156</t>
-  </si>
-  <si>
-    <t>HH-3157</t>
-  </si>
-  <si>
-    <t>HH-3158</t>
-  </si>
-  <si>
-    <t>HH-3159</t>
-  </si>
-  <si>
-    <t>HH-3160</t>
-  </si>
-  <si>
-    <t>HH-3161</t>
-  </si>
-  <si>
-    <t>HH-3162</t>
-  </si>
-  <si>
-    <t>HH-3163</t>
-  </si>
-  <si>
-    <t>HH-3164</t>
-  </si>
-  <si>
-    <t>HH-3165</t>
-  </si>
-  <si>
-    <t>HH-3166</t>
-  </si>
-  <si>
-    <t>HH-3167</t>
-  </si>
-  <si>
-    <t>HH-3168</t>
-  </si>
-  <si>
-    <t>HH-3169</t>
-  </si>
-  <si>
-    <t>HH-3170</t>
-  </si>
-  <si>
-    <t>HH-3171</t>
-  </si>
-  <si>
-    <t>HH-3172</t>
-  </si>
-  <si>
-    <t>HH-3173</t>
-  </si>
-  <si>
-    <t>HH-3174</t>
-  </si>
-  <si>
-    <t>HH-3175</t>
-  </si>
-  <si>
-    <t>HH-3176</t>
-  </si>
-  <si>
-    <t>HH-3177</t>
-  </si>
-  <si>
-    <t>HH-3178</t>
-  </si>
-  <si>
-    <t>HH-3179</t>
-  </si>
-  <si>
-    <t>HH-3180</t>
-  </si>
-  <si>
-    <t>HH-3181</t>
-  </si>
-  <si>
-    <t>HH-3182</t>
-  </si>
-  <si>
-    <t>HH-3183</t>
-  </si>
-  <si>
-    <t>HH-3184</t>
-  </si>
-  <si>
-    <t>HH-3185</t>
-  </si>
-  <si>
-    <t>HH-3186</t>
-  </si>
-  <si>
-    <t>HH-3187</t>
-  </si>
-  <si>
-    <t>HH-3188</t>
-  </si>
-  <si>
-    <t>HH-3189</t>
-  </si>
-  <si>
-    <t>HH-3190</t>
-  </si>
-  <si>
-    <t>HH-3191</t>
-  </si>
-  <si>
-    <t>HH-3192</t>
-  </si>
-  <si>
-    <t>HH-3193</t>
-  </si>
-  <si>
-    <t>HH-3194</t>
-  </si>
-  <si>
-    <t>HH-3195</t>
-  </si>
-  <si>
-    <t>HH-3196</t>
-  </si>
-  <si>
-    <t>HH-3197</t>
-  </si>
-  <si>
-    <t>HH-3198</t>
-  </si>
-  <si>
-    <t>HH-3199</t>
-  </si>
-  <si>
-    <t>HH-3200</t>
   </si>
 </sst>
 </file>
@@ -6714,12 +6114,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -7015,7 +6414,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H2201"/>
+  <dimension ref="A1:H2001"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.85546875" style="2" customWidth="1"/>
@@ -59055,5206 +58454,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2002" spans="1:8">
-      <c r="A2002" s="2" t="s">
-        <v>2018</v>
-      </c>
-      <c r="B2002" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2002" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2002" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2002" s="2">
-        <v>5572</v>
-      </c>
-      <c r="F2002" s="2">
-        <v>7</v>
-      </c>
-      <c r="G2002" s="2">
-        <v>13014</v>
-      </c>
-      <c r="H2002" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2003" spans="1:8">
-      <c r="A2003" s="3" t="s">
-        <v>2019</v>
-      </c>
-      <c r="B2003" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2003" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2003" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2003" s="3">
-        <v>8492</v>
-      </c>
-      <c r="F2003" s="3">
-        <v>7</v>
-      </c>
-      <c r="G2003" s="3">
-        <v>15321</v>
-      </c>
-      <c r="H2003" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2004" spans="1:8">
-      <c r="A2004" s="3" t="s">
-        <v>2020</v>
-      </c>
-      <c r="B2004" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2004" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2004" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2004" s="3">
-        <v>8490</v>
-      </c>
-      <c r="F2004" s="3">
-        <v>10</v>
-      </c>
-      <c r="G2004" s="3">
-        <v>18201</v>
-      </c>
-      <c r="H2004" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2005" spans="1:8">
-      <c r="A2005" s="3" t="s">
-        <v>2021</v>
-      </c>
-      <c r="B2005" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2005" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2005" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2005" s="3">
-        <v>8483</v>
-      </c>
-      <c r="F2005" s="3">
-        <v>0</v>
-      </c>
-      <c r="G2005" s="3">
-        <v>12194</v>
-      </c>
-      <c r="H2005" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2006" spans="1:8">
-      <c r="A2006" s="3" t="s">
-        <v>2022</v>
-      </c>
-      <c r="B2006" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2006" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2006" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2006" s="3">
-        <v>8458</v>
-      </c>
-      <c r="F2006" s="3">
-        <v>0</v>
-      </c>
-      <c r="G2006" s="3">
-        <v>10485</v>
-      </c>
-      <c r="H2006" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2007" spans="1:8">
-      <c r="A2007" s="3" t="s">
-        <v>2023</v>
-      </c>
-      <c r="B2007" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2007" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2007" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2007" s="3">
-        <v>8446</v>
-      </c>
-      <c r="F2007" s="3">
-        <v>9</v>
-      </c>
-      <c r="G2007" s="3">
-        <v>16694</v>
-      </c>
-      <c r="H2007" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2008" spans="1:8">
-      <c r="A2008" s="3" t="s">
-        <v>2024</v>
-      </c>
-      <c r="B2008" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2008" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2008" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2008" s="3">
-        <v>8435</v>
-      </c>
-      <c r="F2008" s="3">
-        <v>0</v>
-      </c>
-      <c r="G2008" s="3">
-        <v>10405</v>
-      </c>
-      <c r="H2008" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2009" spans="1:8">
-      <c r="A2009" s="3" t="s">
-        <v>2025</v>
-      </c>
-      <c r="B2009" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2009" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2009" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2009" s="3">
-        <v>8435</v>
-      </c>
-      <c r="F2009" s="3">
-        <v>6</v>
-      </c>
-      <c r="G2009" s="3">
-        <v>13565</v>
-      </c>
-      <c r="H2009" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2010" spans="1:8">
-      <c r="A2010" s="3" t="s">
-        <v>2026</v>
-      </c>
-      <c r="B2010" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2010" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2010" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2010" s="3">
-        <v>8433</v>
-      </c>
-      <c r="F2010" s="3">
-        <v>4</v>
-      </c>
-      <c r="G2010" s="3">
-        <v>13758</v>
-      </c>
-      <c r="H2010" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2011" spans="1:8">
-      <c r="A2011" s="3" t="s">
-        <v>2027</v>
-      </c>
-      <c r="B2011" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2011" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2011" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2011" s="3">
-        <v>8421</v>
-      </c>
-      <c r="F2011" s="3">
-        <v>9</v>
-      </c>
-      <c r="G2011" s="3">
-        <v>15482</v>
-      </c>
-      <c r="H2011" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2012" spans="1:8">
-      <c r="A2012" s="3" t="s">
-        <v>2028</v>
-      </c>
-      <c r="B2012" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2012" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2012" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2012" s="3">
-        <v>8406</v>
-      </c>
-      <c r="F2012" s="3">
-        <v>6</v>
-      </c>
-      <c r="G2012" s="3">
-        <v>14678</v>
-      </c>
-      <c r="H2012" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2013" spans="1:8">
-      <c r="A2013" s="3" t="s">
-        <v>2029</v>
-      </c>
-      <c r="B2013" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2013" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2013" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2013" s="3">
-        <v>8402</v>
-      </c>
-      <c r="F2013" s="3">
-        <v>5</v>
-      </c>
-      <c r="G2013" s="3">
-        <v>12681</v>
-      </c>
-      <c r="H2013" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2014" spans="1:8">
-      <c r="A2014" s="3" t="s">
-        <v>2030</v>
-      </c>
-      <c r="B2014" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2014" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2014" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2014" s="3">
-        <v>8402</v>
-      </c>
-      <c r="F2014" s="3">
-        <v>3</v>
-      </c>
-      <c r="G2014" s="3">
-        <v>12447</v>
-      </c>
-      <c r="H2014" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2015" spans="1:8">
-      <c r="A2015" s="3" t="s">
-        <v>2031</v>
-      </c>
-      <c r="B2015" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2015" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2015" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2015" s="3">
-        <v>8381</v>
-      </c>
-      <c r="F2015" s="3">
-        <v>9</v>
-      </c>
-      <c r="G2015" s="3">
-        <v>17045</v>
-      </c>
-      <c r="H2015" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2016" spans="1:8">
-      <c r="A2016" s="3" t="s">
-        <v>2032</v>
-      </c>
-      <c r="B2016" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2016" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2016" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2016" s="3">
-        <v>8372</v>
-      </c>
-      <c r="F2016" s="3">
-        <v>3</v>
-      </c>
-      <c r="G2016" s="3">
-        <v>11685</v>
-      </c>
-      <c r="H2016" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2017" spans="1:8">
-      <c r="A2017" s="3" t="s">
-        <v>2033</v>
-      </c>
-      <c r="B2017" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2017" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2017" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2017" s="3">
-        <v>8371</v>
-      </c>
-      <c r="F2017" s="3">
-        <v>7</v>
-      </c>
-      <c r="G2017" s="3">
-        <v>16523</v>
-      </c>
-      <c r="H2017" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2018" spans="1:8">
-      <c r="A2018" s="3" t="s">
-        <v>2034</v>
-      </c>
-      <c r="B2018" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2018" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2018" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2018" s="3">
-        <v>8366</v>
-      </c>
-      <c r="F2018" s="3">
-        <v>0</v>
-      </c>
-      <c r="G2018" s="3">
-        <v>10666</v>
-      </c>
-      <c r="H2018" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2019" spans="1:8">
-      <c r="A2019" s="3" t="s">
-        <v>2035</v>
-      </c>
-      <c r="B2019" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2019" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2019" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2019" s="3">
-        <v>8362</v>
-      </c>
-      <c r="F2019" s="3">
-        <v>10</v>
-      </c>
-      <c r="G2019" s="3">
-        <v>17901</v>
-      </c>
-      <c r="H2019" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2020" spans="1:8">
-      <c r="A2020" s="3" t="s">
-        <v>2036</v>
-      </c>
-      <c r="B2020" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2020" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2020" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2020" s="3">
-        <v>8354</v>
-      </c>
-      <c r="F2020" s="3">
-        <v>2</v>
-      </c>
-      <c r="G2020" s="3">
-        <v>13221</v>
-      </c>
-      <c r="H2020" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2021" spans="1:8">
-      <c r="A2021" s="3" t="s">
-        <v>2037</v>
-      </c>
-      <c r="B2021" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2021" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2021" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2021" s="3">
-        <v>8345</v>
-      </c>
-      <c r="F2021" s="3">
-        <v>4</v>
-      </c>
-      <c r="G2021" s="3">
-        <v>13774</v>
-      </c>
-      <c r="H2021" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2022" spans="1:8">
-      <c r="A2022" s="3" t="s">
-        <v>2038</v>
-      </c>
-      <c r="B2022" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2022" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2022" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2022" s="3">
-        <v>8320</v>
-      </c>
-      <c r="F2022" s="3">
-        <v>4</v>
-      </c>
-      <c r="G2022" s="3">
-        <v>12589</v>
-      </c>
-      <c r="H2022" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2023" spans="1:8">
-      <c r="A2023" s="3" t="s">
-        <v>2039</v>
-      </c>
-      <c r="B2023" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2023" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2023" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2023" s="3">
-        <v>8309</v>
-      </c>
-      <c r="F2023" s="3">
-        <v>10</v>
-      </c>
-      <c r="G2023" s="3">
-        <v>16361</v>
-      </c>
-      <c r="H2023" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2024" spans="1:8">
-      <c r="A2024" s="3" t="s">
-        <v>2040</v>
-      </c>
-      <c r="B2024" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2024" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2024" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2024" s="3">
-        <v>8302</v>
-      </c>
-      <c r="F2024" s="3">
-        <v>8</v>
-      </c>
-      <c r="G2024" s="3">
-        <v>16689</v>
-      </c>
-      <c r="H2024" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2025" spans="1:8">
-      <c r="A2025" s="3" t="s">
-        <v>2041</v>
-      </c>
-      <c r="B2025" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2025" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2025" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2025" s="3">
-        <v>8293</v>
-      </c>
-      <c r="F2025" s="3">
-        <v>5</v>
-      </c>
-      <c r="G2025" s="3">
-        <v>12740</v>
-      </c>
-      <c r="H2025" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2026" spans="1:8">
-      <c r="A2026" s="3" t="s">
-        <v>2042</v>
-      </c>
-      <c r="B2026" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2026" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2026" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2026" s="3">
-        <v>8293</v>
-      </c>
-      <c r="F2026" s="3">
-        <v>9</v>
-      </c>
-      <c r="G2026" s="3">
-        <v>15097</v>
-      </c>
-      <c r="H2026" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2027" spans="1:8">
-      <c r="A2027" s="3" t="s">
-        <v>2043</v>
-      </c>
-      <c r="B2027" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2027" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2027" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2027" s="3">
-        <v>8287</v>
-      </c>
-      <c r="F2027" s="3">
-        <v>1</v>
-      </c>
-      <c r="G2027" s="3">
-        <v>10634</v>
-      </c>
-      <c r="H2027" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2028" spans="1:8">
-      <c r="A2028" s="3" t="s">
-        <v>2044</v>
-      </c>
-      <c r="B2028" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2028" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2028" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2028" s="3">
-        <v>8272</v>
-      </c>
-      <c r="F2028" s="3">
-        <v>6</v>
-      </c>
-      <c r="G2028" s="3">
-        <v>13735</v>
-      </c>
-      <c r="H2028" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2029" spans="1:8">
-      <c r="A2029" s="3" t="s">
-        <v>2045</v>
-      </c>
-      <c r="B2029" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2029" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2029" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2029" s="3">
-        <v>8264</v>
-      </c>
-      <c r="F2029" s="3">
-        <v>6</v>
-      </c>
-      <c r="G2029" s="3">
-        <v>14845</v>
-      </c>
-      <c r="H2029" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2030" spans="1:8">
-      <c r="A2030" s="3" t="s">
-        <v>2046</v>
-      </c>
-      <c r="B2030" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2030" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2030" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2030" s="3">
-        <v>8235</v>
-      </c>
-      <c r="F2030" s="3">
-        <v>6</v>
-      </c>
-      <c r="G2030" s="3">
-        <v>14798</v>
-      </c>
-      <c r="H2030" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2031" spans="1:8">
-      <c r="A2031" s="3" t="s">
-        <v>2047</v>
-      </c>
-      <c r="B2031" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2031" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2031" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2031" s="3">
-        <v>8234</v>
-      </c>
-      <c r="F2031" s="3">
-        <v>1</v>
-      </c>
-      <c r="G2031" s="3">
-        <v>12603</v>
-      </c>
-      <c r="H2031" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2032" spans="1:8">
-      <c r="A2032" s="3" t="s">
-        <v>2048</v>
-      </c>
-      <c r="B2032" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2032" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2032" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2032" s="3">
-        <v>8232</v>
-      </c>
-      <c r="F2032" s="3">
-        <v>8</v>
-      </c>
-      <c r="G2032" s="3">
-        <v>15141</v>
-      </c>
-      <c r="H2032" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2033" spans="1:8">
-      <c r="A2033" s="3" t="s">
-        <v>2049</v>
-      </c>
-      <c r="B2033" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2033" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2033" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2033" s="3">
-        <v>8222</v>
-      </c>
-      <c r="F2033" s="3">
-        <v>3</v>
-      </c>
-      <c r="G2033" s="3">
-        <v>13853</v>
-      </c>
-      <c r="H2033" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2034" spans="1:8">
-      <c r="A2034" s="3" t="s">
-        <v>2050</v>
-      </c>
-      <c r="B2034" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2034" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2034" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2034" s="3">
-        <v>8198</v>
-      </c>
-      <c r="F2034" s="3">
-        <v>4</v>
-      </c>
-      <c r="G2034" s="3">
-        <v>13535</v>
-      </c>
-      <c r="H2034" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2035" spans="1:8">
-      <c r="A2035" s="3" t="s">
-        <v>2051</v>
-      </c>
-      <c r="B2035" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2035" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2035" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2035" s="3">
-        <v>8195</v>
-      </c>
-      <c r="F2035" s="3">
-        <v>6</v>
-      </c>
-      <c r="G2035" s="3">
-        <v>14408</v>
-      </c>
-      <c r="H2035" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2036" spans="1:8">
-      <c r="A2036" s="3" t="s">
-        <v>2052</v>
-      </c>
-      <c r="B2036" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2036" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2036" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2036" s="3">
-        <v>8175</v>
-      </c>
-      <c r="F2036" s="3">
-        <v>3</v>
-      </c>
-      <c r="G2036" s="3">
-        <v>10986</v>
-      </c>
-      <c r="H2036" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2037" spans="1:8">
-      <c r="A2037" s="3" t="s">
-        <v>2053</v>
-      </c>
-      <c r="B2037" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2037" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2037" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2037" s="3">
-        <v>8166</v>
-      </c>
-      <c r="F2037" s="3">
-        <v>9</v>
-      </c>
-      <c r="G2037" s="3">
-        <v>14657</v>
-      </c>
-      <c r="H2037" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2038" spans="1:8">
-      <c r="A2038" s="3" t="s">
-        <v>2054</v>
-      </c>
-      <c r="B2038" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2038" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2038" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2038" s="3">
-        <v>8163</v>
-      </c>
-      <c r="F2038" s="3">
-        <v>5</v>
-      </c>
-      <c r="G2038" s="3">
-        <v>13238</v>
-      </c>
-      <c r="H2038" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2039" spans="1:8">
-      <c r="A2039" s="3" t="s">
-        <v>2055</v>
-      </c>
-      <c r="B2039" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2039" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2039" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2039" s="3">
-        <v>8157</v>
-      </c>
-      <c r="F2039" s="3">
-        <v>0</v>
-      </c>
-      <c r="G2039" s="3">
-        <v>11274</v>
-      </c>
-      <c r="H2039" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2040" spans="1:8">
-      <c r="A2040" s="3" t="s">
-        <v>2056</v>
-      </c>
-      <c r="B2040" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2040" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2040" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2040" s="3">
-        <v>8137</v>
-      </c>
-      <c r="F2040" s="3">
-        <v>3</v>
-      </c>
-      <c r="G2040" s="3">
-        <v>12614</v>
-      </c>
-      <c r="H2040" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2041" spans="1:8">
-      <c r="A2041" s="3" t="s">
-        <v>2057</v>
-      </c>
-      <c r="B2041" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2041" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2041" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2041" s="3">
-        <v>8113</v>
-      </c>
-      <c r="F2041" s="3">
-        <v>6</v>
-      </c>
-      <c r="G2041" s="3">
-        <v>13256</v>
-      </c>
-      <c r="H2041" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2042" spans="1:8">
-      <c r="A2042" s="3" t="s">
-        <v>2058</v>
-      </c>
-      <c r="B2042" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2042" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2042" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2042" s="3">
-        <v>8076</v>
-      </c>
-      <c r="F2042" s="3">
-        <v>4</v>
-      </c>
-      <c r="G2042" s="3">
-        <v>11964</v>
-      </c>
-      <c r="H2042" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2043" spans="1:8">
-      <c r="A2043" s="3" t="s">
-        <v>2059</v>
-      </c>
-      <c r="B2043" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2043" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2043" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2043" s="3">
-        <v>8076</v>
-      </c>
-      <c r="F2043" s="3">
-        <v>6</v>
-      </c>
-      <c r="G2043" s="3">
-        <v>14750</v>
-      </c>
-      <c r="H2043" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2044" spans="1:8">
-      <c r="A2044" s="3" t="s">
-        <v>2060</v>
-      </c>
-      <c r="B2044" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2044" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2044" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2044" s="3">
-        <v>8071</v>
-      </c>
-      <c r="F2044" s="3">
-        <v>8</v>
-      </c>
-      <c r="G2044" s="3">
-        <v>16091</v>
-      </c>
-      <c r="H2044" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2045" spans="1:8">
-      <c r="A2045" s="3" t="s">
-        <v>2061</v>
-      </c>
-      <c r="B2045" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2045" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2045" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2045" s="3">
-        <v>8037</v>
-      </c>
-      <c r="F2045" s="3">
-        <v>5</v>
-      </c>
-      <c r="G2045" s="3">
-        <v>13601</v>
-      </c>
-      <c r="H2045" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2046" spans="1:8">
-      <c r="A2046" s="3" t="s">
-        <v>2062</v>
-      </c>
-      <c r="B2046" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2046" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2046" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2046" s="3">
-        <v>8032</v>
-      </c>
-      <c r="F2046" s="3">
-        <v>3</v>
-      </c>
-      <c r="G2046" s="3">
-        <v>11291</v>
-      </c>
-      <c r="H2046" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2047" spans="1:8">
-      <c r="A2047" s="3" t="s">
-        <v>2063</v>
-      </c>
-      <c r="B2047" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2047" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2047" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2047" s="3">
-        <v>8020</v>
-      </c>
-      <c r="F2047" s="3">
-        <v>3</v>
-      </c>
-      <c r="G2047" s="3">
-        <v>12899</v>
-      </c>
-      <c r="H2047" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2048" spans="1:8">
-      <c r="A2048" s="3" t="s">
-        <v>2064</v>
-      </c>
-      <c r="B2048" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2048" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2048" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2048" s="3">
-        <v>8009</v>
-      </c>
-      <c r="F2048" s="3">
-        <v>0</v>
-      </c>
-      <c r="G2048" s="3">
-        <v>9818</v>
-      </c>
-      <c r="H2048" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2049" spans="1:8">
-      <c r="A2049" s="3" t="s">
-        <v>2065</v>
-      </c>
-      <c r="B2049" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2049" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2049" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2049" s="3">
-        <v>7999</v>
-      </c>
-      <c r="F2049" s="3">
-        <v>1</v>
-      </c>
-      <c r="G2049" s="3">
-        <v>11219</v>
-      </c>
-      <c r="H2049" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2050" spans="1:8">
-      <c r="A2050" s="3" t="s">
-        <v>2066</v>
-      </c>
-      <c r="B2050" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2050" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2050" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2050" s="3">
-        <v>7985</v>
-      </c>
-      <c r="F2050" s="3">
-        <v>0</v>
-      </c>
-      <c r="G2050" s="3">
-        <v>10174</v>
-      </c>
-      <c r="H2050" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2051" spans="1:8">
-      <c r="A2051" s="3" t="s">
-        <v>2067</v>
-      </c>
-      <c r="B2051" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2051" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2051" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2051" s="3">
-        <v>7973</v>
-      </c>
-      <c r="F2051" s="3">
-        <v>3</v>
-      </c>
-      <c r="G2051" s="3">
-        <v>13398</v>
-      </c>
-      <c r="H2051" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2052" spans="1:8">
-      <c r="A2052" s="3" t="s">
-        <v>2068</v>
-      </c>
-      <c r="B2052" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2052" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2052" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2052" s="3">
-        <v>7969</v>
-      </c>
-      <c r="F2052" s="3">
-        <v>10</v>
-      </c>
-      <c r="G2052" s="3">
-        <v>16532</v>
-      </c>
-      <c r="H2052" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2053" spans="1:8">
-      <c r="A2053" s="3" t="s">
-        <v>2069</v>
-      </c>
-      <c r="B2053" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2053" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2053" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2053" s="3">
-        <v>7969</v>
-      </c>
-      <c r="F2053" s="3">
-        <v>10</v>
-      </c>
-      <c r="G2053" s="3">
-        <v>16713</v>
-      </c>
-      <c r="H2053" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2054" spans="1:8">
-      <c r="A2054" s="3" t="s">
-        <v>2070</v>
-      </c>
-      <c r="B2054" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2054" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2054" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2054" s="3">
-        <v>7961</v>
-      </c>
-      <c r="F2054" s="3">
-        <v>9</v>
-      </c>
-      <c r="G2054" s="3">
-        <v>16543</v>
-      </c>
-      <c r="H2054" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2055" spans="1:8">
-      <c r="A2055" s="3" t="s">
-        <v>2071</v>
-      </c>
-      <c r="B2055" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2055" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2055" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2055" s="3">
-        <v>7951</v>
-      </c>
-      <c r="F2055" s="3">
-        <v>8</v>
-      </c>
-      <c r="G2055" s="3">
-        <v>15397</v>
-      </c>
-      <c r="H2055" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2056" spans="1:8">
-      <c r="A2056" s="3" t="s">
-        <v>2072</v>
-      </c>
-      <c r="B2056" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2056" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2056" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2056" s="3">
-        <v>7945</v>
-      </c>
-      <c r="F2056" s="3">
-        <v>5</v>
-      </c>
-      <c r="G2056" s="3">
-        <v>13552</v>
-      </c>
-      <c r="H2056" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2057" spans="1:8">
-      <c r="A2057" s="3" t="s">
-        <v>2073</v>
-      </c>
-      <c r="B2057" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2057" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2057" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2057" s="3">
-        <v>7932</v>
-      </c>
-      <c r="F2057" s="3">
-        <v>6</v>
-      </c>
-      <c r="G2057" s="3">
-        <v>14477</v>
-      </c>
-      <c r="H2057" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2058" spans="1:8">
-      <c r="A2058" s="3" t="s">
-        <v>2074</v>
-      </c>
-      <c r="B2058" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2058" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2058" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2058" s="3">
-        <v>7906</v>
-      </c>
-      <c r="F2058" s="3">
-        <v>5</v>
-      </c>
-      <c r="G2058" s="3">
-        <v>12650</v>
-      </c>
-      <c r="H2058" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2059" spans="1:8">
-      <c r="A2059" s="3" t="s">
-        <v>2075</v>
-      </c>
-      <c r="B2059" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2059" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2059" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2059" s="3">
-        <v>7883</v>
-      </c>
-      <c r="F2059" s="3">
-        <v>9</v>
-      </c>
-      <c r="G2059" s="3">
-        <v>15914</v>
-      </c>
-      <c r="H2059" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2060" spans="1:8">
-      <c r="A2060" s="3" t="s">
-        <v>2076</v>
-      </c>
-      <c r="B2060" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2060" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2060" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2060" s="3">
-        <v>7875</v>
-      </c>
-      <c r="F2060" s="3">
-        <v>1</v>
-      </c>
-      <c r="G2060" s="3">
-        <v>10748</v>
-      </c>
-      <c r="H2060" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2061" spans="1:8">
-      <c r="A2061" s="3" t="s">
-        <v>2077</v>
-      </c>
-      <c r="B2061" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2061" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2061" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2061" s="3">
-        <v>7865</v>
-      </c>
-      <c r="F2061" s="3">
-        <v>1</v>
-      </c>
-      <c r="G2061" s="3">
-        <v>11823</v>
-      </c>
-      <c r="H2061" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2062" spans="1:8">
-      <c r="A2062" s="3" t="s">
-        <v>2078</v>
-      </c>
-      <c r="B2062" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2062" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2062" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2062" s="3">
-        <v>7863</v>
-      </c>
-      <c r="F2062" s="3">
-        <v>10</v>
-      </c>
-      <c r="G2062" s="3">
-        <v>15643</v>
-      </c>
-      <c r="H2062" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2063" spans="1:8">
-      <c r="A2063" s="3" t="s">
-        <v>2079</v>
-      </c>
-      <c r="B2063" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2063" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2063" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2063" s="3">
-        <v>7832</v>
-      </c>
-      <c r="F2063" s="3">
-        <v>8</v>
-      </c>
-      <c r="G2063" s="3">
-        <v>14637</v>
-      </c>
-      <c r="H2063" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2064" spans="1:8">
-      <c r="A2064" s="3" t="s">
-        <v>2080</v>
-      </c>
-      <c r="B2064" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2064" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2064" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2064" s="3">
-        <v>7815</v>
-      </c>
-      <c r="F2064" s="3">
-        <v>9</v>
-      </c>
-      <c r="G2064" s="3">
-        <v>15298</v>
-      </c>
-      <c r="H2064" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2065" spans="1:8">
-      <c r="A2065" s="3" t="s">
-        <v>2081</v>
-      </c>
-      <c r="B2065" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2065" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2065" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2065" s="3">
-        <v>7814</v>
-      </c>
-      <c r="F2065" s="3">
-        <v>6</v>
-      </c>
-      <c r="G2065" s="3">
-        <v>15158</v>
-      </c>
-      <c r="H2065" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2066" spans="1:8">
-      <c r="A2066" s="3" t="s">
-        <v>2082</v>
-      </c>
-      <c r="B2066" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2066" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2066" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2066" s="3">
-        <v>7786</v>
-      </c>
-      <c r="F2066" s="3">
-        <v>3</v>
-      </c>
-      <c r="G2066" s="3">
-        <v>13483</v>
-      </c>
-      <c r="H2066" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2067" spans="1:8">
-      <c r="A2067" s="3" t="s">
-        <v>2083</v>
-      </c>
-      <c r="B2067" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2067" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2067" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2067" s="3">
-        <v>7783</v>
-      </c>
-      <c r="F2067" s="3">
-        <v>6</v>
-      </c>
-      <c r="G2067" s="3">
-        <v>14058</v>
-      </c>
-      <c r="H2067" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2068" spans="1:8">
-      <c r="A2068" s="3" t="s">
-        <v>2084</v>
-      </c>
-      <c r="B2068" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2068" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2068" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2068" s="3">
-        <v>7764</v>
-      </c>
-      <c r="F2068" s="3">
-        <v>2</v>
-      </c>
-      <c r="G2068" s="3">
-        <v>11901</v>
-      </c>
-      <c r="H2068" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2069" spans="1:8">
-      <c r="A2069" s="3" t="s">
-        <v>2085</v>
-      </c>
-      <c r="B2069" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2069" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2069" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2069" s="3">
-        <v>7740</v>
-      </c>
-      <c r="F2069" s="3">
-        <v>6</v>
-      </c>
-      <c r="G2069" s="3">
-        <v>12945</v>
-      </c>
-      <c r="H2069" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2070" spans="1:8">
-      <c r="A2070" s="3" t="s">
-        <v>2086</v>
-      </c>
-      <c r="B2070" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2070" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2070" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2070" s="3">
-        <v>7737</v>
-      </c>
-      <c r="F2070" s="3">
-        <v>1</v>
-      </c>
-      <c r="G2070" s="3">
-        <v>12057</v>
-      </c>
-      <c r="H2070" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2071" spans="1:8">
-      <c r="A2071" s="3" t="s">
-        <v>2087</v>
-      </c>
-      <c r="B2071" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2071" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2071" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2071" s="3">
-        <v>7734</v>
-      </c>
-      <c r="F2071" s="3">
-        <v>9</v>
-      </c>
-      <c r="G2071" s="3">
-        <v>14725</v>
-      </c>
-      <c r="H2071" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2072" spans="1:8">
-      <c r="A2072" s="3" t="s">
-        <v>2088</v>
-      </c>
-      <c r="B2072" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2072" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2072" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2072" s="3">
-        <v>7720</v>
-      </c>
-      <c r="F2072" s="3">
-        <v>6</v>
-      </c>
-      <c r="G2072" s="3">
-        <v>15259</v>
-      </c>
-      <c r="H2072" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2073" spans="1:8">
-      <c r="A2073" s="3" t="s">
-        <v>2089</v>
-      </c>
-      <c r="B2073" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2073" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2073" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2073" s="3">
-        <v>7718</v>
-      </c>
-      <c r="F2073" s="3">
-        <v>9</v>
-      </c>
-      <c r="G2073" s="3">
-        <v>14228</v>
-      </c>
-      <c r="H2073" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2074" spans="1:8">
-      <c r="A2074" s="3" t="s">
-        <v>2090</v>
-      </c>
-      <c r="B2074" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2074" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2074" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2074" s="3">
-        <v>7696</v>
-      </c>
-      <c r="F2074" s="3">
-        <v>4</v>
-      </c>
-      <c r="G2074" s="3">
-        <v>12663</v>
-      </c>
-      <c r="H2074" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2075" spans="1:8">
-      <c r="A2075" s="3" t="s">
-        <v>2091</v>
-      </c>
-      <c r="B2075" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2075" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2075" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2075" s="3">
-        <v>7688</v>
-      </c>
-      <c r="F2075" s="3">
-        <v>5</v>
-      </c>
-      <c r="G2075" s="3">
-        <v>11761</v>
-      </c>
-      <c r="H2075" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2076" spans="1:8">
-      <c r="A2076" s="3" t="s">
-        <v>2092</v>
-      </c>
-      <c r="B2076" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2076" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2076" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2076" s="3">
-        <v>7675</v>
-      </c>
-      <c r="F2076" s="3">
-        <v>6</v>
-      </c>
-      <c r="G2076" s="3">
-        <v>14977</v>
-      </c>
-      <c r="H2076" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2077" spans="1:8">
-      <c r="A2077" s="3" t="s">
-        <v>2093</v>
-      </c>
-      <c r="B2077" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2077" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2077" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2077" s="3">
-        <v>7673</v>
-      </c>
-      <c r="F2077" s="3">
-        <v>3</v>
-      </c>
-      <c r="G2077" s="3">
-        <v>12352</v>
-      </c>
-      <c r="H2077" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2078" spans="1:8">
-      <c r="A2078" s="3" t="s">
-        <v>2094</v>
-      </c>
-      <c r="B2078" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2078" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2078" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2078" s="3">
-        <v>7672</v>
-      </c>
-      <c r="F2078" s="3">
-        <v>0</v>
-      </c>
-      <c r="G2078" s="3">
-        <v>10057</v>
-      </c>
-      <c r="H2078" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2079" spans="1:8">
-      <c r="A2079" s="3" t="s">
-        <v>2095</v>
-      </c>
-      <c r="B2079" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2079" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2079" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2079" s="3">
-        <v>7670</v>
-      </c>
-      <c r="F2079" s="3">
-        <v>2</v>
-      </c>
-      <c r="G2079" s="3">
-        <v>10857</v>
-      </c>
-      <c r="H2079" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2080" spans="1:8">
-      <c r="A2080" s="3" t="s">
-        <v>2096</v>
-      </c>
-      <c r="B2080" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2080" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2080" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2080" s="3">
-        <v>7664</v>
-      </c>
-      <c r="F2080" s="3">
-        <v>5</v>
-      </c>
-      <c r="G2080" s="3">
-        <v>13542</v>
-      </c>
-      <c r="H2080" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2081" spans="1:8">
-      <c r="A2081" s="3" t="s">
-        <v>2097</v>
-      </c>
-      <c r="B2081" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2081" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2081" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2081" s="3">
-        <v>7634</v>
-      </c>
-      <c r="F2081" s="3">
-        <v>9</v>
-      </c>
-      <c r="G2081" s="3">
-        <v>15995</v>
-      </c>
-      <c r="H2081" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2082" spans="1:8">
-      <c r="A2082" s="3" t="s">
-        <v>2098</v>
-      </c>
-      <c r="B2082" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2082" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2082" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2082" s="3">
-        <v>7597</v>
-      </c>
-      <c r="F2082" s="3">
-        <v>1</v>
-      </c>
-      <c r="G2082" s="3">
-        <v>10593</v>
-      </c>
-      <c r="H2082" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2083" spans="1:8">
-      <c r="A2083" s="3" t="s">
-        <v>2099</v>
-      </c>
-      <c r="B2083" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2083" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2083" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2083" s="3">
-        <v>7566</v>
-      </c>
-      <c r="F2083" s="3">
-        <v>7</v>
-      </c>
-      <c r="G2083" s="3">
-        <v>14833</v>
-      </c>
-      <c r="H2083" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2084" spans="1:8">
-      <c r="A2084" s="3" t="s">
-        <v>2100</v>
-      </c>
-      <c r="B2084" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2084" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2084" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2084" s="3">
-        <v>7548</v>
-      </c>
-      <c r="F2084" s="3">
-        <v>4</v>
-      </c>
-      <c r="G2084" s="3">
-        <v>13697</v>
-      </c>
-      <c r="H2084" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2085" spans="1:8">
-      <c r="A2085" s="3" t="s">
-        <v>2101</v>
-      </c>
-      <c r="B2085" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2085" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2085" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2085" s="3">
-        <v>7538</v>
-      </c>
-      <c r="F2085" s="3">
-        <v>6</v>
-      </c>
-      <c r="G2085" s="3">
-        <v>14336</v>
-      </c>
-      <c r="H2085" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2086" spans="1:8">
-      <c r="A2086" s="3" t="s">
-        <v>2102</v>
-      </c>
-      <c r="B2086" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2086" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2086" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2086" s="3">
-        <v>7531</v>
-      </c>
-      <c r="F2086" s="3">
-        <v>1</v>
-      </c>
-      <c r="G2086" s="3">
-        <v>10480</v>
-      </c>
-      <c r="H2086" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2087" spans="1:8">
-      <c r="A2087" s="3" t="s">
-        <v>2103</v>
-      </c>
-      <c r="B2087" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2087" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2087" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2087" s="3">
-        <v>7523</v>
-      </c>
-      <c r="F2087" s="3">
-        <v>5</v>
-      </c>
-      <c r="G2087" s="3">
-        <v>13409</v>
-      </c>
-      <c r="H2087" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2088" spans="1:8">
-      <c r="A2088" s="3" t="s">
-        <v>2104</v>
-      </c>
-      <c r="B2088" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2088" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2088" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2088" s="3">
-        <v>7518</v>
-      </c>
-      <c r="F2088" s="3">
-        <v>8</v>
-      </c>
-      <c r="G2088" s="3">
-        <v>14258</v>
-      </c>
-      <c r="H2088" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2089" spans="1:8">
-      <c r="A2089" s="3" t="s">
-        <v>2105</v>
-      </c>
-      <c r="B2089" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2089" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2089" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2089" s="3">
-        <v>7516</v>
-      </c>
-      <c r="F2089" s="3">
-        <v>0</v>
-      </c>
-      <c r="G2089" s="3">
-        <v>11262</v>
-      </c>
-      <c r="H2089" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2090" spans="1:8">
-      <c r="A2090" s="3" t="s">
-        <v>2106</v>
-      </c>
-      <c r="B2090" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2090" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2090" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2090" s="3">
-        <v>7515</v>
-      </c>
-      <c r="F2090" s="3">
-        <v>9</v>
-      </c>
-      <c r="G2090" s="3">
-        <v>15312</v>
-      </c>
-      <c r="H2090" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2091" spans="1:8">
-      <c r="A2091" s="3" t="s">
-        <v>2107</v>
-      </c>
-      <c r="B2091" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2091" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2091" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2091" s="3">
-        <v>7513</v>
-      </c>
-      <c r="F2091" s="3">
-        <v>9</v>
-      </c>
-      <c r="G2091" s="3">
-        <v>14532</v>
-      </c>
-      <c r="H2091" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2092" spans="1:8">
-      <c r="A2092" s="3" t="s">
-        <v>2108</v>
-      </c>
-      <c r="B2092" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2092" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2092" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2092" s="3">
-        <v>7491</v>
-      </c>
-      <c r="F2092" s="3">
-        <v>6</v>
-      </c>
-      <c r="G2092" s="3">
-        <v>14143</v>
-      </c>
-      <c r="H2092" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2093" spans="1:8">
-      <c r="A2093" s="3" t="s">
-        <v>2109</v>
-      </c>
-      <c r="B2093" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2093" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2093" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2093" s="3">
-        <v>7491</v>
-      </c>
-      <c r="F2093" s="3">
-        <v>3</v>
-      </c>
-      <c r="G2093" s="3">
-        <v>11816</v>
-      </c>
-      <c r="H2093" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2094" spans="1:8">
-      <c r="A2094" s="3" t="s">
-        <v>2110</v>
-      </c>
-      <c r="B2094" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2094" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2094" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2094" s="3">
-        <v>7428</v>
-      </c>
-      <c r="F2094" s="3">
-        <v>8</v>
-      </c>
-      <c r="G2094" s="3">
-        <v>14820</v>
-      </c>
-      <c r="H2094" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2095" spans="1:8">
-      <c r="A2095" s="3" t="s">
-        <v>2111</v>
-      </c>
-      <c r="B2095" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2095" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2095" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2095" s="3">
-        <v>7408</v>
-      </c>
-      <c r="F2095" s="3">
-        <v>10</v>
-      </c>
-      <c r="G2095" s="3">
-        <v>15029</v>
-      </c>
-      <c r="H2095" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2096" spans="1:8">
-      <c r="A2096" s="3" t="s">
-        <v>2112</v>
-      </c>
-      <c r="B2096" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2096" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2096" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2096" s="3">
-        <v>7382</v>
-      </c>
-      <c r="F2096" s="3">
-        <v>8</v>
-      </c>
-      <c r="G2096" s="3">
-        <v>14361</v>
-      </c>
-      <c r="H2096" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2097" spans="1:8">
-      <c r="A2097" s="3" t="s">
-        <v>2113</v>
-      </c>
-      <c r="B2097" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2097" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2097" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2097" s="3">
-        <v>7373</v>
-      </c>
-      <c r="F2097" s="3">
-        <v>9</v>
-      </c>
-      <c r="G2097" s="3">
-        <v>16155</v>
-      </c>
-      <c r="H2097" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2098" spans="1:8">
-      <c r="A2098" s="3" t="s">
-        <v>2114</v>
-      </c>
-      <c r="B2098" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2098" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2098" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2098" s="3">
-        <v>7368</v>
-      </c>
-      <c r="F2098" s="3">
-        <v>8</v>
-      </c>
-      <c r="G2098" s="3">
-        <v>14704</v>
-      </c>
-      <c r="H2098" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2099" spans="1:8">
-      <c r="A2099" s="3" t="s">
-        <v>2115</v>
-      </c>
-      <c r="B2099" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2099" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2099" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2099" s="3">
-        <v>7361</v>
-      </c>
-      <c r="F2099" s="3">
-        <v>10</v>
-      </c>
-      <c r="G2099" s="3">
-        <v>15920</v>
-      </c>
-      <c r="H2099" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2100" spans="1:8">
-      <c r="A2100" s="3" t="s">
-        <v>2116</v>
-      </c>
-      <c r="B2100" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2100" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2100" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2100" s="3">
-        <v>7342</v>
-      </c>
-      <c r="F2100" s="3">
-        <v>10</v>
-      </c>
-      <c r="G2100" s="3">
-        <v>16753</v>
-      </c>
-      <c r="H2100" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2101" spans="1:8">
-      <c r="A2101" s="3" t="s">
-        <v>2117</v>
-      </c>
-      <c r="B2101" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2101" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2101" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2101" s="3">
-        <v>7326</v>
-      </c>
-      <c r="F2101" s="3">
-        <v>1</v>
-      </c>
-      <c r="G2101" s="3">
-        <v>11346</v>
-      </c>
-      <c r="H2101" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2102" spans="1:8">
-      <c r="A2102" s="3" t="s">
-        <v>2118</v>
-      </c>
-      <c r="B2102" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2102" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2102" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2102" s="3">
-        <v>7324</v>
-      </c>
-      <c r="F2102" s="3">
-        <v>4</v>
-      </c>
-      <c r="G2102" s="3">
-        <v>11302</v>
-      </c>
-      <c r="H2102" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2103" spans="1:8">
-      <c r="A2103" s="3" t="s">
-        <v>2119</v>
-      </c>
-      <c r="B2103" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2103" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2103" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2103" s="3">
-        <v>7308</v>
-      </c>
-      <c r="F2103" s="3">
-        <v>5</v>
-      </c>
-      <c r="G2103" s="3">
-        <v>12968</v>
-      </c>
-      <c r="H2103" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2104" spans="1:8">
-      <c r="A2104" s="3" t="s">
-        <v>2120</v>
-      </c>
-      <c r="B2104" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2104" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2104" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2104" s="3">
-        <v>7293</v>
-      </c>
-      <c r="F2104" s="3">
-        <v>1</v>
-      </c>
-      <c r="G2104" s="3">
-        <v>10293</v>
-      </c>
-      <c r="H2104" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2105" spans="1:8">
-      <c r="A2105" s="3" t="s">
-        <v>2121</v>
-      </c>
-      <c r="B2105" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2105" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2105" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2105" s="3">
-        <v>7291</v>
-      </c>
-      <c r="F2105" s="3">
-        <v>1</v>
-      </c>
-      <c r="G2105" s="3">
-        <v>9587</v>
-      </c>
-      <c r="H2105" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2106" spans="1:8">
-      <c r="A2106" s="3" t="s">
-        <v>2122</v>
-      </c>
-      <c r="B2106" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2106" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2106" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2106" s="3">
-        <v>7287</v>
-      </c>
-      <c r="F2106" s="3">
-        <v>0</v>
-      </c>
-      <c r="G2106" s="3">
-        <v>9870</v>
-      </c>
-      <c r="H2106" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2107" spans="1:8">
-      <c r="A2107" s="3" t="s">
-        <v>2123</v>
-      </c>
-      <c r="B2107" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2107" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2107" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2107" s="3">
-        <v>7284</v>
-      </c>
-      <c r="F2107" s="3">
-        <v>7</v>
-      </c>
-      <c r="G2107" s="3">
-        <v>14740</v>
-      </c>
-      <c r="H2107" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2108" spans="1:8">
-      <c r="A2108" s="3" t="s">
-        <v>2124</v>
-      </c>
-      <c r="B2108" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2108" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2108" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2108" s="3">
-        <v>7263</v>
-      </c>
-      <c r="F2108" s="3">
-        <v>2</v>
-      </c>
-      <c r="G2108" s="3">
-        <v>12408</v>
-      </c>
-      <c r="H2108" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2109" spans="1:8">
-      <c r="A2109" s="3" t="s">
-        <v>2125</v>
-      </c>
-      <c r="B2109" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2109" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2109" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2109" s="3">
-        <v>7253</v>
-      </c>
-      <c r="F2109" s="3">
-        <v>4</v>
-      </c>
-      <c r="G2109" s="3">
-        <v>13319</v>
-      </c>
-      <c r="H2109" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2110" spans="1:8">
-      <c r="A2110" s="3" t="s">
-        <v>2126</v>
-      </c>
-      <c r="B2110" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2110" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2110" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2110" s="3">
-        <v>7247</v>
-      </c>
-      <c r="F2110" s="3">
-        <v>9</v>
-      </c>
-      <c r="G2110" s="3">
-        <v>14680</v>
-      </c>
-      <c r="H2110" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2111" spans="1:8">
-      <c r="A2111" s="3" t="s">
-        <v>2127</v>
-      </c>
-      <c r="B2111" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2111" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2111" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2111" s="3">
-        <v>7201</v>
-      </c>
-      <c r="F2111" s="3">
-        <v>9</v>
-      </c>
-      <c r="G2111" s="3">
-        <v>15772</v>
-      </c>
-      <c r="H2111" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2112" spans="1:8">
-      <c r="A2112" s="3" t="s">
-        <v>2128</v>
-      </c>
-      <c r="B2112" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2112" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2112" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2112" s="3">
-        <v>7192</v>
-      </c>
-      <c r="F2112" s="3">
-        <v>10</v>
-      </c>
-      <c r="G2112" s="3">
-        <v>14600</v>
-      </c>
-      <c r="H2112" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2113" spans="1:8">
-      <c r="A2113" s="3" t="s">
-        <v>2129</v>
-      </c>
-      <c r="B2113" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2113" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2113" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2113" s="3">
-        <v>7185</v>
-      </c>
-      <c r="F2113" s="3">
-        <v>6</v>
-      </c>
-      <c r="G2113" s="3">
-        <v>11880</v>
-      </c>
-      <c r="H2113" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2114" spans="1:8">
-      <c r="A2114" s="3" t="s">
-        <v>2130</v>
-      </c>
-      <c r="B2114" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2114" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2114" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2114" s="3">
-        <v>7142</v>
-      </c>
-      <c r="F2114" s="3">
-        <v>9</v>
-      </c>
-      <c r="G2114" s="3">
-        <v>16522</v>
-      </c>
-      <c r="H2114" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2115" spans="1:8">
-      <c r="A2115" s="3" t="s">
-        <v>2131</v>
-      </c>
-      <c r="B2115" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2115" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2115" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2115" s="3">
-        <v>7083</v>
-      </c>
-      <c r="F2115" s="3">
-        <v>10</v>
-      </c>
-      <c r="G2115" s="3">
-        <v>15829</v>
-      </c>
-      <c r="H2115" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2116" spans="1:8">
-      <c r="A2116" s="3" t="s">
-        <v>2132</v>
-      </c>
-      <c r="B2116" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2116" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2116" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2116" s="3">
-        <v>7083</v>
-      </c>
-      <c r="F2116" s="3">
-        <v>7</v>
-      </c>
-      <c r="G2116" s="3">
-        <v>15051</v>
-      </c>
-      <c r="H2116" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2117" spans="1:8">
-      <c r="A2117" s="3" t="s">
-        <v>2133</v>
-      </c>
-      <c r="B2117" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2117" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2117" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2117" s="3">
-        <v>7083</v>
-      </c>
-      <c r="F2117" s="3">
-        <v>1</v>
-      </c>
-      <c r="G2117" s="3">
-        <v>8816</v>
-      </c>
-      <c r="H2117" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2118" spans="1:8">
-      <c r="A2118" s="3" t="s">
-        <v>2134</v>
-      </c>
-      <c r="B2118" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2118" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2118" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2118" s="3">
-        <v>7078</v>
-      </c>
-      <c r="F2118" s="3">
-        <v>7</v>
-      </c>
-      <c r="G2118" s="3">
-        <v>12410</v>
-      </c>
-      <c r="H2118" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2119" spans="1:8">
-      <c r="A2119" s="3" t="s">
-        <v>2135</v>
-      </c>
-      <c r="B2119" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2119" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2119" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2119" s="3">
-        <v>7075</v>
-      </c>
-      <c r="F2119" s="3">
-        <v>8</v>
-      </c>
-      <c r="G2119" s="3">
-        <v>13210</v>
-      </c>
-      <c r="H2119" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2120" spans="1:8">
-      <c r="A2120" s="3" t="s">
-        <v>2136</v>
-      </c>
-      <c r="B2120" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2120" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2120" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2120" s="3">
-        <v>7066</v>
-      </c>
-      <c r="F2120" s="3">
-        <v>8</v>
-      </c>
-      <c r="G2120" s="3">
-        <v>14348</v>
-      </c>
-      <c r="H2120" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2121" spans="1:8">
-      <c r="A2121" s="3" t="s">
-        <v>2137</v>
-      </c>
-      <c r="B2121" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2121" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2121" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2121" s="3">
-        <v>7062</v>
-      </c>
-      <c r="F2121" s="3">
-        <v>9</v>
-      </c>
-      <c r="G2121" s="3">
-        <v>16199</v>
-      </c>
-      <c r="H2121" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2122" spans="1:8">
-      <c r="A2122" s="3" t="s">
-        <v>2138</v>
-      </c>
-      <c r="B2122" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2122" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2122" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2122" s="3">
-        <v>7057</v>
-      </c>
-      <c r="F2122" s="3">
-        <v>4</v>
-      </c>
-      <c r="G2122" s="3">
-        <v>12669</v>
-      </c>
-      <c r="H2122" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2123" spans="1:8">
-      <c r="A2123" s="3" t="s">
-        <v>2139</v>
-      </c>
-      <c r="B2123" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2123" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2123" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2123" s="3">
-        <v>7052</v>
-      </c>
-      <c r="F2123" s="3">
-        <v>4</v>
-      </c>
-      <c r="G2123" s="3">
-        <v>11401</v>
-      </c>
-      <c r="H2123" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2124" spans="1:8">
-      <c r="A2124" s="3" t="s">
-        <v>2140</v>
-      </c>
-      <c r="B2124" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2124" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2124" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2124" s="3">
-        <v>7047</v>
-      </c>
-      <c r="F2124" s="3">
-        <v>7</v>
-      </c>
-      <c r="G2124" s="3">
-        <v>13716</v>
-      </c>
-      <c r="H2124" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2125" spans="1:8">
-      <c r="A2125" s="3" t="s">
-        <v>2141</v>
-      </c>
-      <c r="B2125" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2125" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2125" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2125" s="3">
-        <v>7010</v>
-      </c>
-      <c r="F2125" s="3">
-        <v>0</v>
-      </c>
-      <c r="G2125" s="3">
-        <v>8313</v>
-      </c>
-      <c r="H2125" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2126" spans="1:8">
-      <c r="A2126" s="3" t="s">
-        <v>2142</v>
-      </c>
-      <c r="B2126" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2126" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2126" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2126" s="3">
-        <v>6985</v>
-      </c>
-      <c r="F2126" s="3">
-        <v>9</v>
-      </c>
-      <c r="G2126" s="3">
-        <v>14590</v>
-      </c>
-      <c r="H2126" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2127" spans="1:8">
-      <c r="A2127" s="3" t="s">
-        <v>2143</v>
-      </c>
-      <c r="B2127" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2127" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2127" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2127" s="3">
-        <v>6971</v>
-      </c>
-      <c r="F2127" s="3">
-        <v>2</v>
-      </c>
-      <c r="G2127" s="3">
-        <v>10648</v>
-      </c>
-      <c r="H2127" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2128" spans="1:8">
-      <c r="A2128" s="3" t="s">
-        <v>2144</v>
-      </c>
-      <c r="B2128" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2128" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2128" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2128" s="3">
-        <v>6962</v>
-      </c>
-      <c r="F2128" s="3">
-        <v>9</v>
-      </c>
-      <c r="G2128" s="3">
-        <v>14062</v>
-      </c>
-      <c r="H2128" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2129" spans="1:8">
-      <c r="A2129" s="3" t="s">
-        <v>2145</v>
-      </c>
-      <c r="B2129" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2129" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2129" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2129" s="3">
-        <v>6956</v>
-      </c>
-      <c r="F2129" s="3">
-        <v>6</v>
-      </c>
-      <c r="G2129" s="3">
-        <v>12278</v>
-      </c>
-      <c r="H2129" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2130" spans="1:8">
-      <c r="A2130" s="3" t="s">
-        <v>2146</v>
-      </c>
-      <c r="B2130" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2130" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2130" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2130" s="3">
-        <v>6939</v>
-      </c>
-      <c r="F2130" s="3">
-        <v>5</v>
-      </c>
-      <c r="G2130" s="3">
-        <v>12450</v>
-      </c>
-      <c r="H2130" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2131" spans="1:8">
-      <c r="A2131" s="3" t="s">
-        <v>2147</v>
-      </c>
-      <c r="B2131" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2131" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2131" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2131" s="3">
-        <v>6933</v>
-      </c>
-      <c r="F2131" s="3">
-        <v>8</v>
-      </c>
-      <c r="G2131" s="3">
-        <v>13292</v>
-      </c>
-      <c r="H2131" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2132" spans="1:8">
-      <c r="A2132" s="3" t="s">
-        <v>2148</v>
-      </c>
-      <c r="B2132" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2132" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2132" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2132" s="3">
-        <v>6916</v>
-      </c>
-      <c r="F2132" s="3">
-        <v>1</v>
-      </c>
-      <c r="G2132" s="3">
-        <v>11260</v>
-      </c>
-      <c r="H2132" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2133" spans="1:8">
-      <c r="A2133" s="3" t="s">
-        <v>2149</v>
-      </c>
-      <c r="B2133" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2133" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2133" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2133" s="3">
-        <v>6880</v>
-      </c>
-      <c r="F2133" s="3">
-        <v>6</v>
-      </c>
-      <c r="G2133" s="3">
-        <v>12463</v>
-      </c>
-      <c r="H2133" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2134" spans="1:8">
-      <c r="A2134" s="3" t="s">
-        <v>2150</v>
-      </c>
-      <c r="B2134" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2134" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2134" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2134" s="3">
-        <v>6869</v>
-      </c>
-      <c r="F2134" s="3">
-        <v>7</v>
-      </c>
-      <c r="G2134" s="3">
-        <v>14284</v>
-      </c>
-      <c r="H2134" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2135" spans="1:8">
-      <c r="A2135" s="3" t="s">
-        <v>2151</v>
-      </c>
-      <c r="B2135" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2135" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2135" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2135" s="3">
-        <v>6868</v>
-      </c>
-      <c r="F2135" s="3">
-        <v>1</v>
-      </c>
-      <c r="G2135" s="3">
-        <v>10576</v>
-      </c>
-      <c r="H2135" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2136" spans="1:8">
-      <c r="A2136" s="3" t="s">
-        <v>2152</v>
-      </c>
-      <c r="B2136" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2136" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2136" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2136" s="3">
-        <v>6860</v>
-      </c>
-      <c r="F2136" s="3">
-        <v>8</v>
-      </c>
-      <c r="G2136" s="3">
-        <v>13729</v>
-      </c>
-      <c r="H2136" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2137" spans="1:8">
-      <c r="A2137" s="3" t="s">
-        <v>2153</v>
-      </c>
-      <c r="B2137" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2137" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2137" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2137" s="3">
-        <v>6857</v>
-      </c>
-      <c r="F2137" s="3">
-        <v>9</v>
-      </c>
-      <c r="G2137" s="3">
-        <v>14708</v>
-      </c>
-      <c r="H2137" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2138" spans="1:8">
-      <c r="A2138" s="3" t="s">
-        <v>2154</v>
-      </c>
-      <c r="B2138" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2138" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2138" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2138" s="3">
-        <v>6857</v>
-      </c>
-      <c r="F2138" s="3">
-        <v>3</v>
-      </c>
-      <c r="G2138" s="3">
-        <v>10726</v>
-      </c>
-      <c r="H2138" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2139" spans="1:8">
-      <c r="A2139" s="3" t="s">
-        <v>2155</v>
-      </c>
-      <c r="B2139" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2139" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2139" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2139" s="3">
-        <v>6838</v>
-      </c>
-      <c r="F2139" s="3">
-        <v>1</v>
-      </c>
-      <c r="G2139" s="3">
-        <v>8912</v>
-      </c>
-      <c r="H2139" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2140" spans="1:8">
-      <c r="A2140" s="3" t="s">
-        <v>2156</v>
-      </c>
-      <c r="B2140" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2140" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2140" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2140" s="3">
-        <v>6838</v>
-      </c>
-      <c r="F2140" s="3">
-        <v>2</v>
-      </c>
-      <c r="G2140" s="3">
-        <v>9222</v>
-      </c>
-      <c r="H2140" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2141" spans="1:8">
-      <c r="A2141" s="3" t="s">
-        <v>2157</v>
-      </c>
-      <c r="B2141" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2141" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2141" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2141" s="3">
-        <v>6835</v>
-      </c>
-      <c r="F2141" s="3">
-        <v>9</v>
-      </c>
-      <c r="G2141" s="3">
-        <v>15709</v>
-      </c>
-      <c r="H2141" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2142" spans="1:8">
-      <c r="A2142" s="3" t="s">
-        <v>2158</v>
-      </c>
-      <c r="B2142" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2142" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2142" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2142" s="3">
-        <v>6825</v>
-      </c>
-      <c r="F2142" s="3">
-        <v>7</v>
-      </c>
-      <c r="G2142" s="3">
-        <v>14468</v>
-      </c>
-      <c r="H2142" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2143" spans="1:8">
-      <c r="A2143" s="3" t="s">
-        <v>2159</v>
-      </c>
-      <c r="B2143" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2143" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2143" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2143" s="3">
-        <v>6812</v>
-      </c>
-      <c r="F2143" s="3">
-        <v>2</v>
-      </c>
-      <c r="G2143" s="3">
-        <v>10321</v>
-      </c>
-      <c r="H2143" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2144" spans="1:8">
-      <c r="A2144" s="3" t="s">
-        <v>2160</v>
-      </c>
-      <c r="B2144" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2144" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2144" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2144" s="3">
-        <v>6794</v>
-      </c>
-      <c r="F2144" s="3">
-        <v>9</v>
-      </c>
-      <c r="G2144" s="3">
-        <v>14291</v>
-      </c>
-      <c r="H2144" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2145" spans="1:8">
-      <c r="A2145" s="3" t="s">
-        <v>2161</v>
-      </c>
-      <c r="B2145" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2145" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2145" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2145" s="3">
-        <v>6784</v>
-      </c>
-      <c r="F2145" s="3">
-        <v>5</v>
-      </c>
-      <c r="G2145" s="3">
-        <v>13675</v>
-      </c>
-      <c r="H2145" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2146" spans="1:8">
-      <c r="A2146" s="3" t="s">
-        <v>2162</v>
-      </c>
-      <c r="B2146" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2146" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2146" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2146" s="3">
-        <v>6762</v>
-      </c>
-      <c r="F2146" s="3">
-        <v>2</v>
-      </c>
-      <c r="G2146" s="3">
-        <v>10632</v>
-      </c>
-      <c r="H2146" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2147" spans="1:8">
-      <c r="A2147" s="3" t="s">
-        <v>2163</v>
-      </c>
-      <c r="B2147" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2147" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2147" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2147" s="3">
-        <v>6737</v>
-      </c>
-      <c r="F2147" s="3">
-        <v>10</v>
-      </c>
-      <c r="G2147" s="3">
-        <v>14601</v>
-      </c>
-      <c r="H2147" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2148" spans="1:8">
-      <c r="A2148" s="3" t="s">
-        <v>2164</v>
-      </c>
-      <c r="B2148" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2148" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2148" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2148" s="3">
-        <v>6735</v>
-      </c>
-      <c r="F2148" s="3">
-        <v>5</v>
-      </c>
-      <c r="G2148" s="3">
-        <v>13401</v>
-      </c>
-      <c r="H2148" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2149" spans="1:8">
-      <c r="A2149" s="3" t="s">
-        <v>2165</v>
-      </c>
-      <c r="B2149" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2149" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2149" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2149" s="3">
-        <v>6731</v>
-      </c>
-      <c r="F2149" s="3">
-        <v>4</v>
-      </c>
-      <c r="G2149" s="3">
-        <v>11616</v>
-      </c>
-      <c r="H2149" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2150" spans="1:8">
-      <c r="A2150" s="3" t="s">
-        <v>2166</v>
-      </c>
-      <c r="B2150" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2150" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2150" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2150" s="3">
-        <v>6711</v>
-      </c>
-      <c r="F2150" s="3">
-        <v>5</v>
-      </c>
-      <c r="G2150" s="3">
-        <v>10866</v>
-      </c>
-      <c r="H2150" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2151" spans="1:8">
-      <c r="A2151" s="3" t="s">
-        <v>2167</v>
-      </c>
-      <c r="B2151" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2151" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2151" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2151" s="3">
-        <v>6707</v>
-      </c>
-      <c r="F2151" s="3">
-        <v>9</v>
-      </c>
-      <c r="G2151" s="3">
-        <v>14143</v>
-      </c>
-      <c r="H2151" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2152" spans="1:8">
-      <c r="A2152" s="3" t="s">
-        <v>2168</v>
-      </c>
-      <c r="B2152" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2152" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2152" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2152" s="3">
-        <v>6705</v>
-      </c>
-      <c r="F2152" s="3">
-        <v>8</v>
-      </c>
-      <c r="G2152" s="3">
-        <v>13344</v>
-      </c>
-      <c r="H2152" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2153" spans="1:8">
-      <c r="A2153" s="3" t="s">
-        <v>2169</v>
-      </c>
-      <c r="B2153" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2153" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2153" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2153" s="3">
-        <v>6700</v>
-      </c>
-      <c r="F2153" s="3">
-        <v>9</v>
-      </c>
-      <c r="G2153" s="3">
-        <v>15395</v>
-      </c>
-      <c r="H2153" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2154" spans="1:8">
-      <c r="A2154" s="3" t="s">
-        <v>2170</v>
-      </c>
-      <c r="B2154" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2154" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2154" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2154" s="3">
-        <v>6689</v>
-      </c>
-      <c r="F2154" s="3">
-        <v>5</v>
-      </c>
-      <c r="G2154" s="3">
-        <v>13282</v>
-      </c>
-      <c r="H2154" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2155" spans="1:8">
-      <c r="A2155" s="3" t="s">
-        <v>2171</v>
-      </c>
-      <c r="B2155" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2155" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2155" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2155" s="3">
-        <v>6668</v>
-      </c>
-      <c r="F2155" s="3">
-        <v>5</v>
-      </c>
-      <c r="G2155" s="3">
-        <v>12948</v>
-      </c>
-      <c r="H2155" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2156" spans="1:8">
-      <c r="A2156" s="3" t="s">
-        <v>2172</v>
-      </c>
-      <c r="B2156" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2156" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2156" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2156" s="3">
-        <v>6658</v>
-      </c>
-      <c r="F2156" s="3">
-        <v>6</v>
-      </c>
-      <c r="G2156" s="3">
-        <v>12206</v>
-      </c>
-      <c r="H2156" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2157" spans="1:8">
-      <c r="A2157" s="3" t="s">
-        <v>2173</v>
-      </c>
-      <c r="B2157" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2157" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2157" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2157" s="3">
-        <v>6652</v>
-      </c>
-      <c r="F2157" s="3">
-        <v>8</v>
-      </c>
-      <c r="G2157" s="3">
-        <v>12518</v>
-      </c>
-      <c r="H2157" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2158" spans="1:8">
-      <c r="A2158" s="3" t="s">
-        <v>2174</v>
-      </c>
-      <c r="B2158" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2158" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2158" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2158" s="3">
-        <v>6636</v>
-      </c>
-      <c r="F2158" s="3">
-        <v>4</v>
-      </c>
-      <c r="G2158" s="3">
-        <v>10143</v>
-      </c>
-      <c r="H2158" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2159" spans="1:8">
-      <c r="A2159" s="3" t="s">
-        <v>2175</v>
-      </c>
-      <c r="B2159" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2159" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2159" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2159" s="3">
-        <v>6624</v>
-      </c>
-      <c r="F2159" s="3">
-        <v>9</v>
-      </c>
-      <c r="G2159" s="3">
-        <v>14520</v>
-      </c>
-      <c r="H2159" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2160" spans="1:8">
-      <c r="A2160" s="3" t="s">
-        <v>2176</v>
-      </c>
-      <c r="B2160" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2160" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2160" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2160" s="3">
-        <v>6623</v>
-      </c>
-      <c r="F2160" s="3">
-        <v>9</v>
-      </c>
-      <c r="G2160" s="3">
-        <v>14533</v>
-      </c>
-      <c r="H2160" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2161" spans="1:8">
-      <c r="A2161" s="3" t="s">
-        <v>2177</v>
-      </c>
-      <c r="B2161" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2161" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2161" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2161" s="3">
-        <v>6605</v>
-      </c>
-      <c r="F2161" s="3">
-        <v>2</v>
-      </c>
-      <c r="G2161" s="3">
-        <v>9948</v>
-      </c>
-      <c r="H2161" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2162" spans="1:8">
-      <c r="A2162" s="3" t="s">
-        <v>2178</v>
-      </c>
-      <c r="B2162" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2162" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2162" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2162" s="3">
-        <v>6571</v>
-      </c>
-      <c r="F2162" s="3">
-        <v>10</v>
-      </c>
-      <c r="G2162" s="3">
-        <v>16416</v>
-      </c>
-      <c r="H2162" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2163" spans="1:8">
-      <c r="A2163" s="3" t="s">
-        <v>2179</v>
-      </c>
-      <c r="B2163" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2163" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2163" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2163" s="3">
-        <v>6558</v>
-      </c>
-      <c r="F2163" s="3">
-        <v>10</v>
-      </c>
-      <c r="G2163" s="3">
-        <v>16107</v>
-      </c>
-      <c r="H2163" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2164" spans="1:8">
-      <c r="A2164" s="3" t="s">
-        <v>2180</v>
-      </c>
-      <c r="B2164" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2164" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2164" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2164" s="3">
-        <v>6513</v>
-      </c>
-      <c r="F2164" s="3">
-        <v>4</v>
-      </c>
-      <c r="G2164" s="3">
-        <v>10670</v>
-      </c>
-      <c r="H2164" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2165" spans="1:8">
-      <c r="A2165" s="3" t="s">
-        <v>2181</v>
-      </c>
-      <c r="B2165" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2165" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2165" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2165" s="3">
-        <v>6510</v>
-      </c>
-      <c r="F2165" s="3">
-        <v>0</v>
-      </c>
-      <c r="G2165" s="3">
-        <v>7627</v>
-      </c>
-      <c r="H2165" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2166" spans="1:8">
-      <c r="A2166" s="3" t="s">
-        <v>2182</v>
-      </c>
-      <c r="B2166" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2166" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2166" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2166" s="3">
-        <v>6502</v>
-      </c>
-      <c r="F2166" s="3">
-        <v>10</v>
-      </c>
-      <c r="G2166" s="3">
-        <v>13817</v>
-      </c>
-      <c r="H2166" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2167" spans="1:8">
-      <c r="A2167" s="3" t="s">
-        <v>2183</v>
-      </c>
-      <c r="B2167" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2167" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2167" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2167" s="3">
-        <v>6494</v>
-      </c>
-      <c r="F2167" s="3">
-        <v>4</v>
-      </c>
-      <c r="G2167" s="3">
-        <v>12442</v>
-      </c>
-      <c r="H2167" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2168" spans="1:8">
-      <c r="A2168" s="3" t="s">
-        <v>2184</v>
-      </c>
-      <c r="B2168" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2168" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2168" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2168" s="3">
-        <v>6469</v>
-      </c>
-      <c r="F2168" s="3">
-        <v>8</v>
-      </c>
-      <c r="G2168" s="3">
-        <v>14904</v>
-      </c>
-      <c r="H2168" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2169" spans="1:8">
-      <c r="A2169" s="3" t="s">
-        <v>2185</v>
-      </c>
-      <c r="B2169" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2169" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2169" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2169" s="3">
-        <v>6443</v>
-      </c>
-      <c r="F2169" s="3">
-        <v>7</v>
-      </c>
-      <c r="G2169" s="3">
-        <v>12029</v>
-      </c>
-      <c r="H2169" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2170" spans="1:8">
-      <c r="A2170" s="3" t="s">
-        <v>2186</v>
-      </c>
-      <c r="B2170" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2170" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2170" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2170" s="3">
-        <v>6437</v>
-      </c>
-      <c r="F2170" s="3">
-        <v>2</v>
-      </c>
-      <c r="G2170" s="3">
-        <v>9998</v>
-      </c>
-      <c r="H2170" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2171" spans="1:8">
-      <c r="A2171" s="3" t="s">
-        <v>2187</v>
-      </c>
-      <c r="B2171" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2171" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2171" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2171" s="3">
-        <v>6429</v>
-      </c>
-      <c r="F2171" s="3">
-        <v>1</v>
-      </c>
-      <c r="G2171" s="3">
-        <v>10032</v>
-      </c>
-      <c r="H2171" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2172" spans="1:8">
-      <c r="A2172" s="3" t="s">
-        <v>2188</v>
-      </c>
-      <c r="B2172" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2172" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2172" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2172" s="3">
-        <v>6379</v>
-      </c>
-      <c r="F2172" s="3">
-        <v>2</v>
-      </c>
-      <c r="G2172" s="3">
-        <v>10823</v>
-      </c>
-      <c r="H2172" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2173" spans="1:8">
-      <c r="A2173" s="3" t="s">
-        <v>2189</v>
-      </c>
-      <c r="B2173" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2173" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2173" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2173" s="3">
-        <v>6370</v>
-      </c>
-      <c r="F2173" s="3">
-        <v>7</v>
-      </c>
-      <c r="G2173" s="3">
-        <v>12508</v>
-      </c>
-      <c r="H2173" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2174" spans="1:8">
-      <c r="A2174" s="3" t="s">
-        <v>2190</v>
-      </c>
-      <c r="B2174" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2174" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2174" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2174" s="3">
-        <v>6367</v>
-      </c>
-      <c r="F2174" s="3">
-        <v>9</v>
-      </c>
-      <c r="G2174" s="3">
-        <v>13780</v>
-      </c>
-      <c r="H2174" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2175" spans="1:8">
-      <c r="A2175" s="3" t="s">
-        <v>2191</v>
-      </c>
-      <c r="B2175" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2175" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2175" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2175" s="3">
-        <v>6327</v>
-      </c>
-      <c r="F2175" s="3">
-        <v>8</v>
-      </c>
-      <c r="G2175" s="3">
-        <v>14962</v>
-      </c>
-      <c r="H2175" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2176" spans="1:8">
-      <c r="A2176" s="3" t="s">
-        <v>2192</v>
-      </c>
-      <c r="B2176" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2176" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2176" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2176" s="3">
-        <v>6311</v>
-      </c>
-      <c r="F2176" s="3">
-        <v>0</v>
-      </c>
-      <c r="G2176" s="3">
-        <v>8014</v>
-      </c>
-      <c r="H2176" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2177" spans="1:8">
-      <c r="A2177" s="3" t="s">
-        <v>2193</v>
-      </c>
-      <c r="B2177" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2177" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2177" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2177" s="3">
-        <v>6300</v>
-      </c>
-      <c r="F2177" s="3">
-        <v>5</v>
-      </c>
-      <c r="G2177" s="3">
-        <v>10975</v>
-      </c>
-      <c r="H2177" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2178" spans="1:8">
-      <c r="A2178" s="3" t="s">
-        <v>2194</v>
-      </c>
-      <c r="B2178" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2178" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2178" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2178" s="3">
-        <v>6277</v>
-      </c>
-      <c r="F2178" s="3">
-        <v>7</v>
-      </c>
-      <c r="G2178" s="3">
-        <v>13158</v>
-      </c>
-      <c r="H2178" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2179" spans="1:8">
-      <c r="A2179" s="3" t="s">
-        <v>2195</v>
-      </c>
-      <c r="B2179" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2179" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2179" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2179" s="3">
-        <v>6276</v>
-      </c>
-      <c r="F2179" s="3">
-        <v>5</v>
-      </c>
-      <c r="G2179" s="3">
-        <v>10347</v>
-      </c>
-      <c r="H2179" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2180" spans="1:8">
-      <c r="A2180" s="3" t="s">
-        <v>2196</v>
-      </c>
-      <c r="B2180" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2180" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2180" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2180" s="3">
-        <v>6273</v>
-      </c>
-      <c r="F2180" s="3">
-        <v>5</v>
-      </c>
-      <c r="G2180" s="3">
-        <v>10871</v>
-      </c>
-      <c r="H2180" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2181" spans="1:8">
-      <c r="A2181" s="3" t="s">
-        <v>2197</v>
-      </c>
-      <c r="B2181" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2181" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2181" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2181" s="3">
-        <v>6266</v>
-      </c>
-      <c r="F2181" s="3">
-        <v>8</v>
-      </c>
-      <c r="G2181" s="3">
-        <v>14413</v>
-      </c>
-      <c r="H2181" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2182" spans="1:8">
-      <c r="A2182" s="3" t="s">
-        <v>2198</v>
-      </c>
-      <c r="B2182" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2182" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2182" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2182" s="3">
-        <v>6262</v>
-      </c>
-      <c r="F2182" s="3">
-        <v>3</v>
-      </c>
-      <c r="G2182" s="3">
-        <v>11108</v>
-      </c>
-      <c r="H2182" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2183" spans="1:8">
-      <c r="A2183" s="3" t="s">
-        <v>2199</v>
-      </c>
-      <c r="B2183" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2183" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2183" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2183" s="3">
-        <v>6198</v>
-      </c>
-      <c r="F2183" s="3">
-        <v>1</v>
-      </c>
-      <c r="G2183" s="3">
-        <v>9539</v>
-      </c>
-      <c r="H2183" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2184" spans="1:8">
-      <c r="A2184" s="3" t="s">
-        <v>2200</v>
-      </c>
-      <c r="B2184" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2184" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2184" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2184" s="3">
-        <v>6196</v>
-      </c>
-      <c r="F2184" s="3">
-        <v>2</v>
-      </c>
-      <c r="G2184" s="3">
-        <v>8917</v>
-      </c>
-      <c r="H2184" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2185" spans="1:8">
-      <c r="A2185" s="3" t="s">
-        <v>2201</v>
-      </c>
-      <c r="B2185" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2185" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2185" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2185" s="3">
-        <v>6194</v>
-      </c>
-      <c r="F2185" s="3">
-        <v>2</v>
-      </c>
-      <c r="G2185" s="3">
-        <v>9895</v>
-      </c>
-      <c r="H2185" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2186" spans="1:8">
-      <c r="A2186" s="3" t="s">
-        <v>2202</v>
-      </c>
-      <c r="B2186" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2186" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2186" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2186" s="3">
-        <v>6187</v>
-      </c>
-      <c r="F2186" s="3">
-        <v>8</v>
-      </c>
-      <c r="G2186" s="3">
-        <v>12445</v>
-      </c>
-      <c r="H2186" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2187" spans="1:8">
-      <c r="A2187" s="3" t="s">
-        <v>2203</v>
-      </c>
-      <c r="B2187" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2187" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2187" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2187" s="3">
-        <v>6166</v>
-      </c>
-      <c r="F2187" s="3">
-        <v>3</v>
-      </c>
-      <c r="G2187" s="3">
-        <v>9617</v>
-      </c>
-      <c r="H2187" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2188" spans="1:8">
-      <c r="A2188" s="3" t="s">
-        <v>2204</v>
-      </c>
-      <c r="B2188" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2188" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2188" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2188" s="3">
-        <v>6166</v>
-      </c>
-      <c r="F2188" s="3">
-        <v>8</v>
-      </c>
-      <c r="G2188" s="3">
-        <v>13107</v>
-      </c>
-      <c r="H2188" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2189" spans="1:8">
-      <c r="A2189" s="3" t="s">
-        <v>2205</v>
-      </c>
-      <c r="B2189" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2189" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2189" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2189" s="3">
-        <v>6163</v>
-      </c>
-      <c r="F2189" s="3">
-        <v>6</v>
-      </c>
-      <c r="G2189" s="3">
-        <v>11596</v>
-      </c>
-      <c r="H2189" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2190" spans="1:8">
-      <c r="A2190" s="3" t="s">
-        <v>2206</v>
-      </c>
-      <c r="B2190" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2190" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2190" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2190" s="3">
-        <v>6149</v>
-      </c>
-      <c r="F2190" s="3">
-        <v>7</v>
-      </c>
-      <c r="G2190" s="3">
-        <v>13612</v>
-      </c>
-      <c r="H2190" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2191" spans="1:8">
-      <c r="A2191" s="3" t="s">
-        <v>2207</v>
-      </c>
-      <c r="B2191" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2191" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2191" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2191" s="3">
-        <v>6134</v>
-      </c>
-      <c r="F2191" s="3">
-        <v>3</v>
-      </c>
-      <c r="G2191" s="3">
-        <v>9720</v>
-      </c>
-      <c r="H2191" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2192" spans="1:8">
-      <c r="A2192" s="3" t="s">
-        <v>2208</v>
-      </c>
-      <c r="B2192" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2192" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2192" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2192" s="3">
-        <v>6116</v>
-      </c>
-      <c r="F2192" s="3">
-        <v>0</v>
-      </c>
-      <c r="G2192" s="3">
-        <v>9985</v>
-      </c>
-      <c r="H2192" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2193" spans="1:8">
-      <c r="A2193" s="3" t="s">
-        <v>2209</v>
-      </c>
-      <c r="B2193" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2193" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2193" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2193" s="3">
-        <v>6113</v>
-      </c>
-      <c r="F2193" s="3">
-        <v>1</v>
-      </c>
-      <c r="G2193" s="3">
-        <v>8131</v>
-      </c>
-      <c r="H2193" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2194" spans="1:8">
-      <c r="A2194" s="3" t="s">
-        <v>2210</v>
-      </c>
-      <c r="B2194" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2194" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2194" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2194" s="3">
-        <v>6096</v>
-      </c>
-      <c r="F2194" s="3">
-        <v>7</v>
-      </c>
-      <c r="G2194" s="3">
-        <v>14005</v>
-      </c>
-      <c r="H2194" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2195" spans="1:8">
-      <c r="A2195" s="3" t="s">
-        <v>2211</v>
-      </c>
-      <c r="B2195" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2195" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2195" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2195" s="3">
-        <v>6076</v>
-      </c>
-      <c r="F2195" s="3">
-        <v>10</v>
-      </c>
-      <c r="G2195" s="3">
-        <v>15001</v>
-      </c>
-      <c r="H2195" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2196" spans="1:8">
-      <c r="A2196" s="3" t="s">
-        <v>2212</v>
-      </c>
-      <c r="B2196" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2196" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2196" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2196" s="3">
-        <v>6073</v>
-      </c>
-      <c r="F2196" s="3">
-        <v>1</v>
-      </c>
-      <c r="G2196" s="3">
-        <v>9317</v>
-      </c>
-      <c r="H2196" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2197" spans="1:8">
-      <c r="A2197" s="3" t="s">
-        <v>2213</v>
-      </c>
-      <c r="B2197" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2197" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2197" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2197" s="3">
-        <v>6064</v>
-      </c>
-      <c r="F2197" s="3">
-        <v>5</v>
-      </c>
-      <c r="G2197" s="3">
-        <v>12092</v>
-      </c>
-      <c r="H2197" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2198" spans="1:8">
-      <c r="A2198" s="3" t="s">
-        <v>2214</v>
-      </c>
-      <c r="B2198" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2198" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2198" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2198" s="3">
-        <v>6047</v>
-      </c>
-      <c r="F2198" s="3">
-        <v>0</v>
-      </c>
-      <c r="G2198" s="3">
-        <v>10040</v>
-      </c>
-      <c r="H2198" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2199" spans="1:8">
-      <c r="A2199" s="3" t="s">
-        <v>2215</v>
-      </c>
-      <c r="B2199" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2199" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2199" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2199" s="3">
-        <v>6040</v>
-      </c>
-      <c r="F2199" s="3">
-        <v>10</v>
-      </c>
-      <c r="G2199" s="3">
-        <v>14324</v>
-      </c>
-      <c r="H2199" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2200" spans="1:8">
-      <c r="A2200" s="3" t="s">
-        <v>2216</v>
-      </c>
-      <c r="B2200" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2200" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2200" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2200" s="3">
-        <v>6024</v>
-      </c>
-      <c r="F2200" s="3">
-        <v>4</v>
-      </c>
-      <c r="G2200" s="3">
-        <v>11486</v>
-      </c>
-      <c r="H2200" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2201" spans="1:8">
-      <c r="A2201" s="3" t="s">
-        <v>2217</v>
-      </c>
-      <c r="B2201" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2201" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2201" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2201" s="3">
-        <v>5998</v>
-      </c>
-      <c r="F2201" s="3">
-        <v>9</v>
-      </c>
-      <c r="G2201" s="3">
-        <v>13649</v>
-      </c>
-      <c r="H2201" s="3">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/NGO_Project_MNE_Dataset_2000.xlsx
+++ b/NGO_Project_MNE_Dataset_2000.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$2001</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$1</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8008" uniqueCount="2018">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8808" uniqueCount="2218">
   <si>
     <t>Household_ID</t>
   </si>
@@ -6071,6 +6071,606 @@
   </si>
   <si>
     <t>HH-3000</t>
+  </si>
+  <si>
+    <t>HH-3001</t>
+  </si>
+  <si>
+    <t>HH-3002</t>
+  </si>
+  <si>
+    <t>HH-3003</t>
+  </si>
+  <si>
+    <t>HH-3004</t>
+  </si>
+  <si>
+    <t>HH-3005</t>
+  </si>
+  <si>
+    <t>HH-3006</t>
+  </si>
+  <si>
+    <t>HH-3007</t>
+  </si>
+  <si>
+    <t>HH-3008</t>
+  </si>
+  <si>
+    <t>HH-3009</t>
+  </si>
+  <si>
+    <t>HH-3010</t>
+  </si>
+  <si>
+    <t>HH-3011</t>
+  </si>
+  <si>
+    <t>HH-3012</t>
+  </si>
+  <si>
+    <t>HH-3013</t>
+  </si>
+  <si>
+    <t>HH-3014</t>
+  </si>
+  <si>
+    <t>HH-3015</t>
+  </si>
+  <si>
+    <t>HH-3016</t>
+  </si>
+  <si>
+    <t>HH-3017</t>
+  </si>
+  <si>
+    <t>HH-3018</t>
+  </si>
+  <si>
+    <t>HH-3019</t>
+  </si>
+  <si>
+    <t>HH-3020</t>
+  </si>
+  <si>
+    <t>HH-3021</t>
+  </si>
+  <si>
+    <t>HH-3022</t>
+  </si>
+  <si>
+    <t>HH-3023</t>
+  </si>
+  <si>
+    <t>HH-3024</t>
+  </si>
+  <si>
+    <t>HH-3025</t>
+  </si>
+  <si>
+    <t>HH-3026</t>
+  </si>
+  <si>
+    <t>HH-3027</t>
+  </si>
+  <si>
+    <t>HH-3028</t>
+  </si>
+  <si>
+    <t>HH-3029</t>
+  </si>
+  <si>
+    <t>HH-3030</t>
+  </si>
+  <si>
+    <t>HH-3031</t>
+  </si>
+  <si>
+    <t>HH-3032</t>
+  </si>
+  <si>
+    <t>HH-3033</t>
+  </si>
+  <si>
+    <t>HH-3034</t>
+  </si>
+  <si>
+    <t>HH-3035</t>
+  </si>
+  <si>
+    <t>HH-3036</t>
+  </si>
+  <si>
+    <t>HH-3037</t>
+  </si>
+  <si>
+    <t>HH-3038</t>
+  </si>
+  <si>
+    <t>HH-3039</t>
+  </si>
+  <si>
+    <t>HH-3040</t>
+  </si>
+  <si>
+    <t>HH-3041</t>
+  </si>
+  <si>
+    <t>HH-3042</t>
+  </si>
+  <si>
+    <t>HH-3043</t>
+  </si>
+  <si>
+    <t>HH-3044</t>
+  </si>
+  <si>
+    <t>HH-3045</t>
+  </si>
+  <si>
+    <t>HH-3046</t>
+  </si>
+  <si>
+    <t>HH-3047</t>
+  </si>
+  <si>
+    <t>HH-3048</t>
+  </si>
+  <si>
+    <t>HH-3049</t>
+  </si>
+  <si>
+    <t>HH-3050</t>
+  </si>
+  <si>
+    <t>HH-3051</t>
+  </si>
+  <si>
+    <t>HH-3052</t>
+  </si>
+  <si>
+    <t>HH-3053</t>
+  </si>
+  <si>
+    <t>HH-3054</t>
+  </si>
+  <si>
+    <t>HH-3055</t>
+  </si>
+  <si>
+    <t>HH-3056</t>
+  </si>
+  <si>
+    <t>HH-3057</t>
+  </si>
+  <si>
+    <t>HH-3058</t>
+  </si>
+  <si>
+    <t>HH-3059</t>
+  </si>
+  <si>
+    <t>HH-3060</t>
+  </si>
+  <si>
+    <t>HH-3061</t>
+  </si>
+  <si>
+    <t>HH-3062</t>
+  </si>
+  <si>
+    <t>HH-3063</t>
+  </si>
+  <si>
+    <t>HH-3064</t>
+  </si>
+  <si>
+    <t>HH-3065</t>
+  </si>
+  <si>
+    <t>HH-3066</t>
+  </si>
+  <si>
+    <t>HH-3067</t>
+  </si>
+  <si>
+    <t>HH-3068</t>
+  </si>
+  <si>
+    <t>HH-3069</t>
+  </si>
+  <si>
+    <t>HH-3070</t>
+  </si>
+  <si>
+    <t>HH-3071</t>
+  </si>
+  <si>
+    <t>HH-3072</t>
+  </si>
+  <si>
+    <t>HH-3073</t>
+  </si>
+  <si>
+    <t>HH-3074</t>
+  </si>
+  <si>
+    <t>HH-3075</t>
+  </si>
+  <si>
+    <t>HH-3076</t>
+  </si>
+  <si>
+    <t>HH-3077</t>
+  </si>
+  <si>
+    <t>HH-3078</t>
+  </si>
+  <si>
+    <t>HH-3079</t>
+  </si>
+  <si>
+    <t>HH-3080</t>
+  </si>
+  <si>
+    <t>HH-3081</t>
+  </si>
+  <si>
+    <t>HH-3082</t>
+  </si>
+  <si>
+    <t>HH-3083</t>
+  </si>
+  <si>
+    <t>HH-3084</t>
+  </si>
+  <si>
+    <t>HH-3085</t>
+  </si>
+  <si>
+    <t>HH-3086</t>
+  </si>
+  <si>
+    <t>HH-3087</t>
+  </si>
+  <si>
+    <t>HH-3088</t>
+  </si>
+  <si>
+    <t>HH-3089</t>
+  </si>
+  <si>
+    <t>HH-3090</t>
+  </si>
+  <si>
+    <t>HH-3091</t>
+  </si>
+  <si>
+    <t>HH-3092</t>
+  </si>
+  <si>
+    <t>HH-3093</t>
+  </si>
+  <si>
+    <t>HH-3094</t>
+  </si>
+  <si>
+    <t>HH-3095</t>
+  </si>
+  <si>
+    <t>HH-3096</t>
+  </si>
+  <si>
+    <t>HH-3097</t>
+  </si>
+  <si>
+    <t>HH-3098</t>
+  </si>
+  <si>
+    <t>HH-3099</t>
+  </si>
+  <si>
+    <t>HH-3100</t>
+  </si>
+  <si>
+    <t>HH-3101</t>
+  </si>
+  <si>
+    <t>HH-3102</t>
+  </si>
+  <si>
+    <t>HH-3103</t>
+  </si>
+  <si>
+    <t>HH-3104</t>
+  </si>
+  <si>
+    <t>HH-3105</t>
+  </si>
+  <si>
+    <t>HH-3106</t>
+  </si>
+  <si>
+    <t>HH-3107</t>
+  </si>
+  <si>
+    <t>HH-3108</t>
+  </si>
+  <si>
+    <t>HH-3109</t>
+  </si>
+  <si>
+    <t>HH-3110</t>
+  </si>
+  <si>
+    <t>HH-3111</t>
+  </si>
+  <si>
+    <t>HH-3112</t>
+  </si>
+  <si>
+    <t>HH-3113</t>
+  </si>
+  <si>
+    <t>HH-3114</t>
+  </si>
+  <si>
+    <t>HH-3115</t>
+  </si>
+  <si>
+    <t>HH-3116</t>
+  </si>
+  <si>
+    <t>HH-3117</t>
+  </si>
+  <si>
+    <t>HH-3118</t>
+  </si>
+  <si>
+    <t>HH-3119</t>
+  </si>
+  <si>
+    <t>HH-3120</t>
+  </si>
+  <si>
+    <t>HH-3121</t>
+  </si>
+  <si>
+    <t>HH-3122</t>
+  </si>
+  <si>
+    <t>HH-3123</t>
+  </si>
+  <si>
+    <t>HH-3124</t>
+  </si>
+  <si>
+    <t>HH-3125</t>
+  </si>
+  <si>
+    <t>HH-3126</t>
+  </si>
+  <si>
+    <t>HH-3127</t>
+  </si>
+  <si>
+    <t>HH-3128</t>
+  </si>
+  <si>
+    <t>HH-3129</t>
+  </si>
+  <si>
+    <t>HH-3130</t>
+  </si>
+  <si>
+    <t>HH-3131</t>
+  </si>
+  <si>
+    <t>HH-3132</t>
+  </si>
+  <si>
+    <t>HH-3133</t>
+  </si>
+  <si>
+    <t>HH-3134</t>
+  </si>
+  <si>
+    <t>HH-3135</t>
+  </si>
+  <si>
+    <t>HH-3136</t>
+  </si>
+  <si>
+    <t>HH-3137</t>
+  </si>
+  <si>
+    <t>HH-3138</t>
+  </si>
+  <si>
+    <t>HH-3139</t>
+  </si>
+  <si>
+    <t>HH-3140</t>
+  </si>
+  <si>
+    <t>HH-3141</t>
+  </si>
+  <si>
+    <t>HH-3142</t>
+  </si>
+  <si>
+    <t>HH-3143</t>
+  </si>
+  <si>
+    <t>HH-3144</t>
+  </si>
+  <si>
+    <t>HH-3145</t>
+  </si>
+  <si>
+    <t>HH-3146</t>
+  </si>
+  <si>
+    <t>HH-3147</t>
+  </si>
+  <si>
+    <t>HH-3148</t>
+  </si>
+  <si>
+    <t>HH-3149</t>
+  </si>
+  <si>
+    <t>HH-3150</t>
+  </si>
+  <si>
+    <t>HH-3151</t>
+  </si>
+  <si>
+    <t>HH-3152</t>
+  </si>
+  <si>
+    <t>HH-3153</t>
+  </si>
+  <si>
+    <t>HH-3154</t>
+  </si>
+  <si>
+    <t>HH-3155</t>
+  </si>
+  <si>
+    <t>HH-3156</t>
+  </si>
+  <si>
+    <t>HH-3157</t>
+  </si>
+  <si>
+    <t>HH-3158</t>
+  </si>
+  <si>
+    <t>HH-3159</t>
+  </si>
+  <si>
+    <t>HH-3160</t>
+  </si>
+  <si>
+    <t>HH-3161</t>
+  </si>
+  <si>
+    <t>HH-3162</t>
+  </si>
+  <si>
+    <t>HH-3163</t>
+  </si>
+  <si>
+    <t>HH-3164</t>
+  </si>
+  <si>
+    <t>HH-3165</t>
+  </si>
+  <si>
+    <t>HH-3166</t>
+  </si>
+  <si>
+    <t>HH-3167</t>
+  </si>
+  <si>
+    <t>HH-3168</t>
+  </si>
+  <si>
+    <t>HH-3169</t>
+  </si>
+  <si>
+    <t>HH-3170</t>
+  </si>
+  <si>
+    <t>HH-3171</t>
+  </si>
+  <si>
+    <t>HH-3172</t>
+  </si>
+  <si>
+    <t>HH-3173</t>
+  </si>
+  <si>
+    <t>HH-3174</t>
+  </si>
+  <si>
+    <t>HH-3175</t>
+  </si>
+  <si>
+    <t>HH-3176</t>
+  </si>
+  <si>
+    <t>HH-3177</t>
+  </si>
+  <si>
+    <t>HH-3178</t>
+  </si>
+  <si>
+    <t>HH-3179</t>
+  </si>
+  <si>
+    <t>HH-3180</t>
+  </si>
+  <si>
+    <t>HH-3181</t>
+  </si>
+  <si>
+    <t>HH-3182</t>
+  </si>
+  <si>
+    <t>HH-3183</t>
+  </si>
+  <si>
+    <t>HH-3184</t>
+  </si>
+  <si>
+    <t>HH-3185</t>
+  </si>
+  <si>
+    <t>HH-3186</t>
+  </si>
+  <si>
+    <t>HH-3187</t>
+  </si>
+  <si>
+    <t>HH-3188</t>
+  </si>
+  <si>
+    <t>HH-3189</t>
+  </si>
+  <si>
+    <t>HH-3190</t>
+  </si>
+  <si>
+    <t>HH-3191</t>
+  </si>
+  <si>
+    <t>HH-3192</t>
+  </si>
+  <si>
+    <t>HH-3193</t>
+  </si>
+  <si>
+    <t>HH-3194</t>
+  </si>
+  <si>
+    <t>HH-3195</t>
+  </si>
+  <si>
+    <t>HH-3196</t>
+  </si>
+  <si>
+    <t>HH-3197</t>
+  </si>
+  <si>
+    <t>HH-3198</t>
+  </si>
+  <si>
+    <t>HH-3199</t>
+  </si>
+  <si>
+    <t>HH-3200</t>
   </si>
 </sst>
 </file>
@@ -6114,11 +6714,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -6414,7 +7015,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H2001"/>
+  <dimension ref="A1:H2201"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.85546875" style="2" customWidth="1"/>
@@ -58454,6 +59055,5206 @@
         <v>5</v>
       </c>
     </row>
+    <row r="2002" spans="1:8">
+      <c r="A2002" s="2" t="s">
+        <v>2018</v>
+      </c>
+      <c r="B2002" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2002" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2002" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2002" s="2">
+        <v>5572</v>
+      </c>
+      <c r="F2002" s="2">
+        <v>7</v>
+      </c>
+      <c r="G2002" s="2">
+        <v>13014</v>
+      </c>
+      <c r="H2002" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2003" spans="1:8">
+      <c r="A2003" s="3" t="s">
+        <v>2019</v>
+      </c>
+      <c r="B2003" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2003" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2003" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2003" s="3">
+        <v>8492</v>
+      </c>
+      <c r="F2003" s="3">
+        <v>7</v>
+      </c>
+      <c r="G2003" s="3">
+        <v>15321</v>
+      </c>
+      <c r="H2003" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2004" spans="1:8">
+      <c r="A2004" s="3" t="s">
+        <v>2020</v>
+      </c>
+      <c r="B2004" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2004" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2004" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2004" s="3">
+        <v>8490</v>
+      </c>
+      <c r="F2004" s="3">
+        <v>10</v>
+      </c>
+      <c r="G2004" s="3">
+        <v>18201</v>
+      </c>
+      <c r="H2004" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2005" spans="1:8">
+      <c r="A2005" s="3" t="s">
+        <v>2021</v>
+      </c>
+      <c r="B2005" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2005" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2005" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2005" s="3">
+        <v>8483</v>
+      </c>
+      <c r="F2005" s="3">
+        <v>0</v>
+      </c>
+      <c r="G2005" s="3">
+        <v>12194</v>
+      </c>
+      <c r="H2005" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2006" spans="1:8">
+      <c r="A2006" s="3" t="s">
+        <v>2022</v>
+      </c>
+      <c r="B2006" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2006" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2006" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2006" s="3">
+        <v>8458</v>
+      </c>
+      <c r="F2006" s="3">
+        <v>0</v>
+      </c>
+      <c r="G2006" s="3">
+        <v>10485</v>
+      </c>
+      <c r="H2006" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2007" spans="1:8">
+      <c r="A2007" s="3" t="s">
+        <v>2023</v>
+      </c>
+      <c r="B2007" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2007" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2007" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2007" s="3">
+        <v>8446</v>
+      </c>
+      <c r="F2007" s="3">
+        <v>9</v>
+      </c>
+      <c r="G2007" s="3">
+        <v>16694</v>
+      </c>
+      <c r="H2007" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2008" spans="1:8">
+      <c r="A2008" s="3" t="s">
+        <v>2024</v>
+      </c>
+      <c r="B2008" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2008" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2008" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2008" s="3">
+        <v>8435</v>
+      </c>
+      <c r="F2008" s="3">
+        <v>0</v>
+      </c>
+      <c r="G2008" s="3">
+        <v>10405</v>
+      </c>
+      <c r="H2008" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2009" spans="1:8">
+      <c r="A2009" s="3" t="s">
+        <v>2025</v>
+      </c>
+      <c r="B2009" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2009" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2009" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2009" s="3">
+        <v>8435</v>
+      </c>
+      <c r="F2009" s="3">
+        <v>6</v>
+      </c>
+      <c r="G2009" s="3">
+        <v>13565</v>
+      </c>
+      <c r="H2009" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2010" spans="1:8">
+      <c r="A2010" s="3" t="s">
+        <v>2026</v>
+      </c>
+      <c r="B2010" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2010" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2010" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2010" s="3">
+        <v>8433</v>
+      </c>
+      <c r="F2010" s="3">
+        <v>4</v>
+      </c>
+      <c r="G2010" s="3">
+        <v>13758</v>
+      </c>
+      <c r="H2010" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2011" spans="1:8">
+      <c r="A2011" s="3" t="s">
+        <v>2027</v>
+      </c>
+      <c r="B2011" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2011" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2011" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2011" s="3">
+        <v>8421</v>
+      </c>
+      <c r="F2011" s="3">
+        <v>9</v>
+      </c>
+      <c r="G2011" s="3">
+        <v>15482</v>
+      </c>
+      <c r="H2011" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2012" spans="1:8">
+      <c r="A2012" s="3" t="s">
+        <v>2028</v>
+      </c>
+      <c r="B2012" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2012" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2012" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2012" s="3">
+        <v>8406</v>
+      </c>
+      <c r="F2012" s="3">
+        <v>6</v>
+      </c>
+      <c r="G2012" s="3">
+        <v>14678</v>
+      </c>
+      <c r="H2012" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2013" spans="1:8">
+      <c r="A2013" s="3" t="s">
+        <v>2029</v>
+      </c>
+      <c r="B2013" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2013" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2013" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2013" s="3">
+        <v>8402</v>
+      </c>
+      <c r="F2013" s="3">
+        <v>5</v>
+      </c>
+      <c r="G2013" s="3">
+        <v>12681</v>
+      </c>
+      <c r="H2013" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2014" spans="1:8">
+      <c r="A2014" s="3" t="s">
+        <v>2030</v>
+      </c>
+      <c r="B2014" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2014" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2014" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2014" s="3">
+        <v>8402</v>
+      </c>
+      <c r="F2014" s="3">
+        <v>3</v>
+      </c>
+      <c r="G2014" s="3">
+        <v>12447</v>
+      </c>
+      <c r="H2014" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2015" spans="1:8">
+      <c r="A2015" s="3" t="s">
+        <v>2031</v>
+      </c>
+      <c r="B2015" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2015" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2015" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2015" s="3">
+        <v>8381</v>
+      </c>
+      <c r="F2015" s="3">
+        <v>9</v>
+      </c>
+      <c r="G2015" s="3">
+        <v>17045</v>
+      </c>
+      <c r="H2015" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2016" spans="1:8">
+      <c r="A2016" s="3" t="s">
+        <v>2032</v>
+      </c>
+      <c r="B2016" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2016" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2016" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2016" s="3">
+        <v>8372</v>
+      </c>
+      <c r="F2016" s="3">
+        <v>3</v>
+      </c>
+      <c r="G2016" s="3">
+        <v>11685</v>
+      </c>
+      <c r="H2016" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2017" spans="1:8">
+      <c r="A2017" s="3" t="s">
+        <v>2033</v>
+      </c>
+      <c r="B2017" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2017" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2017" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2017" s="3">
+        <v>8371</v>
+      </c>
+      <c r="F2017" s="3">
+        <v>7</v>
+      </c>
+      <c r="G2017" s="3">
+        <v>16523</v>
+      </c>
+      <c r="H2017" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2018" spans="1:8">
+      <c r="A2018" s="3" t="s">
+        <v>2034</v>
+      </c>
+      <c r="B2018" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2018" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2018" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2018" s="3">
+        <v>8366</v>
+      </c>
+      <c r="F2018" s="3">
+        <v>0</v>
+      </c>
+      <c r="G2018" s="3">
+        <v>10666</v>
+      </c>
+      <c r="H2018" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2019" spans="1:8">
+      <c r="A2019" s="3" t="s">
+        <v>2035</v>
+      </c>
+      <c r="B2019" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2019" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2019" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2019" s="3">
+        <v>8362</v>
+      </c>
+      <c r="F2019" s="3">
+        <v>10</v>
+      </c>
+      <c r="G2019" s="3">
+        <v>17901</v>
+      </c>
+      <c r="H2019" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2020" spans="1:8">
+      <c r="A2020" s="3" t="s">
+        <v>2036</v>
+      </c>
+      <c r="B2020" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2020" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2020" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2020" s="3">
+        <v>8354</v>
+      </c>
+      <c r="F2020" s="3">
+        <v>2</v>
+      </c>
+      <c r="G2020" s="3">
+        <v>13221</v>
+      </c>
+      <c r="H2020" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2021" spans="1:8">
+      <c r="A2021" s="3" t="s">
+        <v>2037</v>
+      </c>
+      <c r="B2021" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2021" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2021" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2021" s="3">
+        <v>8345</v>
+      </c>
+      <c r="F2021" s="3">
+        <v>4</v>
+      </c>
+      <c r="G2021" s="3">
+        <v>13774</v>
+      </c>
+      <c r="H2021" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2022" spans="1:8">
+      <c r="A2022" s="3" t="s">
+        <v>2038</v>
+      </c>
+      <c r="B2022" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2022" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2022" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2022" s="3">
+        <v>8320</v>
+      </c>
+      <c r="F2022" s="3">
+        <v>4</v>
+      </c>
+      <c r="G2022" s="3">
+        <v>12589</v>
+      </c>
+      <c r="H2022" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2023" spans="1:8">
+      <c r="A2023" s="3" t="s">
+        <v>2039</v>
+      </c>
+      <c r="B2023" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2023" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2023" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2023" s="3">
+        <v>8309</v>
+      </c>
+      <c r="F2023" s="3">
+        <v>10</v>
+      </c>
+      <c r="G2023" s="3">
+        <v>16361</v>
+      </c>
+      <c r="H2023" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2024" spans="1:8">
+      <c r="A2024" s="3" t="s">
+        <v>2040</v>
+      </c>
+      <c r="B2024" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2024" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2024" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2024" s="3">
+        <v>8302</v>
+      </c>
+      <c r="F2024" s="3">
+        <v>8</v>
+      </c>
+      <c r="G2024" s="3">
+        <v>16689</v>
+      </c>
+      <c r="H2024" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2025" spans="1:8">
+      <c r="A2025" s="3" t="s">
+        <v>2041</v>
+      </c>
+      <c r="B2025" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2025" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2025" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2025" s="3">
+        <v>8293</v>
+      </c>
+      <c r="F2025" s="3">
+        <v>5</v>
+      </c>
+      <c r="G2025" s="3">
+        <v>12740</v>
+      </c>
+      <c r="H2025" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2026" spans="1:8">
+      <c r="A2026" s="3" t="s">
+        <v>2042</v>
+      </c>
+      <c r="B2026" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2026" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2026" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2026" s="3">
+        <v>8293</v>
+      </c>
+      <c r="F2026" s="3">
+        <v>9</v>
+      </c>
+      <c r="G2026" s="3">
+        <v>15097</v>
+      </c>
+      <c r="H2026" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2027" spans="1:8">
+      <c r="A2027" s="3" t="s">
+        <v>2043</v>
+      </c>
+      <c r="B2027" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2027" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2027" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2027" s="3">
+        <v>8287</v>
+      </c>
+      <c r="F2027" s="3">
+        <v>1</v>
+      </c>
+      <c r="G2027" s="3">
+        <v>10634</v>
+      </c>
+      <c r="H2027" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2028" spans="1:8">
+      <c r="A2028" s="3" t="s">
+        <v>2044</v>
+      </c>
+      <c r="B2028" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2028" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2028" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2028" s="3">
+        <v>8272</v>
+      </c>
+      <c r="F2028" s="3">
+        <v>6</v>
+      </c>
+      <c r="G2028" s="3">
+        <v>13735</v>
+      </c>
+      <c r="H2028" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2029" spans="1:8">
+      <c r="A2029" s="3" t="s">
+        <v>2045</v>
+      </c>
+      <c r="B2029" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2029" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2029" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2029" s="3">
+        <v>8264</v>
+      </c>
+      <c r="F2029" s="3">
+        <v>6</v>
+      </c>
+      <c r="G2029" s="3">
+        <v>14845</v>
+      </c>
+      <c r="H2029" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2030" spans="1:8">
+      <c r="A2030" s="3" t="s">
+        <v>2046</v>
+      </c>
+      <c r="B2030" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2030" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2030" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2030" s="3">
+        <v>8235</v>
+      </c>
+      <c r="F2030" s="3">
+        <v>6</v>
+      </c>
+      <c r="G2030" s="3">
+        <v>14798</v>
+      </c>
+      <c r="H2030" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2031" spans="1:8">
+      <c r="A2031" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="B2031" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2031" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2031" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2031" s="3">
+        <v>8234</v>
+      </c>
+      <c r="F2031" s="3">
+        <v>1</v>
+      </c>
+      <c r="G2031" s="3">
+        <v>12603</v>
+      </c>
+      <c r="H2031" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2032" spans="1:8">
+      <c r="A2032" s="3" t="s">
+        <v>2048</v>
+      </c>
+      <c r="B2032" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2032" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2032" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2032" s="3">
+        <v>8232</v>
+      </c>
+      <c r="F2032" s="3">
+        <v>8</v>
+      </c>
+      <c r="G2032" s="3">
+        <v>15141</v>
+      </c>
+      <c r="H2032" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2033" spans="1:8">
+      <c r="A2033" s="3" t="s">
+        <v>2049</v>
+      </c>
+      <c r="B2033" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2033" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2033" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2033" s="3">
+        <v>8222</v>
+      </c>
+      <c r="F2033" s="3">
+        <v>3</v>
+      </c>
+      <c r="G2033" s="3">
+        <v>13853</v>
+      </c>
+      <c r="H2033" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2034" spans="1:8">
+      <c r="A2034" s="3" t="s">
+        <v>2050</v>
+      </c>
+      <c r="B2034" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2034" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2034" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2034" s="3">
+        <v>8198</v>
+      </c>
+      <c r="F2034" s="3">
+        <v>4</v>
+      </c>
+      <c r="G2034" s="3">
+        <v>13535</v>
+      </c>
+      <c r="H2034" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2035" spans="1:8">
+      <c r="A2035" s="3" t="s">
+        <v>2051</v>
+      </c>
+      <c r="B2035" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2035" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2035" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2035" s="3">
+        <v>8195</v>
+      </c>
+      <c r="F2035" s="3">
+        <v>6</v>
+      </c>
+      <c r="G2035" s="3">
+        <v>14408</v>
+      </c>
+      <c r="H2035" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2036" spans="1:8">
+      <c r="A2036" s="3" t="s">
+        <v>2052</v>
+      </c>
+      <c r="B2036" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2036" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2036" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2036" s="3">
+        <v>8175</v>
+      </c>
+      <c r="F2036" s="3">
+        <v>3</v>
+      </c>
+      <c r="G2036" s="3">
+        <v>10986</v>
+      </c>
+      <c r="H2036" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2037" spans="1:8">
+      <c r="A2037" s="3" t="s">
+        <v>2053</v>
+      </c>
+      <c r="B2037" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2037" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2037" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2037" s="3">
+        <v>8166</v>
+      </c>
+      <c r="F2037" s="3">
+        <v>9</v>
+      </c>
+      <c r="G2037" s="3">
+        <v>14657</v>
+      </c>
+      <c r="H2037" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2038" spans="1:8">
+      <c r="A2038" s="3" t="s">
+        <v>2054</v>
+      </c>
+      <c r="B2038" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2038" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2038" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2038" s="3">
+        <v>8163</v>
+      </c>
+      <c r="F2038" s="3">
+        <v>5</v>
+      </c>
+      <c r="G2038" s="3">
+        <v>13238</v>
+      </c>
+      <c r="H2038" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2039" spans="1:8">
+      <c r="A2039" s="3" t="s">
+        <v>2055</v>
+      </c>
+      <c r="B2039" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2039" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2039" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2039" s="3">
+        <v>8157</v>
+      </c>
+      <c r="F2039" s="3">
+        <v>0</v>
+      </c>
+      <c r="G2039" s="3">
+        <v>11274</v>
+      </c>
+      <c r="H2039" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2040" spans="1:8">
+      <c r="A2040" s="3" t="s">
+        <v>2056</v>
+      </c>
+      <c r="B2040" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2040" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2040" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2040" s="3">
+        <v>8137</v>
+      </c>
+      <c r="F2040" s="3">
+        <v>3</v>
+      </c>
+      <c r="G2040" s="3">
+        <v>12614</v>
+      </c>
+      <c r="H2040" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2041" spans="1:8">
+      <c r="A2041" s="3" t="s">
+        <v>2057</v>
+      </c>
+      <c r="B2041" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2041" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2041" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2041" s="3">
+        <v>8113</v>
+      </c>
+      <c r="F2041" s="3">
+        <v>6</v>
+      </c>
+      <c r="G2041" s="3">
+        <v>13256</v>
+      </c>
+      <c r="H2041" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2042" spans="1:8">
+      <c r="A2042" s="3" t="s">
+        <v>2058</v>
+      </c>
+      <c r="B2042" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2042" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2042" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2042" s="3">
+        <v>8076</v>
+      </c>
+      <c r="F2042" s="3">
+        <v>4</v>
+      </c>
+      <c r="G2042" s="3">
+        <v>11964</v>
+      </c>
+      <c r="H2042" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2043" spans="1:8">
+      <c r="A2043" s="3" t="s">
+        <v>2059</v>
+      </c>
+      <c r="B2043" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2043" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2043" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2043" s="3">
+        <v>8076</v>
+      </c>
+      <c r="F2043" s="3">
+        <v>6</v>
+      </c>
+      <c r="G2043" s="3">
+        <v>14750</v>
+      </c>
+      <c r="H2043" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2044" spans="1:8">
+      <c r="A2044" s="3" t="s">
+        <v>2060</v>
+      </c>
+      <c r="B2044" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2044" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2044" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2044" s="3">
+        <v>8071</v>
+      </c>
+      <c r="F2044" s="3">
+        <v>8</v>
+      </c>
+      <c r="G2044" s="3">
+        <v>16091</v>
+      </c>
+      <c r="H2044" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2045" spans="1:8">
+      <c r="A2045" s="3" t="s">
+        <v>2061</v>
+      </c>
+      <c r="B2045" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2045" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2045" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2045" s="3">
+        <v>8037</v>
+      </c>
+      <c r="F2045" s="3">
+        <v>5</v>
+      </c>
+      <c r="G2045" s="3">
+        <v>13601</v>
+      </c>
+      <c r="H2045" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2046" spans="1:8">
+      <c r="A2046" s="3" t="s">
+        <v>2062</v>
+      </c>
+      <c r="B2046" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2046" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2046" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2046" s="3">
+        <v>8032</v>
+      </c>
+      <c r="F2046" s="3">
+        <v>3</v>
+      </c>
+      <c r="G2046" s="3">
+        <v>11291</v>
+      </c>
+      <c r="H2046" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2047" spans="1:8">
+      <c r="A2047" s="3" t="s">
+        <v>2063</v>
+      </c>
+      <c r="B2047" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2047" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2047" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2047" s="3">
+        <v>8020</v>
+      </c>
+      <c r="F2047" s="3">
+        <v>3</v>
+      </c>
+      <c r="G2047" s="3">
+        <v>12899</v>
+      </c>
+      <c r="H2047" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2048" spans="1:8">
+      <c r="A2048" s="3" t="s">
+        <v>2064</v>
+      </c>
+      <c r="B2048" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2048" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2048" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2048" s="3">
+        <v>8009</v>
+      </c>
+      <c r="F2048" s="3">
+        <v>0</v>
+      </c>
+      <c r="G2048" s="3">
+        <v>9818</v>
+      </c>
+      <c r="H2048" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2049" spans="1:8">
+      <c r="A2049" s="3" t="s">
+        <v>2065</v>
+      </c>
+      <c r="B2049" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2049" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2049" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2049" s="3">
+        <v>7999</v>
+      </c>
+      <c r="F2049" s="3">
+        <v>1</v>
+      </c>
+      <c r="G2049" s="3">
+        <v>11219</v>
+      </c>
+      <c r="H2049" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2050" spans="1:8">
+      <c r="A2050" s="3" t="s">
+        <v>2066</v>
+      </c>
+      <c r="B2050" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2050" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2050" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2050" s="3">
+        <v>7985</v>
+      </c>
+      <c r="F2050" s="3">
+        <v>0</v>
+      </c>
+      <c r="G2050" s="3">
+        <v>10174</v>
+      </c>
+      <c r="H2050" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2051" spans="1:8">
+      <c r="A2051" s="3" t="s">
+        <v>2067</v>
+      </c>
+      <c r="B2051" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2051" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2051" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2051" s="3">
+        <v>7973</v>
+      </c>
+      <c r="F2051" s="3">
+        <v>3</v>
+      </c>
+      <c r="G2051" s="3">
+        <v>13398</v>
+      </c>
+      <c r="H2051" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2052" spans="1:8">
+      <c r="A2052" s="3" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B2052" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2052" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2052" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2052" s="3">
+        <v>7969</v>
+      </c>
+      <c r="F2052" s="3">
+        <v>10</v>
+      </c>
+      <c r="G2052" s="3">
+        <v>16532</v>
+      </c>
+      <c r="H2052" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2053" spans="1:8">
+      <c r="A2053" s="3" t="s">
+        <v>2069</v>
+      </c>
+      <c r="B2053" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2053" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2053" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2053" s="3">
+        <v>7969</v>
+      </c>
+      <c r="F2053" s="3">
+        <v>10</v>
+      </c>
+      <c r="G2053" s="3">
+        <v>16713</v>
+      </c>
+      <c r="H2053" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2054" spans="1:8">
+      <c r="A2054" s="3" t="s">
+        <v>2070</v>
+      </c>
+      <c r="B2054" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2054" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2054" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2054" s="3">
+        <v>7961</v>
+      </c>
+      <c r="F2054" s="3">
+        <v>9</v>
+      </c>
+      <c r="G2054" s="3">
+        <v>16543</v>
+      </c>
+      <c r="H2054" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2055" spans="1:8">
+      <c r="A2055" s="3" t="s">
+        <v>2071</v>
+      </c>
+      <c r="B2055" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2055" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2055" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2055" s="3">
+        <v>7951</v>
+      </c>
+      <c r="F2055" s="3">
+        <v>8</v>
+      </c>
+      <c r="G2055" s="3">
+        <v>15397</v>
+      </c>
+      <c r="H2055" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2056" spans="1:8">
+      <c r="A2056" s="3" t="s">
+        <v>2072</v>
+      </c>
+      <c r="B2056" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2056" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2056" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2056" s="3">
+        <v>7945</v>
+      </c>
+      <c r="F2056" s="3">
+        <v>5</v>
+      </c>
+      <c r="G2056" s="3">
+        <v>13552</v>
+      </c>
+      <c r="H2056" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2057" spans="1:8">
+      <c r="A2057" s="3" t="s">
+        <v>2073</v>
+      </c>
+      <c r="B2057" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2057" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2057" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2057" s="3">
+        <v>7932</v>
+      </c>
+      <c r="F2057" s="3">
+        <v>6</v>
+      </c>
+      <c r="G2057" s="3">
+        <v>14477</v>
+      </c>
+      <c r="H2057" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2058" spans="1:8">
+      <c r="A2058" s="3" t="s">
+        <v>2074</v>
+      </c>
+      <c r="B2058" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2058" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2058" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2058" s="3">
+        <v>7906</v>
+      </c>
+      <c r="F2058" s="3">
+        <v>5</v>
+      </c>
+      <c r="G2058" s="3">
+        <v>12650</v>
+      </c>
+      <c r="H2058" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2059" spans="1:8">
+      <c r="A2059" s="3" t="s">
+        <v>2075</v>
+      </c>
+      <c r="B2059" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2059" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2059" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2059" s="3">
+        <v>7883</v>
+      </c>
+      <c r="F2059" s="3">
+        <v>9</v>
+      </c>
+      <c r="G2059" s="3">
+        <v>15914</v>
+      </c>
+      <c r="H2059" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2060" spans="1:8">
+      <c r="A2060" s="3" t="s">
+        <v>2076</v>
+      </c>
+      <c r="B2060" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2060" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2060" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2060" s="3">
+        <v>7875</v>
+      </c>
+      <c r="F2060" s="3">
+        <v>1</v>
+      </c>
+      <c r="G2060" s="3">
+        <v>10748</v>
+      </c>
+      <c r="H2060" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2061" spans="1:8">
+      <c r="A2061" s="3" t="s">
+        <v>2077</v>
+      </c>
+      <c r="B2061" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2061" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2061" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2061" s="3">
+        <v>7865</v>
+      </c>
+      <c r="F2061" s="3">
+        <v>1</v>
+      </c>
+      <c r="G2061" s="3">
+        <v>11823</v>
+      </c>
+      <c r="H2061" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2062" spans="1:8">
+      <c r="A2062" s="3" t="s">
+        <v>2078</v>
+      </c>
+      <c r="B2062" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2062" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2062" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2062" s="3">
+        <v>7863</v>
+      </c>
+      <c r="F2062" s="3">
+        <v>10</v>
+      </c>
+      <c r="G2062" s="3">
+        <v>15643</v>
+      </c>
+      <c r="H2062" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2063" spans="1:8">
+      <c r="A2063" s="3" t="s">
+        <v>2079</v>
+      </c>
+      <c r="B2063" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2063" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2063" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2063" s="3">
+        <v>7832</v>
+      </c>
+      <c r="F2063" s="3">
+        <v>8</v>
+      </c>
+      <c r="G2063" s="3">
+        <v>14637</v>
+      </c>
+      <c r="H2063" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2064" spans="1:8">
+      <c r="A2064" s="3" t="s">
+        <v>2080</v>
+      </c>
+      <c r="B2064" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2064" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2064" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2064" s="3">
+        <v>7815</v>
+      </c>
+      <c r="F2064" s="3">
+        <v>9</v>
+      </c>
+      <c r="G2064" s="3">
+        <v>15298</v>
+      </c>
+      <c r="H2064" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2065" spans="1:8">
+      <c r="A2065" s="3" t="s">
+        <v>2081</v>
+      </c>
+      <c r="B2065" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2065" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2065" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2065" s="3">
+        <v>7814</v>
+      </c>
+      <c r="F2065" s="3">
+        <v>6</v>
+      </c>
+      <c r="G2065" s="3">
+        <v>15158</v>
+      </c>
+      <c r="H2065" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2066" spans="1:8">
+      <c r="A2066" s="3" t="s">
+        <v>2082</v>
+      </c>
+      <c r="B2066" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2066" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2066" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2066" s="3">
+        <v>7786</v>
+      </c>
+      <c r="F2066" s="3">
+        <v>3</v>
+      </c>
+      <c r="G2066" s="3">
+        <v>13483</v>
+      </c>
+      <c r="H2066" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2067" spans="1:8">
+      <c r="A2067" s="3" t="s">
+        <v>2083</v>
+      </c>
+      <c r="B2067" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2067" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2067" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2067" s="3">
+        <v>7783</v>
+      </c>
+      <c r="F2067" s="3">
+        <v>6</v>
+      </c>
+      <c r="G2067" s="3">
+        <v>14058</v>
+      </c>
+      <c r="H2067" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2068" spans="1:8">
+      <c r="A2068" s="3" t="s">
+        <v>2084</v>
+      </c>
+      <c r="B2068" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2068" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2068" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2068" s="3">
+        <v>7764</v>
+      </c>
+      <c r="F2068" s="3">
+        <v>2</v>
+      </c>
+      <c r="G2068" s="3">
+        <v>11901</v>
+      </c>
+      <c r="H2068" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2069" spans="1:8">
+      <c r="A2069" s="3" t="s">
+        <v>2085</v>
+      </c>
+      <c r="B2069" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2069" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2069" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2069" s="3">
+        <v>7740</v>
+      </c>
+      <c r="F2069" s="3">
+        <v>6</v>
+      </c>
+      <c r="G2069" s="3">
+        <v>12945</v>
+      </c>
+      <c r="H2069" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2070" spans="1:8">
+      <c r="A2070" s="3" t="s">
+        <v>2086</v>
+      </c>
+      <c r="B2070" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2070" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2070" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2070" s="3">
+        <v>7737</v>
+      </c>
+      <c r="F2070" s="3">
+        <v>1</v>
+      </c>
+      <c r="G2070" s="3">
+        <v>12057</v>
+      </c>
+      <c r="H2070" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2071" spans="1:8">
+      <c r="A2071" s="3" t="s">
+        <v>2087</v>
+      </c>
+      <c r="B2071" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2071" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2071" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2071" s="3">
+        <v>7734</v>
+      </c>
+      <c r="F2071" s="3">
+        <v>9</v>
+      </c>
+      <c r="G2071" s="3">
+        <v>14725</v>
+      </c>
+      <c r="H2071" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2072" spans="1:8">
+      <c r="A2072" s="3" t="s">
+        <v>2088</v>
+      </c>
+      <c r="B2072" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2072" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2072" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2072" s="3">
+        <v>7720</v>
+      </c>
+      <c r="F2072" s="3">
+        <v>6</v>
+      </c>
+      <c r="G2072" s="3">
+        <v>15259</v>
+      </c>
+      <c r="H2072" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2073" spans="1:8">
+      <c r="A2073" s="3" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B2073" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2073" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2073" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2073" s="3">
+        <v>7718</v>
+      </c>
+      <c r="F2073" s="3">
+        <v>9</v>
+      </c>
+      <c r="G2073" s="3">
+        <v>14228</v>
+      </c>
+      <c r="H2073" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2074" spans="1:8">
+      <c r="A2074" s="3" t="s">
+        <v>2090</v>
+      </c>
+      <c r="B2074" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2074" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2074" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2074" s="3">
+        <v>7696</v>
+      </c>
+      <c r="F2074" s="3">
+        <v>4</v>
+      </c>
+      <c r="G2074" s="3">
+        <v>12663</v>
+      </c>
+      <c r="H2074" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2075" spans="1:8">
+      <c r="A2075" s="3" t="s">
+        <v>2091</v>
+      </c>
+      <c r="B2075" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2075" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2075" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2075" s="3">
+        <v>7688</v>
+      </c>
+      <c r="F2075" s="3">
+        <v>5</v>
+      </c>
+      <c r="G2075" s="3">
+        <v>11761</v>
+      </c>
+      <c r="H2075" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2076" spans="1:8">
+      <c r="A2076" s="3" t="s">
+        <v>2092</v>
+      </c>
+      <c r="B2076" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2076" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2076" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2076" s="3">
+        <v>7675</v>
+      </c>
+      <c r="F2076" s="3">
+        <v>6</v>
+      </c>
+      <c r="G2076" s="3">
+        <v>14977</v>
+      </c>
+      <c r="H2076" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2077" spans="1:8">
+      <c r="A2077" s="3" t="s">
+        <v>2093</v>
+      </c>
+      <c r="B2077" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2077" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2077" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2077" s="3">
+        <v>7673</v>
+      </c>
+      <c r="F2077" s="3">
+        <v>3</v>
+      </c>
+      <c r="G2077" s="3">
+        <v>12352</v>
+      </c>
+      <c r="H2077" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2078" spans="1:8">
+      <c r="A2078" s="3" t="s">
+        <v>2094</v>
+      </c>
+      <c r="B2078" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2078" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2078" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2078" s="3">
+        <v>7672</v>
+      </c>
+      <c r="F2078" s="3">
+        <v>0</v>
+      </c>
+      <c r="G2078" s="3">
+        <v>10057</v>
+      </c>
+      <c r="H2078" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2079" spans="1:8">
+      <c r="A2079" s="3" t="s">
+        <v>2095</v>
+      </c>
+      <c r="B2079" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2079" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2079" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2079" s="3">
+        <v>7670</v>
+      </c>
+      <c r="F2079" s="3">
+        <v>2</v>
+      </c>
+      <c r="G2079" s="3">
+        <v>10857</v>
+      </c>
+      <c r="H2079" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2080" spans="1:8">
+      <c r="A2080" s="3" t="s">
+        <v>2096</v>
+      </c>
+      <c r="B2080" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2080" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2080" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2080" s="3">
+        <v>7664</v>
+      </c>
+      <c r="F2080" s="3">
+        <v>5</v>
+      </c>
+      <c r="G2080" s="3">
+        <v>13542</v>
+      </c>
+      <c r="H2080" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2081" spans="1:8">
+      <c r="A2081" s="3" t="s">
+        <v>2097</v>
+      </c>
+      <c r="B2081" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2081" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2081" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2081" s="3">
+        <v>7634</v>
+      </c>
+      <c r="F2081" s="3">
+        <v>9</v>
+      </c>
+      <c r="G2081" s="3">
+        <v>15995</v>
+      </c>
+      <c r="H2081" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2082" spans="1:8">
+      <c r="A2082" s="3" t="s">
+        <v>2098</v>
+      </c>
+      <c r="B2082" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2082" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2082" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2082" s="3">
+        <v>7597</v>
+      </c>
+      <c r="F2082" s="3">
+        <v>1</v>
+      </c>
+      <c r="G2082" s="3">
+        <v>10593</v>
+      </c>
+      <c r="H2082" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2083" spans="1:8">
+      <c r="A2083" s="3" t="s">
+        <v>2099</v>
+      </c>
+      <c r="B2083" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2083" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2083" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2083" s="3">
+        <v>7566</v>
+      </c>
+      <c r="F2083" s="3">
+        <v>7</v>
+      </c>
+      <c r="G2083" s="3">
+        <v>14833</v>
+      </c>
+      <c r="H2083" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2084" spans="1:8">
+      <c r="A2084" s="3" t="s">
+        <v>2100</v>
+      </c>
+      <c r="B2084" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2084" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2084" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2084" s="3">
+        <v>7548</v>
+      </c>
+      <c r="F2084" s="3">
+        <v>4</v>
+      </c>
+      <c r="G2084" s="3">
+        <v>13697</v>
+      </c>
+      <c r="H2084" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2085" spans="1:8">
+      <c r="A2085" s="3" t="s">
+        <v>2101</v>
+      </c>
+      <c r="B2085" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2085" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2085" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2085" s="3">
+        <v>7538</v>
+      </c>
+      <c r="F2085" s="3">
+        <v>6</v>
+      </c>
+      <c r="G2085" s="3">
+        <v>14336</v>
+      </c>
+      <c r="H2085" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2086" spans="1:8">
+      <c r="A2086" s="3" t="s">
+        <v>2102</v>
+      </c>
+      <c r="B2086" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2086" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2086" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2086" s="3">
+        <v>7531</v>
+      </c>
+      <c r="F2086" s="3">
+        <v>1</v>
+      </c>
+      <c r="G2086" s="3">
+        <v>10480</v>
+      </c>
+      <c r="H2086" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2087" spans="1:8">
+      <c r="A2087" s="3" t="s">
+        <v>2103</v>
+      </c>
+      <c r="B2087" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2087" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2087" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2087" s="3">
+        <v>7523</v>
+      </c>
+      <c r="F2087" s="3">
+        <v>5</v>
+      </c>
+      <c r="G2087" s="3">
+        <v>13409</v>
+      </c>
+      <c r="H2087" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2088" spans="1:8">
+      <c r="A2088" s="3" t="s">
+        <v>2104</v>
+      </c>
+      <c r="B2088" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2088" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2088" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2088" s="3">
+        <v>7518</v>
+      </c>
+      <c r="F2088" s="3">
+        <v>8</v>
+      </c>
+      <c r="G2088" s="3">
+        <v>14258</v>
+      </c>
+      <c r="H2088" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2089" spans="1:8">
+      <c r="A2089" s="3" t="s">
+        <v>2105</v>
+      </c>
+      <c r="B2089" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2089" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2089" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2089" s="3">
+        <v>7516</v>
+      </c>
+      <c r="F2089" s="3">
+        <v>0</v>
+      </c>
+      <c r="G2089" s="3">
+        <v>11262</v>
+      </c>
+      <c r="H2089" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2090" spans="1:8">
+      <c r="A2090" s="3" t="s">
+        <v>2106</v>
+      </c>
+      <c r="B2090" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2090" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2090" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2090" s="3">
+        <v>7515</v>
+      </c>
+      <c r="F2090" s="3">
+        <v>9</v>
+      </c>
+      <c r="G2090" s="3">
+        <v>15312</v>
+      </c>
+      <c r="H2090" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2091" spans="1:8">
+      <c r="A2091" s="3" t="s">
+        <v>2107</v>
+      </c>
+      <c r="B2091" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2091" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2091" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2091" s="3">
+        <v>7513</v>
+      </c>
+      <c r="F2091" s="3">
+        <v>9</v>
+      </c>
+      <c r="G2091" s="3">
+        <v>14532</v>
+      </c>
+      <c r="H2091" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2092" spans="1:8">
+      <c r="A2092" s="3" t="s">
+        <v>2108</v>
+      </c>
+      <c r="B2092" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2092" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2092" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2092" s="3">
+        <v>7491</v>
+      </c>
+      <c r="F2092" s="3">
+        <v>6</v>
+      </c>
+      <c r="G2092" s="3">
+        <v>14143</v>
+      </c>
+      <c r="H2092" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2093" spans="1:8">
+      <c r="A2093" s="3" t="s">
+        <v>2109</v>
+      </c>
+      <c r="B2093" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2093" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2093" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2093" s="3">
+        <v>7491</v>
+      </c>
+      <c r="F2093" s="3">
+        <v>3</v>
+      </c>
+      <c r="G2093" s="3">
+        <v>11816</v>
+      </c>
+      <c r="H2093" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2094" spans="1:8">
+      <c r="A2094" s="3" t="s">
+        <v>2110</v>
+      </c>
+      <c r="B2094" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2094" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2094" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2094" s="3">
+        <v>7428</v>
+      </c>
+      <c r="F2094" s="3">
+        <v>8</v>
+      </c>
+      <c r="G2094" s="3">
+        <v>14820</v>
+      </c>
+      <c r="H2094" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2095" spans="1:8">
+      <c r="A2095" s="3" t="s">
+        <v>2111</v>
+      </c>
+      <c r="B2095" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2095" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2095" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2095" s="3">
+        <v>7408</v>
+      </c>
+      <c r="F2095" s="3">
+        <v>10</v>
+      </c>
+      <c r="G2095" s="3">
+        <v>15029</v>
+      </c>
+      <c r="H2095" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2096" spans="1:8">
+      <c r="A2096" s="3" t="s">
+        <v>2112</v>
+      </c>
+      <c r="B2096" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2096" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2096" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2096" s="3">
+        <v>7382</v>
+      </c>
+      <c r="F2096" s="3">
+        <v>8</v>
+      </c>
+      <c r="G2096" s="3">
+        <v>14361</v>
+      </c>
+      <c r="H2096" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2097" spans="1:8">
+      <c r="A2097" s="3" t="s">
+        <v>2113</v>
+      </c>
+      <c r="B2097" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2097" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2097" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2097" s="3">
+        <v>7373</v>
+      </c>
+      <c r="F2097" s="3">
+        <v>9</v>
+      </c>
+      <c r="G2097" s="3">
+        <v>16155</v>
+      </c>
+      <c r="H2097" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2098" spans="1:8">
+      <c r="A2098" s="3" t="s">
+        <v>2114</v>
+      </c>
+      <c r="B2098" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2098" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2098" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2098" s="3">
+        <v>7368</v>
+      </c>
+      <c r="F2098" s="3">
+        <v>8</v>
+      </c>
+      <c r="G2098" s="3">
+        <v>14704</v>
+      </c>
+      <c r="H2098" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2099" spans="1:8">
+      <c r="A2099" s="3" t="s">
+        <v>2115</v>
+      </c>
+      <c r="B2099" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2099" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2099" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2099" s="3">
+        <v>7361</v>
+      </c>
+      <c r="F2099" s="3">
+        <v>10</v>
+      </c>
+      <c r="G2099" s="3">
+        <v>15920</v>
+      </c>
+      <c r="H2099" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2100" spans="1:8">
+      <c r="A2100" s="3" t="s">
+        <v>2116</v>
+      </c>
+      <c r="B2100" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2100" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2100" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2100" s="3">
+        <v>7342</v>
+      </c>
+      <c r="F2100" s="3">
+        <v>10</v>
+      </c>
+      <c r="G2100" s="3">
+        <v>16753</v>
+      </c>
+      <c r="H2100" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2101" spans="1:8">
+      <c r="A2101" s="3" t="s">
+        <v>2117</v>
+      </c>
+      <c r="B2101" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2101" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2101" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2101" s="3">
+        <v>7326</v>
+      </c>
+      <c r="F2101" s="3">
+        <v>1</v>
+      </c>
+      <c r="G2101" s="3">
+        <v>11346</v>
+      </c>
+      <c r="H2101" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2102" spans="1:8">
+      <c r="A2102" s="3" t="s">
+        <v>2118</v>
+      </c>
+      <c r="B2102" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2102" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2102" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2102" s="3">
+        <v>7324</v>
+      </c>
+      <c r="F2102" s="3">
+        <v>4</v>
+      </c>
+      <c r="G2102" s="3">
+        <v>11302</v>
+      </c>
+      <c r="H2102" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2103" spans="1:8">
+      <c r="A2103" s="3" t="s">
+        <v>2119</v>
+      </c>
+      <c r="B2103" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2103" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2103" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2103" s="3">
+        <v>7308</v>
+      </c>
+      <c r="F2103" s="3">
+        <v>5</v>
+      </c>
+      <c r="G2103" s="3">
+        <v>12968</v>
+      </c>
+      <c r="H2103" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2104" spans="1:8">
+      <c r="A2104" s="3" t="s">
+        <v>2120</v>
+      </c>
+      <c r="B2104" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2104" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2104" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2104" s="3">
+        <v>7293</v>
+      </c>
+      <c r="F2104" s="3">
+        <v>1</v>
+      </c>
+      <c r="G2104" s="3">
+        <v>10293</v>
+      </c>
+      <c r="H2104" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2105" spans="1:8">
+      <c r="A2105" s="3" t="s">
+        <v>2121</v>
+      </c>
+      <c r="B2105" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2105" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2105" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2105" s="3">
+        <v>7291</v>
+      </c>
+      <c r="F2105" s="3">
+        <v>1</v>
+      </c>
+      <c r="G2105" s="3">
+        <v>9587</v>
+      </c>
+      <c r="H2105" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2106" spans="1:8">
+      <c r="A2106" s="3" t="s">
+        <v>2122</v>
+      </c>
+      <c r="B2106" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2106" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2106" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2106" s="3">
+        <v>7287</v>
+      </c>
+      <c r="F2106" s="3">
+        <v>0</v>
+      </c>
+      <c r="G2106" s="3">
+        <v>9870</v>
+      </c>
+      <c r="H2106" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2107" spans="1:8">
+      <c r="A2107" s="3" t="s">
+        <v>2123</v>
+      </c>
+      <c r="B2107" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2107" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2107" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2107" s="3">
+        <v>7284</v>
+      </c>
+      <c r="F2107" s="3">
+        <v>7</v>
+      </c>
+      <c r="G2107" s="3">
+        <v>14740</v>
+      </c>
+      <c r="H2107" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2108" spans="1:8">
+      <c r="A2108" s="3" t="s">
+        <v>2124</v>
+      </c>
+      <c r="B2108" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2108" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2108" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2108" s="3">
+        <v>7263</v>
+      </c>
+      <c r="F2108" s="3">
+        <v>2</v>
+      </c>
+      <c r="G2108" s="3">
+        <v>12408</v>
+      </c>
+      <c r="H2108" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2109" spans="1:8">
+      <c r="A2109" s="3" t="s">
+        <v>2125</v>
+      </c>
+      <c r="B2109" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2109" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2109" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2109" s="3">
+        <v>7253</v>
+      </c>
+      <c r="F2109" s="3">
+        <v>4</v>
+      </c>
+      <c r="G2109" s="3">
+        <v>13319</v>
+      </c>
+      <c r="H2109" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2110" spans="1:8">
+      <c r="A2110" s="3" t="s">
+        <v>2126</v>
+      </c>
+      <c r="B2110" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2110" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2110" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2110" s="3">
+        <v>7247</v>
+      </c>
+      <c r="F2110" s="3">
+        <v>9</v>
+      </c>
+      <c r="G2110" s="3">
+        <v>14680</v>
+      </c>
+      <c r="H2110" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2111" spans="1:8">
+      <c r="A2111" s="3" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B2111" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2111" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2111" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2111" s="3">
+        <v>7201</v>
+      </c>
+      <c r="F2111" s="3">
+        <v>9</v>
+      </c>
+      <c r="G2111" s="3">
+        <v>15772</v>
+      </c>
+      <c r="H2111" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2112" spans="1:8">
+      <c r="A2112" s="3" t="s">
+        <v>2128</v>
+      </c>
+      <c r="B2112" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2112" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2112" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2112" s="3">
+        <v>7192</v>
+      </c>
+      <c r="F2112" s="3">
+        <v>10</v>
+      </c>
+      <c r="G2112" s="3">
+        <v>14600</v>
+      </c>
+      <c r="H2112" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2113" spans="1:8">
+      <c r="A2113" s="3" t="s">
+        <v>2129</v>
+      </c>
+      <c r="B2113" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2113" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2113" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2113" s="3">
+        <v>7185</v>
+      </c>
+      <c r="F2113" s="3">
+        <v>6</v>
+      </c>
+      <c r="G2113" s="3">
+        <v>11880</v>
+      </c>
+      <c r="H2113" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2114" spans="1:8">
+      <c r="A2114" s="3" t="s">
+        <v>2130</v>
+      </c>
+      <c r="B2114" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2114" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2114" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2114" s="3">
+        <v>7142</v>
+      </c>
+      <c r="F2114" s="3">
+        <v>9</v>
+      </c>
+      <c r="G2114" s="3">
+        <v>16522</v>
+      </c>
+      <c r="H2114" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2115" spans="1:8">
+      <c r="A2115" s="3" t="s">
+        <v>2131</v>
+      </c>
+      <c r="B2115" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2115" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2115" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2115" s="3">
+        <v>7083</v>
+      </c>
+      <c r="F2115" s="3">
+        <v>10</v>
+      </c>
+      <c r="G2115" s="3">
+        <v>15829</v>
+      </c>
+      <c r="H2115" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2116" spans="1:8">
+      <c r="A2116" s="3" t="s">
+        <v>2132</v>
+      </c>
+      <c r="B2116" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2116" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2116" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2116" s="3">
+        <v>7083</v>
+      </c>
+      <c r="F2116" s="3">
+        <v>7</v>
+      </c>
+      <c r="G2116" s="3">
+        <v>15051</v>
+      </c>
+      <c r="H2116" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2117" spans="1:8">
+      <c r="A2117" s="3" t="s">
+        <v>2133</v>
+      </c>
+      <c r="B2117" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2117" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2117" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2117" s="3">
+        <v>7083</v>
+      </c>
+      <c r="F2117" s="3">
+        <v>1</v>
+      </c>
+      <c r="G2117" s="3">
+        <v>8816</v>
+      </c>
+      <c r="H2117" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2118" spans="1:8">
+      <c r="A2118" s="3" t="s">
+        <v>2134</v>
+      </c>
+      <c r="B2118" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2118" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2118" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2118" s="3">
+        <v>7078</v>
+      </c>
+      <c r="F2118" s="3">
+        <v>7</v>
+      </c>
+      <c r="G2118" s="3">
+        <v>12410</v>
+      </c>
+      <c r="H2118" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2119" spans="1:8">
+      <c r="A2119" s="3" t="s">
+        <v>2135</v>
+      </c>
+      <c r="B2119" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2119" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2119" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2119" s="3">
+        <v>7075</v>
+      </c>
+      <c r="F2119" s="3">
+        <v>8</v>
+      </c>
+      <c r="G2119" s="3">
+        <v>13210</v>
+      </c>
+      <c r="H2119" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2120" spans="1:8">
+      <c r="A2120" s="3" t="s">
+        <v>2136</v>
+      </c>
+      <c r="B2120" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2120" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2120" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2120" s="3">
+        <v>7066</v>
+      </c>
+      <c r="F2120" s="3">
+        <v>8</v>
+      </c>
+      <c r="G2120" s="3">
+        <v>14348</v>
+      </c>
+      <c r="H2120" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2121" spans="1:8">
+      <c r="A2121" s="3" t="s">
+        <v>2137</v>
+      </c>
+      <c r="B2121" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2121" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2121" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2121" s="3">
+        <v>7062</v>
+      </c>
+      <c r="F2121" s="3">
+        <v>9</v>
+      </c>
+      <c r="G2121" s="3">
+        <v>16199</v>
+      </c>
+      <c r="H2121" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2122" spans="1:8">
+      <c r="A2122" s="3" t="s">
+        <v>2138</v>
+      </c>
+      <c r="B2122" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2122" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2122" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2122" s="3">
+        <v>7057</v>
+      </c>
+      <c r="F2122" s="3">
+        <v>4</v>
+      </c>
+      <c r="G2122" s="3">
+        <v>12669</v>
+      </c>
+      <c r="H2122" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2123" spans="1:8">
+      <c r="A2123" s="3" t="s">
+        <v>2139</v>
+      </c>
+      <c r="B2123" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2123" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2123" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2123" s="3">
+        <v>7052</v>
+      </c>
+      <c r="F2123" s="3">
+        <v>4</v>
+      </c>
+      <c r="G2123" s="3">
+        <v>11401</v>
+      </c>
+      <c r="H2123" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2124" spans="1:8">
+      <c r="A2124" s="3" t="s">
+        <v>2140</v>
+      </c>
+      <c r="B2124" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2124" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2124" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2124" s="3">
+        <v>7047</v>
+      </c>
+      <c r="F2124" s="3">
+        <v>7</v>
+      </c>
+      <c r="G2124" s="3">
+        <v>13716</v>
+      </c>
+      <c r="H2124" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2125" spans="1:8">
+      <c r="A2125" s="3" t="s">
+        <v>2141</v>
+      </c>
+      <c r="B2125" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2125" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2125" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2125" s="3">
+        <v>7010</v>
+      </c>
+      <c r="F2125" s="3">
+        <v>0</v>
+      </c>
+      <c r="G2125" s="3">
+        <v>8313</v>
+      </c>
+      <c r="H2125" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2126" spans="1:8">
+      <c r="A2126" s="3" t="s">
+        <v>2142</v>
+      </c>
+      <c r="B2126" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2126" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2126" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2126" s="3">
+        <v>6985</v>
+      </c>
+      <c r="F2126" s="3">
+        <v>9</v>
+      </c>
+      <c r="G2126" s="3">
+        <v>14590</v>
+      </c>
+      <c r="H2126" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2127" spans="1:8">
+      <c r="A2127" s="3" t="s">
+        <v>2143</v>
+      </c>
+      <c r="B2127" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2127" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2127" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2127" s="3">
+        <v>6971</v>
+      </c>
+      <c r="F2127" s="3">
+        <v>2</v>
+      </c>
+      <c r="G2127" s="3">
+        <v>10648</v>
+      </c>
+      <c r="H2127" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2128" spans="1:8">
+      <c r="A2128" s="3" t="s">
+        <v>2144</v>
+      </c>
+      <c r="B2128" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2128" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2128" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2128" s="3">
+        <v>6962</v>
+      </c>
+      <c r="F2128" s="3">
+        <v>9</v>
+      </c>
+      <c r="G2128" s="3">
+        <v>14062</v>
+      </c>
+      <c r="H2128" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2129" spans="1:8">
+      <c r="A2129" s="3" t="s">
+        <v>2145</v>
+      </c>
+      <c r="B2129" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2129" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2129" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2129" s="3">
+        <v>6956</v>
+      </c>
+      <c r="F2129" s="3">
+        <v>6</v>
+      </c>
+      <c r="G2129" s="3">
+        <v>12278</v>
+      </c>
+      <c r="H2129" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2130" spans="1:8">
+      <c r="A2130" s="3" t="s">
+        <v>2146</v>
+      </c>
+      <c r="B2130" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2130" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2130" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2130" s="3">
+        <v>6939</v>
+      </c>
+      <c r="F2130" s="3">
+        <v>5</v>
+      </c>
+      <c r="G2130" s="3">
+        <v>12450</v>
+      </c>
+      <c r="H2130" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2131" spans="1:8">
+      <c r="A2131" s="3" t="s">
+        <v>2147</v>
+      </c>
+      <c r="B2131" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2131" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2131" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2131" s="3">
+        <v>6933</v>
+      </c>
+      <c r="F2131" s="3">
+        <v>8</v>
+      </c>
+      <c r="G2131" s="3">
+        <v>13292</v>
+      </c>
+      <c r="H2131" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2132" spans="1:8">
+      <c r="A2132" s="3" t="s">
+        <v>2148</v>
+      </c>
+      <c r="B2132" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2132" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2132" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2132" s="3">
+        <v>6916</v>
+      </c>
+      <c r="F2132" s="3">
+        <v>1</v>
+      </c>
+      <c r="G2132" s="3">
+        <v>11260</v>
+      </c>
+      <c r="H2132" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2133" spans="1:8">
+      <c r="A2133" s="3" t="s">
+        <v>2149</v>
+      </c>
+      <c r="B2133" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2133" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2133" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2133" s="3">
+        <v>6880</v>
+      </c>
+      <c r="F2133" s="3">
+        <v>6</v>
+      </c>
+      <c r="G2133" s="3">
+        <v>12463</v>
+      </c>
+      <c r="H2133" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2134" spans="1:8">
+      <c r="A2134" s="3" t="s">
+        <v>2150</v>
+      </c>
+      <c r="B2134" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2134" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2134" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2134" s="3">
+        <v>6869</v>
+      </c>
+      <c r="F2134" s="3">
+        <v>7</v>
+      </c>
+      <c r="G2134" s="3">
+        <v>14284</v>
+      </c>
+      <c r="H2134" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2135" spans="1:8">
+      <c r="A2135" s="3" t="s">
+        <v>2151</v>
+      </c>
+      <c r="B2135" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2135" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2135" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2135" s="3">
+        <v>6868</v>
+      </c>
+      <c r="F2135" s="3">
+        <v>1</v>
+      </c>
+      <c r="G2135" s="3">
+        <v>10576</v>
+      </c>
+      <c r="H2135" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2136" spans="1:8">
+      <c r="A2136" s="3" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B2136" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2136" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2136" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2136" s="3">
+        <v>6860</v>
+      </c>
+      <c r="F2136" s="3">
+        <v>8</v>
+      </c>
+      <c r="G2136" s="3">
+        <v>13729</v>
+      </c>
+      <c r="H2136" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2137" spans="1:8">
+      <c r="A2137" s="3" t="s">
+        <v>2153</v>
+      </c>
+      <c r="B2137" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2137" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2137" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2137" s="3">
+        <v>6857</v>
+      </c>
+      <c r="F2137" s="3">
+        <v>9</v>
+      </c>
+      <c r="G2137" s="3">
+        <v>14708</v>
+      </c>
+      <c r="H2137" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2138" spans="1:8">
+      <c r="A2138" s="3" t="s">
+        <v>2154</v>
+      </c>
+      <c r="B2138" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2138" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2138" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2138" s="3">
+        <v>6857</v>
+      </c>
+      <c r="F2138" s="3">
+        <v>3</v>
+      </c>
+      <c r="G2138" s="3">
+        <v>10726</v>
+      </c>
+      <c r="H2138" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2139" spans="1:8">
+      <c r="A2139" s="3" t="s">
+        <v>2155</v>
+      </c>
+      <c r="B2139" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2139" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2139" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2139" s="3">
+        <v>6838</v>
+      </c>
+      <c r="F2139" s="3">
+        <v>1</v>
+      </c>
+      <c r="G2139" s="3">
+        <v>8912</v>
+      </c>
+      <c r="H2139" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2140" spans="1:8">
+      <c r="A2140" s="3" t="s">
+        <v>2156</v>
+      </c>
+      <c r="B2140" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2140" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2140" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2140" s="3">
+        <v>6838</v>
+      </c>
+      <c r="F2140" s="3">
+        <v>2</v>
+      </c>
+      <c r="G2140" s="3">
+        <v>9222</v>
+      </c>
+      <c r="H2140" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2141" spans="1:8">
+      <c r="A2141" s="3" t="s">
+        <v>2157</v>
+      </c>
+      <c r="B2141" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2141" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2141" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2141" s="3">
+        <v>6835</v>
+      </c>
+      <c r="F2141" s="3">
+        <v>9</v>
+      </c>
+      <c r="G2141" s="3">
+        <v>15709</v>
+      </c>
+      <c r="H2141" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2142" spans="1:8">
+      <c r="A2142" s="3" t="s">
+        <v>2158</v>
+      </c>
+      <c r="B2142" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2142" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2142" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2142" s="3">
+        <v>6825</v>
+      </c>
+      <c r="F2142" s="3">
+        <v>7</v>
+      </c>
+      <c r="G2142" s="3">
+        <v>14468</v>
+      </c>
+      <c r="H2142" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2143" spans="1:8">
+      <c r="A2143" s="3" t="s">
+        <v>2159</v>
+      </c>
+      <c r="B2143" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2143" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2143" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2143" s="3">
+        <v>6812</v>
+      </c>
+      <c r="F2143" s="3">
+        <v>2</v>
+      </c>
+      <c r="G2143" s="3">
+        <v>10321</v>
+      </c>
+      <c r="H2143" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2144" spans="1:8">
+      <c r="A2144" s="3" t="s">
+        <v>2160</v>
+      </c>
+      <c r="B2144" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2144" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2144" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2144" s="3">
+        <v>6794</v>
+      </c>
+      <c r="F2144" s="3">
+        <v>9</v>
+      </c>
+      <c r="G2144" s="3">
+        <v>14291</v>
+      </c>
+      <c r="H2144" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2145" spans="1:8">
+      <c r="A2145" s="3" t="s">
+        <v>2161</v>
+      </c>
+      <c r="B2145" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2145" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2145" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2145" s="3">
+        <v>6784</v>
+      </c>
+      <c r="F2145" s="3">
+        <v>5</v>
+      </c>
+      <c r="G2145" s="3">
+        <v>13675</v>
+      </c>
+      <c r="H2145" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2146" spans="1:8">
+      <c r="A2146" s="3" t="s">
+        <v>2162</v>
+      </c>
+      <c r="B2146" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2146" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2146" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2146" s="3">
+        <v>6762</v>
+      </c>
+      <c r="F2146" s="3">
+        <v>2</v>
+      </c>
+      <c r="G2146" s="3">
+        <v>10632</v>
+      </c>
+      <c r="H2146" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2147" spans="1:8">
+      <c r="A2147" s="3" t="s">
+        <v>2163</v>
+      </c>
+      <c r="B2147" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2147" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2147" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2147" s="3">
+        <v>6737</v>
+      </c>
+      <c r="F2147" s="3">
+        <v>10</v>
+      </c>
+      <c r="G2147" s="3">
+        <v>14601</v>
+      </c>
+      <c r="H2147" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2148" spans="1:8">
+      <c r="A2148" s="3" t="s">
+        <v>2164</v>
+      </c>
+      <c r="B2148" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2148" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2148" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2148" s="3">
+        <v>6735</v>
+      </c>
+      <c r="F2148" s="3">
+        <v>5</v>
+      </c>
+      <c r="G2148" s="3">
+        <v>13401</v>
+      </c>
+      <c r="H2148" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2149" spans="1:8">
+      <c r="A2149" s="3" t="s">
+        <v>2165</v>
+      </c>
+      <c r="B2149" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2149" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2149" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2149" s="3">
+        <v>6731</v>
+      </c>
+      <c r="F2149" s="3">
+        <v>4</v>
+      </c>
+      <c r="G2149" s="3">
+        <v>11616</v>
+      </c>
+      <c r="H2149" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2150" spans="1:8">
+      <c r="A2150" s="3" t="s">
+        <v>2166</v>
+      </c>
+      <c r="B2150" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2150" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2150" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2150" s="3">
+        <v>6711</v>
+      </c>
+      <c r="F2150" s="3">
+        <v>5</v>
+      </c>
+      <c r="G2150" s="3">
+        <v>10866</v>
+      </c>
+      <c r="H2150" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2151" spans="1:8">
+      <c r="A2151" s="3" t="s">
+        <v>2167</v>
+      </c>
+      <c r="B2151" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2151" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2151" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2151" s="3">
+        <v>6707</v>
+      </c>
+      <c r="F2151" s="3">
+        <v>9</v>
+      </c>
+      <c r="G2151" s="3">
+        <v>14143</v>
+      </c>
+      <c r="H2151" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2152" spans="1:8">
+      <c r="A2152" s="3" t="s">
+        <v>2168</v>
+      </c>
+      <c r="B2152" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2152" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2152" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2152" s="3">
+        <v>6705</v>
+      </c>
+      <c r="F2152" s="3">
+        <v>8</v>
+      </c>
+      <c r="G2152" s="3">
+        <v>13344</v>
+      </c>
+      <c r="H2152" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2153" spans="1:8">
+      <c r="A2153" s="3" t="s">
+        <v>2169</v>
+      </c>
+      <c r="B2153" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2153" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2153" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2153" s="3">
+        <v>6700</v>
+      </c>
+      <c r="F2153" s="3">
+        <v>9</v>
+      </c>
+      <c r="G2153" s="3">
+        <v>15395</v>
+      </c>
+      <c r="H2153" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2154" spans="1:8">
+      <c r="A2154" s="3" t="s">
+        <v>2170</v>
+      </c>
+      <c r="B2154" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2154" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2154" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2154" s="3">
+        <v>6689</v>
+      </c>
+      <c r="F2154" s="3">
+        <v>5</v>
+      </c>
+      <c r="G2154" s="3">
+        <v>13282</v>
+      </c>
+      <c r="H2154" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2155" spans="1:8">
+      <c r="A2155" s="3" t="s">
+        <v>2171</v>
+      </c>
+      <c r="B2155" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2155" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2155" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2155" s="3">
+        <v>6668</v>
+      </c>
+      <c r="F2155" s="3">
+        <v>5</v>
+      </c>
+      <c r="G2155" s="3">
+        <v>12948</v>
+      </c>
+      <c r="H2155" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2156" spans="1:8">
+      <c r="A2156" s="3" t="s">
+        <v>2172</v>
+      </c>
+      <c r="B2156" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2156" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2156" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2156" s="3">
+        <v>6658</v>
+      </c>
+      <c r="F2156" s="3">
+        <v>6</v>
+      </c>
+      <c r="G2156" s="3">
+        <v>12206</v>
+      </c>
+      <c r="H2156" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2157" spans="1:8">
+      <c r="A2157" s="3" t="s">
+        <v>2173</v>
+      </c>
+      <c r="B2157" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2157" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2157" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2157" s="3">
+        <v>6652</v>
+      </c>
+      <c r="F2157" s="3">
+        <v>8</v>
+      </c>
+      <c r="G2157" s="3">
+        <v>12518</v>
+      </c>
+      <c r="H2157" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2158" spans="1:8">
+      <c r="A2158" s="3" t="s">
+        <v>2174</v>
+      </c>
+      <c r="B2158" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2158" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2158" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2158" s="3">
+        <v>6636</v>
+      </c>
+      <c r="F2158" s="3">
+        <v>4</v>
+      </c>
+      <c r="G2158" s="3">
+        <v>10143</v>
+      </c>
+      <c r="H2158" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2159" spans="1:8">
+      <c r="A2159" s="3" t="s">
+        <v>2175</v>
+      </c>
+      <c r="B2159" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2159" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2159" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2159" s="3">
+        <v>6624</v>
+      </c>
+      <c r="F2159" s="3">
+        <v>9</v>
+      </c>
+      <c r="G2159" s="3">
+        <v>14520</v>
+      </c>
+      <c r="H2159" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2160" spans="1:8">
+      <c r="A2160" s="3" t="s">
+        <v>2176</v>
+      </c>
+      <c r="B2160" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2160" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2160" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2160" s="3">
+        <v>6623</v>
+      </c>
+      <c r="F2160" s="3">
+        <v>9</v>
+      </c>
+      <c r="G2160" s="3">
+        <v>14533</v>
+      </c>
+      <c r="H2160" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2161" spans="1:8">
+      <c r="A2161" s="3" t="s">
+        <v>2177</v>
+      </c>
+      <c r="B2161" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2161" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2161" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2161" s="3">
+        <v>6605</v>
+      </c>
+      <c r="F2161" s="3">
+        <v>2</v>
+      </c>
+      <c r="G2161" s="3">
+        <v>9948</v>
+      </c>
+      <c r="H2161" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2162" spans="1:8">
+      <c r="A2162" s="3" t="s">
+        <v>2178</v>
+      </c>
+      <c r="B2162" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2162" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2162" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2162" s="3">
+        <v>6571</v>
+      </c>
+      <c r="F2162" s="3">
+        <v>10</v>
+      </c>
+      <c r="G2162" s="3">
+        <v>16416</v>
+      </c>
+      <c r="H2162" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2163" spans="1:8">
+      <c r="A2163" s="3" t="s">
+        <v>2179</v>
+      </c>
+      <c r="B2163" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2163" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2163" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2163" s="3">
+        <v>6558</v>
+      </c>
+      <c r="F2163" s="3">
+        <v>10</v>
+      </c>
+      <c r="G2163" s="3">
+        <v>16107</v>
+      </c>
+      <c r="H2163" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2164" spans="1:8">
+      <c r="A2164" s="3" t="s">
+        <v>2180</v>
+      </c>
+      <c r="B2164" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2164" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2164" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2164" s="3">
+        <v>6513</v>
+      </c>
+      <c r="F2164" s="3">
+        <v>4</v>
+      </c>
+      <c r="G2164" s="3">
+        <v>10670</v>
+      </c>
+      <c r="H2164" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2165" spans="1:8">
+      <c r="A2165" s="3" t="s">
+        <v>2181</v>
+      </c>
+      <c r="B2165" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2165" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2165" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2165" s="3">
+        <v>6510</v>
+      </c>
+      <c r="F2165" s="3">
+        <v>0</v>
+      </c>
+      <c r="G2165" s="3">
+        <v>7627</v>
+      </c>
+      <c r="H2165" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2166" spans="1:8">
+      <c r="A2166" s="3" t="s">
+        <v>2182</v>
+      </c>
+      <c r="B2166" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2166" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2166" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2166" s="3">
+        <v>6502</v>
+      </c>
+      <c r="F2166" s="3">
+        <v>10</v>
+      </c>
+      <c r="G2166" s="3">
+        <v>13817</v>
+      </c>
+      <c r="H2166" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2167" spans="1:8">
+      <c r="A2167" s="3" t="s">
+        <v>2183</v>
+      </c>
+      <c r="B2167" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2167" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2167" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2167" s="3">
+        <v>6494</v>
+      </c>
+      <c r="F2167" s="3">
+        <v>4</v>
+      </c>
+      <c r="G2167" s="3">
+        <v>12442</v>
+      </c>
+      <c r="H2167" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2168" spans="1:8">
+      <c r="A2168" s="3" t="s">
+        <v>2184</v>
+      </c>
+      <c r="B2168" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2168" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2168" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2168" s="3">
+        <v>6469</v>
+      </c>
+      <c r="F2168" s="3">
+        <v>8</v>
+      </c>
+      <c r="G2168" s="3">
+        <v>14904</v>
+      </c>
+      <c r="H2168" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2169" spans="1:8">
+      <c r="A2169" s="3" t="s">
+        <v>2185</v>
+      </c>
+      <c r="B2169" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2169" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2169" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2169" s="3">
+        <v>6443</v>
+      </c>
+      <c r="F2169" s="3">
+        <v>7</v>
+      </c>
+      <c r="G2169" s="3">
+        <v>12029</v>
+      </c>
+      <c r="H2169" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2170" spans="1:8">
+      <c r="A2170" s="3" t="s">
+        <v>2186</v>
+      </c>
+      <c r="B2170" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2170" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2170" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2170" s="3">
+        <v>6437</v>
+      </c>
+      <c r="F2170" s="3">
+        <v>2</v>
+      </c>
+      <c r="G2170" s="3">
+        <v>9998</v>
+      </c>
+      <c r="H2170" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2171" spans="1:8">
+      <c r="A2171" s="3" t="s">
+        <v>2187</v>
+      </c>
+      <c r="B2171" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2171" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2171" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2171" s="3">
+        <v>6429</v>
+      </c>
+      <c r="F2171" s="3">
+        <v>1</v>
+      </c>
+      <c r="G2171" s="3">
+        <v>10032</v>
+      </c>
+      <c r="H2171" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2172" spans="1:8">
+      <c r="A2172" s="3" t="s">
+        <v>2188</v>
+      </c>
+      <c r="B2172" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2172" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2172" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2172" s="3">
+        <v>6379</v>
+      </c>
+      <c r="F2172" s="3">
+        <v>2</v>
+      </c>
+      <c r="G2172" s="3">
+        <v>10823</v>
+      </c>
+      <c r="H2172" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2173" spans="1:8">
+      <c r="A2173" s="3" t="s">
+        <v>2189</v>
+      </c>
+      <c r="B2173" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2173" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2173" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2173" s="3">
+        <v>6370</v>
+      </c>
+      <c r="F2173" s="3">
+        <v>7</v>
+      </c>
+      <c r="G2173" s="3">
+        <v>12508</v>
+      </c>
+      <c r="H2173" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2174" spans="1:8">
+      <c r="A2174" s="3" t="s">
+        <v>2190</v>
+      </c>
+      <c r="B2174" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2174" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2174" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2174" s="3">
+        <v>6367</v>
+      </c>
+      <c r="F2174" s="3">
+        <v>9</v>
+      </c>
+      <c r="G2174" s="3">
+        <v>13780</v>
+      </c>
+      <c r="H2174" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2175" spans="1:8">
+      <c r="A2175" s="3" t="s">
+        <v>2191</v>
+      </c>
+      <c r="B2175" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2175" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2175" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2175" s="3">
+        <v>6327</v>
+      </c>
+      <c r="F2175" s="3">
+        <v>8</v>
+      </c>
+      <c r="G2175" s="3">
+        <v>14962</v>
+      </c>
+      <c r="H2175" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2176" spans="1:8">
+      <c r="A2176" s="3" t="s">
+        <v>2192</v>
+      </c>
+      <c r="B2176" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2176" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2176" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2176" s="3">
+        <v>6311</v>
+      </c>
+      <c r="F2176" s="3">
+        <v>0</v>
+      </c>
+      <c r="G2176" s="3">
+        <v>8014</v>
+      </c>
+      <c r="H2176" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2177" spans="1:8">
+      <c r="A2177" s="3" t="s">
+        <v>2193</v>
+      </c>
+      <c r="B2177" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2177" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2177" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2177" s="3">
+        <v>6300</v>
+      </c>
+      <c r="F2177" s="3">
+        <v>5</v>
+      </c>
+      <c r="G2177" s="3">
+        <v>10975</v>
+      </c>
+      <c r="H2177" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2178" spans="1:8">
+      <c r="A2178" s="3" t="s">
+        <v>2194</v>
+      </c>
+      <c r="B2178" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2178" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2178" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2178" s="3">
+        <v>6277</v>
+      </c>
+      <c r="F2178" s="3">
+        <v>7</v>
+      </c>
+      <c r="G2178" s="3">
+        <v>13158</v>
+      </c>
+      <c r="H2178" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2179" spans="1:8">
+      <c r="A2179" s="3" t="s">
+        <v>2195</v>
+      </c>
+      <c r="B2179" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2179" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2179" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2179" s="3">
+        <v>6276</v>
+      </c>
+      <c r="F2179" s="3">
+        <v>5</v>
+      </c>
+      <c r="G2179" s="3">
+        <v>10347</v>
+      </c>
+      <c r="H2179" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2180" spans="1:8">
+      <c r="A2180" s="3" t="s">
+        <v>2196</v>
+      </c>
+      <c r="B2180" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2180" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2180" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2180" s="3">
+        <v>6273</v>
+      </c>
+      <c r="F2180" s="3">
+        <v>5</v>
+      </c>
+      <c r="G2180" s="3">
+        <v>10871</v>
+      </c>
+      <c r="H2180" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2181" spans="1:8">
+      <c r="A2181" s="3" t="s">
+        <v>2197</v>
+      </c>
+      <c r="B2181" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2181" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2181" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2181" s="3">
+        <v>6266</v>
+      </c>
+      <c r="F2181" s="3">
+        <v>8</v>
+      </c>
+      <c r="G2181" s="3">
+        <v>14413</v>
+      </c>
+      <c r="H2181" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2182" spans="1:8">
+      <c r="A2182" s="3" t="s">
+        <v>2198</v>
+      </c>
+      <c r="B2182" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2182" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2182" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2182" s="3">
+        <v>6262</v>
+      </c>
+      <c r="F2182" s="3">
+        <v>3</v>
+      </c>
+      <c r="G2182" s="3">
+        <v>11108</v>
+      </c>
+      <c r="H2182" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2183" spans="1:8">
+      <c r="A2183" s="3" t="s">
+        <v>2199</v>
+      </c>
+      <c r="B2183" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2183" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2183" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2183" s="3">
+        <v>6198</v>
+      </c>
+      <c r="F2183" s="3">
+        <v>1</v>
+      </c>
+      <c r="G2183" s="3">
+        <v>9539</v>
+      </c>
+      <c r="H2183" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2184" spans="1:8">
+      <c r="A2184" s="3" t="s">
+        <v>2200</v>
+      </c>
+      <c r="B2184" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2184" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2184" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2184" s="3">
+        <v>6196</v>
+      </c>
+      <c r="F2184" s="3">
+        <v>2</v>
+      </c>
+      <c r="G2184" s="3">
+        <v>8917</v>
+      </c>
+      <c r="H2184" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2185" spans="1:8">
+      <c r="A2185" s="3" t="s">
+        <v>2201</v>
+      </c>
+      <c r="B2185" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2185" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2185" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2185" s="3">
+        <v>6194</v>
+      </c>
+      <c r="F2185" s="3">
+        <v>2</v>
+      </c>
+      <c r="G2185" s="3">
+        <v>9895</v>
+      </c>
+      <c r="H2185" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2186" spans="1:8">
+      <c r="A2186" s="3" t="s">
+        <v>2202</v>
+      </c>
+      <c r="B2186" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2186" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2186" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2186" s="3">
+        <v>6187</v>
+      </c>
+      <c r="F2186" s="3">
+        <v>8</v>
+      </c>
+      <c r="G2186" s="3">
+        <v>12445</v>
+      </c>
+      <c r="H2186" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2187" spans="1:8">
+      <c r="A2187" s="3" t="s">
+        <v>2203</v>
+      </c>
+      <c r="B2187" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2187" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2187" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2187" s="3">
+        <v>6166</v>
+      </c>
+      <c r="F2187" s="3">
+        <v>3</v>
+      </c>
+      <c r="G2187" s="3">
+        <v>9617</v>
+      </c>
+      <c r="H2187" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2188" spans="1:8">
+      <c r="A2188" s="3" t="s">
+        <v>2204</v>
+      </c>
+      <c r="B2188" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2188" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2188" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2188" s="3">
+        <v>6166</v>
+      </c>
+      <c r="F2188" s="3">
+        <v>8</v>
+      </c>
+      <c r="G2188" s="3">
+        <v>13107</v>
+      </c>
+      <c r="H2188" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2189" spans="1:8">
+      <c r="A2189" s="3" t="s">
+        <v>2205</v>
+      </c>
+      <c r="B2189" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2189" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2189" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2189" s="3">
+        <v>6163</v>
+      </c>
+      <c r="F2189" s="3">
+        <v>6</v>
+      </c>
+      <c r="G2189" s="3">
+        <v>11596</v>
+      </c>
+      <c r="H2189" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2190" spans="1:8">
+      <c r="A2190" s="3" t="s">
+        <v>2206</v>
+      </c>
+      <c r="B2190" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2190" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2190" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2190" s="3">
+        <v>6149</v>
+      </c>
+      <c r="F2190" s="3">
+        <v>7</v>
+      </c>
+      <c r="G2190" s="3">
+        <v>13612</v>
+      </c>
+      <c r="H2190" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2191" spans="1:8">
+      <c r="A2191" s="3" t="s">
+        <v>2207</v>
+      </c>
+      <c r="B2191" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2191" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2191" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2191" s="3">
+        <v>6134</v>
+      </c>
+      <c r="F2191" s="3">
+        <v>3</v>
+      </c>
+      <c r="G2191" s="3">
+        <v>9720</v>
+      </c>
+      <c r="H2191" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2192" spans="1:8">
+      <c r="A2192" s="3" t="s">
+        <v>2208</v>
+      </c>
+      <c r="B2192" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2192" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2192" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2192" s="3">
+        <v>6116</v>
+      </c>
+      <c r="F2192" s="3">
+        <v>0</v>
+      </c>
+      <c r="G2192" s="3">
+        <v>9985</v>
+      </c>
+      <c r="H2192" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2193" spans="1:8">
+      <c r="A2193" s="3" t="s">
+        <v>2209</v>
+      </c>
+      <c r="B2193" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2193" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2193" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2193" s="3">
+        <v>6113</v>
+      </c>
+      <c r="F2193" s="3">
+        <v>1</v>
+      </c>
+      <c r="G2193" s="3">
+        <v>8131</v>
+      </c>
+      <c r="H2193" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2194" spans="1:8">
+      <c r="A2194" s="3" t="s">
+        <v>2210</v>
+      </c>
+      <c r="B2194" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2194" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2194" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2194" s="3">
+        <v>6096</v>
+      </c>
+      <c r="F2194" s="3">
+        <v>7</v>
+      </c>
+      <c r="G2194" s="3">
+        <v>14005</v>
+      </c>
+      <c r="H2194" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2195" spans="1:8">
+      <c r="A2195" s="3" t="s">
+        <v>2211</v>
+      </c>
+      <c r="B2195" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2195" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2195" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2195" s="3">
+        <v>6076</v>
+      </c>
+      <c r="F2195" s="3">
+        <v>10</v>
+      </c>
+      <c r="G2195" s="3">
+        <v>15001</v>
+      </c>
+      <c r="H2195" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2196" spans="1:8">
+      <c r="A2196" s="3" t="s">
+        <v>2212</v>
+      </c>
+      <c r="B2196" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2196" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2196" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2196" s="3">
+        <v>6073</v>
+      </c>
+      <c r="F2196" s="3">
+        <v>1</v>
+      </c>
+      <c r="G2196" s="3">
+        <v>9317</v>
+      </c>
+      <c r="H2196" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2197" spans="1:8">
+      <c r="A2197" s="3" t="s">
+        <v>2213</v>
+      </c>
+      <c r="B2197" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2197" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2197" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2197" s="3">
+        <v>6064</v>
+      </c>
+      <c r="F2197" s="3">
+        <v>5</v>
+      </c>
+      <c r="G2197" s="3">
+        <v>12092</v>
+      </c>
+      <c r="H2197" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2198" spans="1:8">
+      <c r="A2198" s="3" t="s">
+        <v>2214</v>
+      </c>
+      <c r="B2198" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2198" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2198" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2198" s="3">
+        <v>6047</v>
+      </c>
+      <c r="F2198" s="3">
+        <v>0</v>
+      </c>
+      <c r="G2198" s="3">
+        <v>10040</v>
+      </c>
+      <c r="H2198" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2199" spans="1:8">
+      <c r="A2199" s="3" t="s">
+        <v>2215</v>
+      </c>
+      <c r="B2199" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2199" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2199" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2199" s="3">
+        <v>6040</v>
+      </c>
+      <c r="F2199" s="3">
+        <v>10</v>
+      </c>
+      <c r="G2199" s="3">
+        <v>14324</v>
+      </c>
+      <c r="H2199" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2200" spans="1:8">
+      <c r="A2200" s="3" t="s">
+        <v>2216</v>
+      </c>
+      <c r="B2200" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2200" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2200" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2200" s="3">
+        <v>6024</v>
+      </c>
+      <c r="F2200" s="3">
+        <v>4</v>
+      </c>
+      <c r="G2200" s="3">
+        <v>11486</v>
+      </c>
+      <c r="H2200" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2201" spans="1:8">
+      <c r="A2201" s="3" t="s">
+        <v>2217</v>
+      </c>
+      <c r="B2201" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2201" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2201" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2201" s="3">
+        <v>5998</v>
+      </c>
+      <c r="F2201" s="3">
+        <v>9</v>
+      </c>
+      <c r="G2201" s="3">
+        <v>13649</v>
+      </c>
+      <c r="H2201" s="3">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/NGO_Project_MNE_Dataset_2000.xlsx
+++ b/NGO_Project_MNE_Dataset_2000.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8808" uniqueCount="2218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8812" uniqueCount="2219">
   <si>
     <t>Household_ID</t>
   </si>
@@ -6671,6 +6671,9 @@
   </si>
   <si>
     <t>HH-3200</t>
+  </si>
+  <si>
+    <t>HH-3201</t>
   </si>
 </sst>
 </file>
@@ -7015,7 +7018,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H2201"/>
+  <dimension ref="A1:H2202"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.85546875" style="2" customWidth="1"/>
@@ -64255,6 +64258,32 @@
         <v>5</v>
       </c>
     </row>
+    <row r="2202" spans="1:8">
+      <c r="A2202" s="3" t="s">
+        <v>2218</v>
+      </c>
+      <c r="B2202" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2202" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2202" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2202" s="3">
+        <v>7122</v>
+      </c>
+      <c r="F2202" s="3">
+        <v>4</v>
+      </c>
+      <c r="G2202" s="3">
+        <v>11867</v>
+      </c>
+      <c r="H2202" s="3">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/NGO_Project_MNE_Dataset_2000.xlsx
+++ b/NGO_Project_MNE_Dataset_2000.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$2202</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8812" uniqueCount="2219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8824" uniqueCount="2222">
   <si>
     <t>Household_ID</t>
   </si>
@@ -6674,6 +6674,15 @@
   </si>
   <si>
     <t>HH-3201</t>
+  </si>
+  <si>
+    <t>HH-3202</t>
+  </si>
+  <si>
+    <t>HH-3203</t>
+  </si>
+  <si>
+    <t>HH-3204</t>
   </si>
 </sst>
 </file>
@@ -7018,7 +7027,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H2202"/>
+  <dimension ref="A1:H2205"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.85546875" style="2" customWidth="1"/>
@@ -64284,6 +64293,84 @@
         <v>3</v>
       </c>
     </row>
+    <row r="2203" spans="1:8" s="3" customFormat="1">
+      <c r="A2203" s="3" t="s">
+        <v>2219</v>
+      </c>
+      <c r="B2203" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2203" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2203" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2203" s="3">
+        <v>5998</v>
+      </c>
+      <c r="F2203" s="3">
+        <v>9</v>
+      </c>
+      <c r="G2203" s="3">
+        <v>13649</v>
+      </c>
+      <c r="H2203" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2204" spans="1:8" s="3" customFormat="1">
+      <c r="A2204" s="3" t="s">
+        <v>2220</v>
+      </c>
+      <c r="B2204" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2204" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2204" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2204" s="3">
+        <v>7122</v>
+      </c>
+      <c r="F2204" s="3">
+        <v>4</v>
+      </c>
+      <c r="G2204" s="3">
+        <v>11867</v>
+      </c>
+      <c r="H2204" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2205" spans="1:8" s="3" customFormat="1">
+      <c r="A2205" s="3" t="s">
+        <v>2221</v>
+      </c>
+      <c r="B2205" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2205" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2205" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2205" s="3">
+        <v>5998</v>
+      </c>
+      <c r="F2205" s="3">
+        <v>9</v>
+      </c>
+      <c r="G2205" s="3">
+        <v>13649</v>
+      </c>
+      <c r="H2205" s="3">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/NGO_Project_MNE_Dataset_2000.xlsx
+++ b/NGO_Project_MNE_Dataset_2000.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$2001</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$2153</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8282" uniqueCount="2085">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8614" uniqueCount="2168">
   <si>
     <t>Beneficiary ID</t>
   </si>
@@ -6272,6 +6272,255 @@
   </si>
   <si>
     <t>B-2069</t>
+  </si>
+  <si>
+    <t>B-2070</t>
+  </si>
+  <si>
+    <t>B-2071</t>
+  </si>
+  <si>
+    <t>B-2072</t>
+  </si>
+  <si>
+    <t>B-2073</t>
+  </si>
+  <si>
+    <t>B-2074</t>
+  </si>
+  <si>
+    <t>B-2075</t>
+  </si>
+  <si>
+    <t>B-2076</t>
+  </si>
+  <si>
+    <t>B-2077</t>
+  </si>
+  <si>
+    <t>B-2078</t>
+  </si>
+  <si>
+    <t>B-2079</t>
+  </si>
+  <si>
+    <t>B-2080</t>
+  </si>
+  <si>
+    <t>B-2081</t>
+  </si>
+  <si>
+    <t>B-2082</t>
+  </si>
+  <si>
+    <t>B-2083</t>
+  </si>
+  <si>
+    <t>B-2084</t>
+  </si>
+  <si>
+    <t>B-2085</t>
+  </si>
+  <si>
+    <t>B-2086</t>
+  </si>
+  <si>
+    <t>B-2087</t>
+  </si>
+  <si>
+    <t>B-2088</t>
+  </si>
+  <si>
+    <t>B-2089</t>
+  </si>
+  <si>
+    <t>B-2090</t>
+  </si>
+  <si>
+    <t>B-2091</t>
+  </si>
+  <si>
+    <t>B-2092</t>
+  </si>
+  <si>
+    <t>B-2093</t>
+  </si>
+  <si>
+    <t>B-2094</t>
+  </si>
+  <si>
+    <t>B-2095</t>
+  </si>
+  <si>
+    <t>B-2096</t>
+  </si>
+  <si>
+    <t>B-2097</t>
+  </si>
+  <si>
+    <t>B-2098</t>
+  </si>
+  <si>
+    <t>B-2099</t>
+  </si>
+  <si>
+    <t>B-2100</t>
+  </si>
+  <si>
+    <t>B-2101</t>
+  </si>
+  <si>
+    <t>B-2102</t>
+  </si>
+  <si>
+    <t>B-2103</t>
+  </si>
+  <si>
+    <t>B-2104</t>
+  </si>
+  <si>
+    <t>B-2105</t>
+  </si>
+  <si>
+    <t>B-2106</t>
+  </si>
+  <si>
+    <t>B-2107</t>
+  </si>
+  <si>
+    <t>B-2108</t>
+  </si>
+  <si>
+    <t>B-2109</t>
+  </si>
+  <si>
+    <t>B-2110</t>
+  </si>
+  <si>
+    <t>B-2111</t>
+  </si>
+  <si>
+    <t>B-2112</t>
+  </si>
+  <si>
+    <t>B-2113</t>
+  </si>
+  <si>
+    <t>B-2114</t>
+  </si>
+  <si>
+    <t>B-2115</t>
+  </si>
+  <si>
+    <t>B-2116</t>
+  </si>
+  <si>
+    <t>B-2117</t>
+  </si>
+  <si>
+    <t>B-2118</t>
+  </si>
+  <si>
+    <t>B-2119</t>
+  </si>
+  <si>
+    <t>B-2120</t>
+  </si>
+  <si>
+    <t>B-2121</t>
+  </si>
+  <si>
+    <t>B-2122</t>
+  </si>
+  <si>
+    <t>B-2123</t>
+  </si>
+  <si>
+    <t>B-2124</t>
+  </si>
+  <si>
+    <t>B-2125</t>
+  </si>
+  <si>
+    <t>B-2126</t>
+  </si>
+  <si>
+    <t>B-2127</t>
+  </si>
+  <si>
+    <t>B-2128</t>
+  </si>
+  <si>
+    <t>B-2129</t>
+  </si>
+  <si>
+    <t>B-2130</t>
+  </si>
+  <si>
+    <t>B-2131</t>
+  </si>
+  <si>
+    <t>B-2132</t>
+  </si>
+  <si>
+    <t>B-2133</t>
+  </si>
+  <si>
+    <t>B-2134</t>
+  </si>
+  <si>
+    <t>B-2135</t>
+  </si>
+  <si>
+    <t>B-2136</t>
+  </si>
+  <si>
+    <t>B-2137</t>
+  </si>
+  <si>
+    <t>B-2138</t>
+  </si>
+  <si>
+    <t>B-2139</t>
+  </si>
+  <si>
+    <t>B-2140</t>
+  </si>
+  <si>
+    <t>B-2141</t>
+  </si>
+  <si>
+    <t>B-2142</t>
+  </si>
+  <si>
+    <t>B-2143</t>
+  </si>
+  <si>
+    <t>B-2144</t>
+  </si>
+  <si>
+    <t>B-2145</t>
+  </si>
+  <si>
+    <t>B-2146</t>
+  </si>
+  <si>
+    <t>B-2147</t>
+  </si>
+  <si>
+    <t>B-2148</t>
+  </si>
+  <si>
+    <t>B-2149</t>
+  </si>
+  <si>
+    <t>B-2150</t>
+  </si>
+  <si>
+    <t>B-2151</t>
+  </si>
+  <si>
+    <t>B-2152</t>
   </si>
 </sst>
 </file>
@@ -6307,7 +6556,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
@@ -6604,7 +6854,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2070"/>
+  <dimension ref="A1:F2153"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -48007,6 +48257,1666 @@
         <v>8464.7800000000007</v>
       </c>
     </row>
+    <row r="2071" spans="1:6">
+      <c r="A2071" s="2" t="s">
+        <v>2085</v>
+      </c>
+      <c r="B2071" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2071" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2071" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2071" s="2">
+        <v>4634.24</v>
+      </c>
+      <c r="F2071" s="2">
+        <v>10111.25</v>
+      </c>
+    </row>
+    <row r="2072" spans="1:6">
+      <c r="A2072" s="2" t="s">
+        <v>2086</v>
+      </c>
+      <c r="B2072" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2072" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2072" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2072" s="2">
+        <v>5692.85</v>
+      </c>
+      <c r="F2072" s="2">
+        <v>10925.52</v>
+      </c>
+    </row>
+    <row r="2073" spans="1:6">
+      <c r="A2073" s="2" t="s">
+        <v>2087</v>
+      </c>
+      <c r="B2073" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2073" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2073" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2073" s="2">
+        <v>5377.89</v>
+      </c>
+      <c r="F2073" s="2">
+        <v>10736.02</v>
+      </c>
+    </row>
+    <row r="2074" spans="1:6">
+      <c r="A2074" s="2" t="s">
+        <v>2088</v>
+      </c>
+      <c r="B2074" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2074" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2074" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2074" s="2">
+        <v>5620.05</v>
+      </c>
+      <c r="F2074" s="2">
+        <v>11710.18</v>
+      </c>
+    </row>
+    <row r="2075" spans="1:6">
+      <c r="A2075" s="2" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B2075" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2075" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2075" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2075" s="2">
+        <v>5128.83</v>
+      </c>
+      <c r="F2075" s="2">
+        <v>10053.67</v>
+      </c>
+    </row>
+    <row r="2076" spans="1:6">
+      <c r="A2076" s="2" t="s">
+        <v>2090</v>
+      </c>
+      <c r="B2076" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2076" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2076" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2076" s="2">
+        <v>4321.1899999999996</v>
+      </c>
+      <c r="F2076" s="2">
+        <v>9507.6299999999992</v>
+      </c>
+    </row>
+    <row r="2077" spans="1:6">
+      <c r="A2077" s="2" t="s">
+        <v>2091</v>
+      </c>
+      <c r="B2077" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2077" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2077" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2077" s="2">
+        <v>5595.93</v>
+      </c>
+      <c r="F2077" s="2">
+        <v>12756.07</v>
+      </c>
+    </row>
+    <row r="2078" spans="1:6">
+      <c r="A2078" s="2" t="s">
+        <v>2092</v>
+      </c>
+      <c r="B2078" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2078" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2078" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2078" s="2">
+        <v>8560.49</v>
+      </c>
+      <c r="F2078" s="2">
+        <v>13033.95</v>
+      </c>
+    </row>
+    <row r="2079" spans="1:6">
+      <c r="A2079" s="2" t="s">
+        <v>2093</v>
+      </c>
+      <c r="B2079" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2079" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2079" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2079" s="2">
+        <v>7216.91</v>
+      </c>
+      <c r="F2079" s="2">
+        <v>12608.08</v>
+      </c>
+    </row>
+    <row r="2080" spans="1:6">
+      <c r="A2080" s="2" t="s">
+        <v>2094</v>
+      </c>
+      <c r="B2080" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2080" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2080" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2080" s="2">
+        <v>7655.08</v>
+      </c>
+      <c r="F2080" s="2">
+        <v>13711.6</v>
+      </c>
+    </row>
+    <row r="2081" spans="1:6">
+      <c r="A2081" s="2" t="s">
+        <v>2095</v>
+      </c>
+      <c r="B2081" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2081" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2081" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2081" s="2">
+        <v>6165.11</v>
+      </c>
+      <c r="F2081" s="2">
+        <v>9633.7000000000007</v>
+      </c>
+    </row>
+    <row r="2082" spans="1:6">
+      <c r="A2082" s="2" t="s">
+        <v>2096</v>
+      </c>
+      <c r="B2082" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2082" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2082" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2082" s="2">
+        <v>5597.99</v>
+      </c>
+      <c r="F2082" s="2">
+        <v>10978.59</v>
+      </c>
+    </row>
+    <row r="2083" spans="1:6">
+      <c r="A2083" s="2" t="s">
+        <v>2097</v>
+      </c>
+      <c r="B2083" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2083" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2083" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2083" s="2">
+        <v>5283.64</v>
+      </c>
+      <c r="F2083" s="2">
+        <v>11181.32</v>
+      </c>
+    </row>
+    <row r="2084" spans="1:6">
+      <c r="A2084" s="2" t="s">
+        <v>2098</v>
+      </c>
+      <c r="B2084" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2084" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2084" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2084" s="2">
+        <v>6841.6</v>
+      </c>
+      <c r="F2084" s="2">
+        <v>11738.86</v>
+      </c>
+    </row>
+    <row r="2085" spans="1:6">
+      <c r="A2085" s="2" t="s">
+        <v>2099</v>
+      </c>
+      <c r="B2085" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2085" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2085" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2085" s="2">
+        <v>4829.6499999999996</v>
+      </c>
+      <c r="F2085" s="2">
+        <v>9834.35</v>
+      </c>
+    </row>
+    <row r="2086" spans="1:6">
+      <c r="A2086" s="2" t="s">
+        <v>2100</v>
+      </c>
+      <c r="B2086" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2086" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2086" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2086" s="2">
+        <v>4040.29</v>
+      </c>
+      <c r="F2086" s="2">
+        <v>9390.9</v>
+      </c>
+    </row>
+    <row r="2087" spans="1:6">
+      <c r="A2087" s="2" t="s">
+        <v>2101</v>
+      </c>
+      <c r="B2087" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2087" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2087" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2087" s="2">
+        <v>8151.64</v>
+      </c>
+      <c r="F2087" s="2">
+        <v>15646.37</v>
+      </c>
+    </row>
+    <row r="2088" spans="1:6">
+      <c r="A2088" s="2" t="s">
+        <v>2102</v>
+      </c>
+      <c r="B2088" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2088" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2088" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2088" s="2">
+        <v>4945.46</v>
+      </c>
+      <c r="F2088" s="2">
+        <v>10281.370000000001</v>
+      </c>
+    </row>
+    <row r="2089" spans="1:6">
+      <c r="A2089" s="2" t="s">
+        <v>2103</v>
+      </c>
+      <c r="B2089" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2089" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2089" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2089" s="2">
+        <v>3610.4</v>
+      </c>
+      <c r="F2089" s="2">
+        <v>8604.7999999999993</v>
+      </c>
+    </row>
+    <row r="2090" spans="1:6">
+      <c r="A2090" s="2" t="s">
+        <v>2104</v>
+      </c>
+      <c r="B2090" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2090" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2090" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2090" s="2">
+        <v>7671.82</v>
+      </c>
+      <c r="F2090" s="2">
+        <v>13763.41</v>
+      </c>
+    </row>
+    <row r="2091" spans="1:6">
+      <c r="A2091" s="2" t="s">
+        <v>2105</v>
+      </c>
+      <c r="B2091" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2091" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2091" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2091" s="2">
+        <v>7527.49</v>
+      </c>
+      <c r="F2091" s="2">
+        <v>13574.79</v>
+      </c>
+    </row>
+    <row r="2092" spans="1:6">
+      <c r="A2092" s="2" t="s">
+        <v>2106</v>
+      </c>
+      <c r="B2092" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2092" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2092" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2092" s="2">
+        <v>4714.24</v>
+      </c>
+      <c r="F2092" s="2">
+        <v>9424.31</v>
+      </c>
+    </row>
+    <row r="2093" spans="1:6">
+      <c r="A2093" s="2" t="s">
+        <v>2107</v>
+      </c>
+      <c r="B2093" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2093" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2093" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2093" s="2">
+        <v>5259.86</v>
+      </c>
+      <c r="F2093" s="2">
+        <v>9675.33</v>
+      </c>
+    </row>
+    <row r="2094" spans="1:6">
+      <c r="A2094" s="2" t="s">
+        <v>2108</v>
+      </c>
+      <c r="B2094" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2094" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2094" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2094" s="2">
+        <v>4958.83</v>
+      </c>
+      <c r="F2094" s="2">
+        <v>10465.39</v>
+      </c>
+    </row>
+    <row r="2095" spans="1:6">
+      <c r="A2095" s="2" t="s">
+        <v>2109</v>
+      </c>
+      <c r="B2095" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2095" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2095" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2095" s="2">
+        <v>4770.84</v>
+      </c>
+      <c r="F2095" s="2">
+        <v>10577.75</v>
+      </c>
+    </row>
+    <row r="2096" spans="1:6">
+      <c r="A2096" s="2" t="s">
+        <v>2110</v>
+      </c>
+      <c r="B2096" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2096" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2096" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2096" s="2">
+        <v>6323.81</v>
+      </c>
+      <c r="F2096" s="2">
+        <v>12751.83</v>
+      </c>
+    </row>
+    <row r="2097" spans="1:6">
+      <c r="A2097" s="2" t="s">
+        <v>2111</v>
+      </c>
+      <c r="B2097" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2097" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2097" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2097" s="2">
+        <v>5762.83</v>
+      </c>
+      <c r="F2097" s="2">
+        <v>12489.1</v>
+      </c>
+    </row>
+    <row r="2098" spans="1:6">
+      <c r="A2098" s="2" t="s">
+        <v>2112</v>
+      </c>
+      <c r="B2098" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2098" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2098" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2098" s="2">
+        <v>5289.23</v>
+      </c>
+      <c r="F2098" s="2">
+        <v>10959.71</v>
+      </c>
+    </row>
+    <row r="2099" spans="1:6">
+      <c r="A2099" s="2" t="s">
+        <v>2113</v>
+      </c>
+      <c r="B2099" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2099" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2099" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2099" s="2">
+        <v>6713.29</v>
+      </c>
+      <c r="F2099" s="2">
+        <v>12281.83</v>
+      </c>
+    </row>
+    <row r="2100" spans="1:6">
+      <c r="A2100" s="2" t="s">
+        <v>2114</v>
+      </c>
+      <c r="B2100" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2100" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2100" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2100" s="2">
+        <v>7119.88</v>
+      </c>
+      <c r="F2100" s="2">
+        <v>10571.05</v>
+      </c>
+    </row>
+    <row r="2101" spans="1:6">
+      <c r="A2101" s="2" t="s">
+        <v>2115</v>
+      </c>
+      <c r="B2101" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2101" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2101" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2101" s="2">
+        <v>6294.63</v>
+      </c>
+      <c r="F2101" s="2">
+        <v>12169.96</v>
+      </c>
+    </row>
+    <row r="2102" spans="1:6">
+      <c r="A2102" s="2" t="s">
+        <v>2116</v>
+      </c>
+      <c r="B2102" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2102" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2102" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2102" s="2">
+        <v>5100.84</v>
+      </c>
+      <c r="F2102" s="2">
+        <v>10516.83</v>
+      </c>
+    </row>
+    <row r="2103" spans="1:6">
+      <c r="A2103" s="2" t="s">
+        <v>2117</v>
+      </c>
+      <c r="B2103" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2103" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2103" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2103" s="2">
+        <v>5955.15</v>
+      </c>
+      <c r="F2103" s="2">
+        <v>11570.28</v>
+      </c>
+    </row>
+    <row r="2104" spans="1:6">
+      <c r="A2104" s="2" t="s">
+        <v>2118</v>
+      </c>
+      <c r="B2104" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2104" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2104" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2104" s="2">
+        <v>5641.99</v>
+      </c>
+      <c r="F2104" s="2">
+        <v>11765.12</v>
+      </c>
+    </row>
+    <row r="2105" spans="1:6">
+      <c r="A2105" s="2" t="s">
+        <v>2119</v>
+      </c>
+      <c r="B2105" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2105" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2105" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2105" s="2">
+        <v>6548.7</v>
+      </c>
+      <c r="F2105" s="2">
+        <v>11556.65</v>
+      </c>
+    </row>
+    <row r="2106" spans="1:6">
+      <c r="A2106" s="2" t="s">
+        <v>2120</v>
+      </c>
+      <c r="B2106" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2106" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2106" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2106" s="2">
+        <v>6430.9</v>
+      </c>
+      <c r="F2106" s="2">
+        <v>13027.68</v>
+      </c>
+    </row>
+    <row r="2107" spans="1:6">
+      <c r="A2107" s="2" t="s">
+        <v>2121</v>
+      </c>
+      <c r="B2107" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2107" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2107" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2107" s="2">
+        <v>8893.35</v>
+      </c>
+      <c r="F2107" s="2">
+        <v>13850.15</v>
+      </c>
+    </row>
+    <row r="2108" spans="1:6">
+      <c r="A2108" s="2" t="s">
+        <v>2122</v>
+      </c>
+      <c r="B2108" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2108" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2108" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2108" s="2">
+        <v>7473.66</v>
+      </c>
+      <c r="F2108" s="2">
+        <v>14965.6</v>
+      </c>
+    </row>
+    <row r="2109" spans="1:6">
+      <c r="A2109" s="2" t="s">
+        <v>2123</v>
+      </c>
+      <c r="B2109" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2109" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2109" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2109" s="2">
+        <v>7668.36</v>
+      </c>
+      <c r="F2109" s="2">
+        <v>13450.16</v>
+      </c>
+    </row>
+    <row r="2110" spans="1:6">
+      <c r="A2110" s="2" t="s">
+        <v>2124</v>
+      </c>
+      <c r="B2110" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2110" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2110" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2110" s="2">
+        <v>6452.74</v>
+      </c>
+      <c r="F2110" s="2">
+        <v>11141.21</v>
+      </c>
+    </row>
+    <row r="2111" spans="1:6">
+      <c r="A2111" s="2" t="s">
+        <v>2125</v>
+      </c>
+      <c r="B2111" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2111" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2111" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2111" s="2">
+        <v>5217.67</v>
+      </c>
+      <c r="F2111" s="2">
+        <v>9516.4500000000007</v>
+      </c>
+    </row>
+    <row r="2112" spans="1:6">
+      <c r="A2112" s="2" t="s">
+        <v>2126</v>
+      </c>
+      <c r="B2112" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2112" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2112" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2112" s="2">
+        <v>7358.06</v>
+      </c>
+      <c r="F2112" s="2">
+        <v>12768.1</v>
+      </c>
+    </row>
+    <row r="2113" spans="1:6">
+      <c r="A2113" s="2" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B2113" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2113" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2113" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2113" s="2">
+        <v>5971.05</v>
+      </c>
+      <c r="F2113" s="2">
+        <v>11955.29</v>
+      </c>
+    </row>
+    <row r="2114" spans="1:6">
+      <c r="A2114" s="2" t="s">
+        <v>2128</v>
+      </c>
+      <c r="B2114" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2114" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2114" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2114" s="2">
+        <v>6607.45</v>
+      </c>
+      <c r="F2114" s="2">
+        <v>10432.83</v>
+      </c>
+    </row>
+    <row r="2115" spans="1:6">
+      <c r="A2115" s="2" t="s">
+        <v>2129</v>
+      </c>
+      <c r="B2115" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2115" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2115" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2115" s="2">
+        <v>6747.19</v>
+      </c>
+      <c r="F2115" s="2">
+        <v>11622.44</v>
+      </c>
+    </row>
+    <row r="2116" spans="1:6">
+      <c r="A2116" s="2" t="s">
+        <v>2130</v>
+      </c>
+      <c r="B2116" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2116" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2116" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2116" s="2">
+        <v>4515.22</v>
+      </c>
+      <c r="F2116" s="2">
+        <v>10078.84</v>
+      </c>
+    </row>
+    <row r="2117" spans="1:6">
+      <c r="A2117" s="2" t="s">
+        <v>2131</v>
+      </c>
+      <c r="B2117" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2117" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2117" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2117" s="2">
+        <v>6575.52</v>
+      </c>
+      <c r="F2117" s="2">
+        <v>12754.92</v>
+      </c>
+    </row>
+    <row r="2118" spans="1:6">
+      <c r="A2118" s="2" t="s">
+        <v>2132</v>
+      </c>
+      <c r="B2118" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2118" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2118" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2118" s="2">
+        <v>7453.47</v>
+      </c>
+      <c r="F2118" s="2">
+        <v>13263.14</v>
+      </c>
+    </row>
+    <row r="2119" spans="1:6">
+      <c r="A2119" s="2" t="s">
+        <v>2133</v>
+      </c>
+      <c r="B2119" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2119" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2119" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2119" s="2">
+        <v>9007.81</v>
+      </c>
+      <c r="F2119" s="2">
+        <v>14292.41</v>
+      </c>
+    </row>
+    <row r="2120" spans="1:6">
+      <c r="A2120" s="2" t="s">
+        <v>2134</v>
+      </c>
+      <c r="B2120" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2120" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2120" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2120" s="2">
+        <v>6834.56</v>
+      </c>
+      <c r="F2120" s="2">
+        <v>10561.95</v>
+      </c>
+    </row>
+    <row r="2121" spans="1:6">
+      <c r="A2121" s="2" t="s">
+        <v>2135</v>
+      </c>
+      <c r="B2121" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2121" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2121" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2121" s="2">
+        <v>5244.47</v>
+      </c>
+      <c r="F2121" s="2">
+        <v>10772.91</v>
+      </c>
+    </row>
+    <row r="2122" spans="1:6">
+      <c r="A2122" s="2" t="s">
+        <v>2136</v>
+      </c>
+      <c r="B2122" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2122" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2122" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2122" s="2">
+        <v>7035.95</v>
+      </c>
+      <c r="F2122" s="2">
+        <v>12694.02</v>
+      </c>
+    </row>
+    <row r="2123" spans="1:6">
+      <c r="A2123" s="2" t="s">
+        <v>2137</v>
+      </c>
+      <c r="B2123" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2123" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2123" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2123" s="2">
+        <v>7440.5</v>
+      </c>
+      <c r="F2123" s="2">
+        <v>14445.26</v>
+      </c>
+    </row>
+    <row r="2124" spans="1:6">
+      <c r="A2124" s="2" t="s">
+        <v>2138</v>
+      </c>
+      <c r="B2124" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2124" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2124" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2124" s="2">
+        <v>5299.91</v>
+      </c>
+      <c r="F2124" s="2">
+        <v>11351.99</v>
+      </c>
+    </row>
+    <row r="2125" spans="1:6">
+      <c r="A2125" s="2" t="s">
+        <v>2139</v>
+      </c>
+      <c r="B2125" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2125" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2125" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2125" s="2">
+        <v>6804.16</v>
+      </c>
+      <c r="F2125" s="2">
+        <v>11255.89</v>
+      </c>
+    </row>
+    <row r="2126" spans="1:6">
+      <c r="A2126" s="2" t="s">
+        <v>2140</v>
+      </c>
+      <c r="B2126" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2126" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2126" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2126" s="2">
+        <v>4040.94</v>
+      </c>
+      <c r="F2126" s="2">
+        <v>9896.6</v>
+      </c>
+    </row>
+    <row r="2127" spans="1:6">
+      <c r="A2127" s="2" t="s">
+        <v>2141</v>
+      </c>
+      <c r="B2127" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2127" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2127" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2127" s="2">
+        <v>6617.94</v>
+      </c>
+      <c r="F2127" s="2">
+        <v>12026.37</v>
+      </c>
+    </row>
+    <row r="2128" spans="1:6">
+      <c r="A2128" s="2" t="s">
+        <v>2142</v>
+      </c>
+      <c r="B2128" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2128" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2128" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2128" s="2">
+        <v>4572.0600000000004</v>
+      </c>
+      <c r="F2128" s="2">
+        <v>10302.26</v>
+      </c>
+    </row>
+    <row r="2129" spans="1:6">
+      <c r="A2129" s="2" t="s">
+        <v>2143</v>
+      </c>
+      <c r="B2129" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2129" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2129" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2129" s="2">
+        <v>6854.65</v>
+      </c>
+      <c r="F2129" s="2">
+        <v>12458.06</v>
+      </c>
+    </row>
+    <row r="2130" spans="1:6">
+      <c r="A2130" s="2" t="s">
+        <v>2144</v>
+      </c>
+      <c r="B2130" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2130" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2130" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2130" s="2">
+        <v>6742.54</v>
+      </c>
+      <c r="F2130" s="2">
+        <v>13390.1</v>
+      </c>
+    </row>
+    <row r="2131" spans="1:6">
+      <c r="A2131" s="2" t="s">
+        <v>2145</v>
+      </c>
+      <c r="B2131" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2131" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2131" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2131" s="2">
+        <v>4592.22</v>
+      </c>
+      <c r="F2131" s="2">
+        <v>8387.07</v>
+      </c>
+    </row>
+    <row r="2132" spans="1:6">
+      <c r="A2132" s="2" t="s">
+        <v>2146</v>
+      </c>
+      <c r="B2132" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2132" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2132" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2132" s="2">
+        <v>6947.93</v>
+      </c>
+      <c r="F2132" s="2">
+        <v>12027.48</v>
+      </c>
+    </row>
+    <row r="2133" spans="1:6">
+      <c r="A2133" s="2" t="s">
+        <v>2147</v>
+      </c>
+      <c r="B2133" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2133" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2133" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2133" s="2">
+        <v>6229.86</v>
+      </c>
+      <c r="F2133" s="2">
+        <v>11456.03</v>
+      </c>
+    </row>
+    <row r="2134" spans="1:6">
+      <c r="A2134" s="2" t="s">
+        <v>2148</v>
+      </c>
+      <c r="B2134" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2134" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2134" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2134" s="2">
+        <v>5792.08</v>
+      </c>
+      <c r="F2134" s="2">
+        <v>10832.73</v>
+      </c>
+    </row>
+    <row r="2135" spans="1:6">
+      <c r="A2135" s="2" t="s">
+        <v>2149</v>
+      </c>
+      <c r="B2135" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2135" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2135" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2135" s="2">
+        <v>8222.65</v>
+      </c>
+      <c r="F2135" s="2">
+        <v>13158.48</v>
+      </c>
+    </row>
+    <row r="2136" spans="1:6">
+      <c r="A2136" s="2" t="s">
+        <v>2150</v>
+      </c>
+      <c r="B2136" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2136" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2136" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2136" s="2">
+        <v>4570.04</v>
+      </c>
+      <c r="F2136" s="2">
+        <v>9555.6200000000008</v>
+      </c>
+    </row>
+    <row r="2137" spans="1:6">
+      <c r="A2137" s="2" t="s">
+        <v>2151</v>
+      </c>
+      <c r="B2137" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2137" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2137" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2137" s="2">
+        <v>7668.59</v>
+      </c>
+      <c r="F2137" s="2">
+        <v>12378.55</v>
+      </c>
+    </row>
+    <row r="2138" spans="1:6">
+      <c r="A2138" s="2" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B2138" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2138" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2138" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2138" s="2">
+        <v>7257.84</v>
+      </c>
+      <c r="F2138" s="2">
+        <v>12471.23</v>
+      </c>
+    </row>
+    <row r="2139" spans="1:6">
+      <c r="A2139" s="2" t="s">
+        <v>2153</v>
+      </c>
+      <c r="B2139" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2139" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2139" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2139" s="2">
+        <v>7069.74</v>
+      </c>
+      <c r="F2139" s="2">
+        <v>12381.57</v>
+      </c>
+    </row>
+    <row r="2140" spans="1:6">
+      <c r="A2140" s="2" t="s">
+        <v>2154</v>
+      </c>
+      <c r="B2140" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2140" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2140" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2140" s="2">
+        <v>6753.52</v>
+      </c>
+      <c r="F2140" s="2">
+        <v>12277.56</v>
+      </c>
+    </row>
+    <row r="2141" spans="1:6">
+      <c r="A2141" s="2" t="s">
+        <v>2155</v>
+      </c>
+      <c r="B2141" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2141" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2141" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2141" s="2">
+        <v>6693.88</v>
+      </c>
+      <c r="F2141" s="2">
+        <v>13061.33</v>
+      </c>
+    </row>
+    <row r="2142" spans="1:6">
+      <c r="A2142" s="2" t="s">
+        <v>2156</v>
+      </c>
+      <c r="B2142" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2142" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2142" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2142" s="2">
+        <v>6941.4</v>
+      </c>
+      <c r="F2142" s="2">
+        <v>13772.49</v>
+      </c>
+    </row>
+    <row r="2143" spans="1:6">
+      <c r="A2143" s="2" t="s">
+        <v>2157</v>
+      </c>
+      <c r="B2143" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2143" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2143" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2143" s="2">
+        <v>5834.65</v>
+      </c>
+      <c r="F2143" s="2">
+        <v>10640.08</v>
+      </c>
+    </row>
+    <row r="2144" spans="1:6">
+      <c r="A2144" s="2" t="s">
+        <v>2158</v>
+      </c>
+      <c r="B2144" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2144" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2144" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2144" s="2">
+        <v>6445.02</v>
+      </c>
+      <c r="F2144" s="2">
+        <v>12261.65</v>
+      </c>
+    </row>
+    <row r="2145" spans="1:6">
+      <c r="A2145" s="2" t="s">
+        <v>2159</v>
+      </c>
+      <c r="B2145" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2145" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2145" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2145" s="2">
+        <v>8071.95</v>
+      </c>
+      <c r="F2145" s="2">
+        <v>12929.11</v>
+      </c>
+    </row>
+    <row r="2146" spans="1:6">
+      <c r="A2146" s="2" t="s">
+        <v>2160</v>
+      </c>
+      <c r="B2146" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2146" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2146" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2146" s="2">
+        <v>6310.41</v>
+      </c>
+      <c r="F2146" s="2">
+        <v>13143.17</v>
+      </c>
+    </row>
+    <row r="2147" spans="1:6">
+      <c r="A2147" s="2" t="s">
+        <v>2161</v>
+      </c>
+      <c r="B2147" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2147" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2147" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2147" s="2">
+        <v>6856.66</v>
+      </c>
+      <c r="F2147" s="2">
+        <v>12459.95</v>
+      </c>
+    </row>
+    <row r="2148" spans="1:6">
+      <c r="A2148" s="2" t="s">
+        <v>2162</v>
+      </c>
+      <c r="B2148" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2148" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2148" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2148" s="2">
+        <v>5508.44</v>
+      </c>
+      <c r="F2148" s="2">
+        <v>12096.91</v>
+      </c>
+    </row>
+    <row r="2149" spans="1:6">
+      <c r="A2149" s="2" t="s">
+        <v>2163</v>
+      </c>
+      <c r="B2149" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2149" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2149" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2149" s="2">
+        <v>4915.59</v>
+      </c>
+      <c r="F2149" s="2">
+        <v>10410.200000000001</v>
+      </c>
+    </row>
+    <row r="2150" spans="1:6">
+      <c r="A2150" s="2" t="s">
+        <v>2164</v>
+      </c>
+      <c r="B2150" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2150" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2150" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2150" s="2">
+        <v>6920.03</v>
+      </c>
+      <c r="F2150" s="2">
+        <v>12605.93</v>
+      </c>
+    </row>
+    <row r="2151" spans="1:6">
+      <c r="A2151" s="2" t="s">
+        <v>2165</v>
+      </c>
+      <c r="B2151" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2151" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2151" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2151" s="2">
+        <v>8207.0499999999993</v>
+      </c>
+      <c r="F2151" s="2">
+        <v>14999.67</v>
+      </c>
+    </row>
+    <row r="2152" spans="1:6">
+      <c r="A2152" s="2" t="s">
+        <v>2166</v>
+      </c>
+      <c r="B2152" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2152" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2152" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2152" s="2">
+        <v>4211.29</v>
+      </c>
+      <c r="F2152" s="2">
+        <v>10135.51</v>
+      </c>
+    </row>
+    <row r="2153" spans="1:6">
+      <c r="A2153" s="2" t="s">
+        <v>2167</v>
+      </c>
+      <c r="B2153" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2153" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2153" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2153" s="2">
+        <v>3867.72</v>
+      </c>
+      <c r="F2153" s="2">
+        <v>8563.08</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/NGO_Project_MNE_Dataset_2000.xlsx
+++ b/NGO_Project_MNE_Dataset_2000.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8614" uniqueCount="2168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8618" uniqueCount="2169">
   <si>
     <t>Beneficiary ID</t>
   </si>
@@ -6521,6 +6521,9 @@
   </si>
   <si>
     <t>B-2152</t>
+  </si>
+  <si>
+    <t>B-2153</t>
   </si>
 </sst>
 </file>
@@ -6854,7 +6857,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2153"/>
+  <dimension ref="A1:F2154"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -49917,6 +49920,26 @@
         <v>8563.08</v>
       </c>
     </row>
+    <row r="2154" spans="1:6" s="2" customFormat="1">
+      <c r="A2154" s="2" t="s">
+        <v>2168</v>
+      </c>
+      <c r="B2154" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2154" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2154" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2154" s="2">
+        <v>7466.55</v>
+      </c>
+      <c r="F2154" s="2">
+        <v>12362.08</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/NGO_Project_MNE_Dataset_2000.xlsx
+++ b/NGO_Project_MNE_Dataset_2000.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="150" yWindow="525" windowWidth="15015" windowHeight="7365"/>
@@ -10,14 +10,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$2153</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$2154</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8618" uniqueCount="2169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9078" uniqueCount="2284">
   <si>
     <t>Beneficiary ID</t>
   </si>
@@ -6524,6 +6524,351 @@
   </si>
   <si>
     <t>B-2153</t>
+  </si>
+  <si>
+    <t>B-2154</t>
+  </si>
+  <si>
+    <t>B-2155</t>
+  </si>
+  <si>
+    <t>B-2156</t>
+  </si>
+  <si>
+    <t>B-2157</t>
+  </si>
+  <si>
+    <t>B-2158</t>
+  </si>
+  <si>
+    <t>B-2159</t>
+  </si>
+  <si>
+    <t>B-2160</t>
+  </si>
+  <si>
+    <t>B-2161</t>
+  </si>
+  <si>
+    <t>B-2162</t>
+  </si>
+  <si>
+    <t>B-2163</t>
+  </si>
+  <si>
+    <t>B-2164</t>
+  </si>
+  <si>
+    <t>B-2165</t>
+  </si>
+  <si>
+    <t>B-2166</t>
+  </si>
+  <si>
+    <t>B-2167</t>
+  </si>
+  <si>
+    <t>B-2168</t>
+  </si>
+  <si>
+    <t>B-2169</t>
+  </si>
+  <si>
+    <t>B-2170</t>
+  </si>
+  <si>
+    <t>B-2171</t>
+  </si>
+  <si>
+    <t>B-2172</t>
+  </si>
+  <si>
+    <t>B-2173</t>
+  </si>
+  <si>
+    <t>B-2174</t>
+  </si>
+  <si>
+    <t>B-2175</t>
+  </si>
+  <si>
+    <t>B-2176</t>
+  </si>
+  <si>
+    <t>B-2177</t>
+  </si>
+  <si>
+    <t>B-2178</t>
+  </si>
+  <si>
+    <t>B-2179</t>
+  </si>
+  <si>
+    <t>B-2180</t>
+  </si>
+  <si>
+    <t>B-2181</t>
+  </si>
+  <si>
+    <t>B-2182</t>
+  </si>
+  <si>
+    <t>B-2183</t>
+  </si>
+  <si>
+    <t>B-2184</t>
+  </si>
+  <si>
+    <t>B-2185</t>
+  </si>
+  <si>
+    <t>B-2186</t>
+  </si>
+  <si>
+    <t>B-2187</t>
+  </si>
+  <si>
+    <t>B-2188</t>
+  </si>
+  <si>
+    <t>B-2189</t>
+  </si>
+  <si>
+    <t>B-2190</t>
+  </si>
+  <si>
+    <t>B-2191</t>
+  </si>
+  <si>
+    <t>B-2192</t>
+  </si>
+  <si>
+    <t>B-2193</t>
+  </si>
+  <si>
+    <t>B-2194</t>
+  </si>
+  <si>
+    <t>B-2195</t>
+  </si>
+  <si>
+    <t>B-2196</t>
+  </si>
+  <si>
+    <t>B-2197</t>
+  </si>
+  <si>
+    <t>B-2198</t>
+  </si>
+  <si>
+    <t>B-2199</t>
+  </si>
+  <si>
+    <t>B-2200</t>
+  </si>
+  <si>
+    <t>B-2201</t>
+  </si>
+  <si>
+    <t>B-2202</t>
+  </si>
+  <si>
+    <t>B-2203</t>
+  </si>
+  <si>
+    <t>B-2204</t>
+  </si>
+  <si>
+    <t>B-2205</t>
+  </si>
+  <si>
+    <t>B-2206</t>
+  </si>
+  <si>
+    <t>B-2207</t>
+  </si>
+  <si>
+    <t>B-2208</t>
+  </si>
+  <si>
+    <t>B-2209</t>
+  </si>
+  <si>
+    <t>B-2210</t>
+  </si>
+  <si>
+    <t>B-2211</t>
+  </si>
+  <si>
+    <t>B-2212</t>
+  </si>
+  <si>
+    <t>B-2213</t>
+  </si>
+  <si>
+    <t>B-2214</t>
+  </si>
+  <si>
+    <t>B-2215</t>
+  </si>
+  <si>
+    <t>B-2216</t>
+  </si>
+  <si>
+    <t>B-2217</t>
+  </si>
+  <si>
+    <t>B-2218</t>
+  </si>
+  <si>
+    <t>B-2219</t>
+  </si>
+  <si>
+    <t>B-2220</t>
+  </si>
+  <si>
+    <t>B-2221</t>
+  </si>
+  <si>
+    <t>B-2222</t>
+  </si>
+  <si>
+    <t>B-2223</t>
+  </si>
+  <si>
+    <t>B-2224</t>
+  </si>
+  <si>
+    <t>B-2225</t>
+  </si>
+  <si>
+    <t>B-2226</t>
+  </si>
+  <si>
+    <t>B-2227</t>
+  </si>
+  <si>
+    <t>B-2228</t>
+  </si>
+  <si>
+    <t>B-2229</t>
+  </si>
+  <si>
+    <t>B-2230</t>
+  </si>
+  <si>
+    <t>B-2231</t>
+  </si>
+  <si>
+    <t>B-2232</t>
+  </si>
+  <si>
+    <t>B-2233</t>
+  </si>
+  <si>
+    <t>B-2234</t>
+  </si>
+  <si>
+    <t>B-2235</t>
+  </si>
+  <si>
+    <t>B-2236</t>
+  </si>
+  <si>
+    <t>B-2237</t>
+  </si>
+  <si>
+    <t>B-2238</t>
+  </si>
+  <si>
+    <t>B-2239</t>
+  </si>
+  <si>
+    <t>B-2240</t>
+  </si>
+  <si>
+    <t>B-2241</t>
+  </si>
+  <si>
+    <t>B-2242</t>
+  </si>
+  <si>
+    <t>B-2243</t>
+  </si>
+  <si>
+    <t>B-2244</t>
+  </si>
+  <si>
+    <t>B-2245</t>
+  </si>
+  <si>
+    <t>B-2246</t>
+  </si>
+  <si>
+    <t>B-2247</t>
+  </si>
+  <si>
+    <t>B-2248</t>
+  </si>
+  <si>
+    <t>B-2249</t>
+  </si>
+  <si>
+    <t>B-2250</t>
+  </si>
+  <si>
+    <t>B-2251</t>
+  </si>
+  <si>
+    <t>B-2252</t>
+  </si>
+  <si>
+    <t>B-2253</t>
+  </si>
+  <si>
+    <t>B-2254</t>
+  </si>
+  <si>
+    <t>B-2255</t>
+  </si>
+  <si>
+    <t>B-2256</t>
+  </si>
+  <si>
+    <t>B-2257</t>
+  </si>
+  <si>
+    <t>B-2258</t>
+  </si>
+  <si>
+    <t>B-2259</t>
+  </si>
+  <si>
+    <t>B-2260</t>
+  </si>
+  <si>
+    <t>B-2261</t>
+  </si>
+  <si>
+    <t>B-2262</t>
+  </si>
+  <si>
+    <t>B-2263</t>
+  </si>
+  <si>
+    <t>B-2264</t>
+  </si>
+  <si>
+    <t>B-2265</t>
+  </si>
+  <si>
+    <t>B-2266</t>
+  </si>
+  <si>
+    <t>B-2267</t>
+  </si>
+  <si>
+    <t>B-2268</t>
   </si>
 </sst>
 </file>
@@ -6857,7 +7202,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2154"/>
+  <dimension ref="A1:F2269"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -49940,6 +50285,2306 @@
         <v>12362.08</v>
       </c>
     </row>
+    <row r="2155" spans="1:6">
+      <c r="A2155" s="2" t="s">
+        <v>2169</v>
+      </c>
+      <c r="B2155" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2155" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2155" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2155" s="2">
+        <v>6426.34</v>
+      </c>
+      <c r="F2155" s="2">
+        <v>12792.5</v>
+      </c>
+    </row>
+    <row r="2156" spans="1:6">
+      <c r="A2156" s="2" t="s">
+        <v>2170</v>
+      </c>
+      <c r="B2156" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2156" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2156" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2156" s="2">
+        <v>7466.55</v>
+      </c>
+      <c r="F2156" s="2">
+        <v>12362.08</v>
+      </c>
+    </row>
+    <row r="2157" spans="1:6">
+      <c r="A2157" s="2" t="s">
+        <v>2171</v>
+      </c>
+      <c r="B2157" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2157" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2157" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2157" s="2">
+        <v>6448.65</v>
+      </c>
+      <c r="F2157" s="2">
+        <v>10368.799999999999</v>
+      </c>
+    </row>
+    <row r="2158" spans="1:6">
+      <c r="A2158" s="2" t="s">
+        <v>2172</v>
+      </c>
+      <c r="B2158" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2158" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2158" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2158" s="2">
+        <v>4634.24</v>
+      </c>
+      <c r="F2158" s="2">
+        <v>10111.25</v>
+      </c>
+    </row>
+    <row r="2159" spans="1:6">
+      <c r="A2159" s="2" t="s">
+        <v>2173</v>
+      </c>
+      <c r="B2159" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2159" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2159" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2159" s="2">
+        <v>5744.12</v>
+      </c>
+      <c r="F2159" s="2">
+        <v>11472.96</v>
+      </c>
+    </row>
+    <row r="2160" spans="1:6">
+      <c r="A2160" s="2" t="s">
+        <v>2174</v>
+      </c>
+      <c r="B2160" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2160" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2160" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2160" s="2">
+        <v>6396.62</v>
+      </c>
+      <c r="F2160" s="2">
+        <v>12090.16</v>
+      </c>
+    </row>
+    <row r="2161" spans="1:6">
+      <c r="A2161" s="2" t="s">
+        <v>2175</v>
+      </c>
+      <c r="B2161" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2161" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2161" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2161" s="2">
+        <v>5692.85</v>
+      </c>
+      <c r="F2161" s="2">
+        <v>10925.52</v>
+      </c>
+    </row>
+    <row r="2162" spans="1:6">
+      <c r="A2162" s="2" t="s">
+        <v>2176</v>
+      </c>
+      <c r="B2162" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2162" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2162" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2162" s="2">
+        <v>5975.93</v>
+      </c>
+      <c r="F2162" s="2">
+        <v>11569.74</v>
+      </c>
+    </row>
+    <row r="2163" spans="1:6">
+      <c r="A2163" s="2" t="s">
+        <v>2177</v>
+      </c>
+      <c r="B2163" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2163" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2163" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2163" s="2">
+        <v>6128.63</v>
+      </c>
+      <c r="F2163" s="2">
+        <v>12835</v>
+      </c>
+    </row>
+    <row r="2164" spans="1:6">
+      <c r="A2164" s="2" t="s">
+        <v>2178</v>
+      </c>
+      <c r="B2164" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2164" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2164" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2164" s="2">
+        <v>6141.26</v>
+      </c>
+      <c r="F2164" s="2">
+        <v>11940.66</v>
+      </c>
+    </row>
+    <row r="2165" spans="1:6">
+      <c r="A2165" s="2" t="s">
+        <v>2179</v>
+      </c>
+      <c r="B2165" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2165" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2165" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2165" s="2">
+        <v>6301.02</v>
+      </c>
+      <c r="F2165" s="2">
+        <v>11496.34</v>
+      </c>
+    </row>
+    <row r="2166" spans="1:6">
+      <c r="A2166" s="2" t="s">
+        <v>2180</v>
+      </c>
+      <c r="B2166" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2166" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2166" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2166" s="2">
+        <v>4965.58</v>
+      </c>
+      <c r="F2166" s="2">
+        <v>10059.43</v>
+      </c>
+    </row>
+    <row r="2167" spans="1:6">
+      <c r="A2167" s="2" t="s">
+        <v>2181</v>
+      </c>
+      <c r="B2167" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2167" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2167" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2167" s="2">
+        <v>5377.89</v>
+      </c>
+      <c r="F2167" s="2">
+        <v>10736.02</v>
+      </c>
+    </row>
+    <row r="2168" spans="1:6">
+      <c r="A2168" s="2" t="s">
+        <v>2182</v>
+      </c>
+      <c r="B2168" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2168" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2168" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2168" s="2">
+        <v>4696.8100000000004</v>
+      </c>
+      <c r="F2168" s="2">
+        <v>11500.21</v>
+      </c>
+    </row>
+    <row r="2169" spans="1:6">
+      <c r="A2169" s="2" t="s">
+        <v>2183</v>
+      </c>
+      <c r="B2169" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2169" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2169" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2169" s="2">
+        <v>7411.69</v>
+      </c>
+      <c r="F2169" s="2">
+        <v>12759.06</v>
+      </c>
+    </row>
+    <row r="2170" spans="1:6">
+      <c r="A2170" s="2" t="s">
+        <v>2184</v>
+      </c>
+      <c r="B2170" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2170" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2170" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2170" s="2">
+        <v>3711.53</v>
+      </c>
+      <c r="F2170" s="2">
+        <v>9189.7000000000007</v>
+      </c>
+    </row>
+    <row r="2171" spans="1:6">
+      <c r="A2171" s="2" t="s">
+        <v>2185</v>
+      </c>
+      <c r="B2171" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2171" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2171" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2171" s="2">
+        <v>7622.62</v>
+      </c>
+      <c r="F2171" s="2">
+        <v>12730.78</v>
+      </c>
+    </row>
+    <row r="2172" spans="1:6">
+      <c r="A2172" s="2" t="s">
+        <v>2186</v>
+      </c>
+      <c r="B2172" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2172" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2172" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2172" s="2">
+        <v>7901.93</v>
+      </c>
+      <c r="F2172" s="2">
+        <v>14275.13</v>
+      </c>
+    </row>
+    <row r="2173" spans="1:6">
+      <c r="A2173" s="2" t="s">
+        <v>2187</v>
+      </c>
+      <c r="B2173" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2173" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2173" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2173" s="2">
+        <v>5875.69</v>
+      </c>
+      <c r="F2173" s="2">
+        <v>12937.57</v>
+      </c>
+    </row>
+    <row r="2174" spans="1:6">
+      <c r="A2174" s="2" t="s">
+        <v>2188</v>
+      </c>
+      <c r="B2174" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2174" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2174" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2174" s="2">
+        <v>3500</v>
+      </c>
+      <c r="F2174" s="2">
+        <v>9354.5</v>
+      </c>
+    </row>
+    <row r="2175" spans="1:6">
+      <c r="A2175" s="2" t="s">
+        <v>2189</v>
+      </c>
+      <c r="B2175" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2175" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2175" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2175" s="2">
+        <v>5804.74</v>
+      </c>
+      <c r="F2175" s="2">
+        <v>11364.97</v>
+      </c>
+    </row>
+    <row r="2176" spans="1:6">
+      <c r="A2176" s="2" t="s">
+        <v>2190</v>
+      </c>
+      <c r="B2176" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2176" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2176" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2176" s="2">
+        <v>6161.29</v>
+      </c>
+      <c r="F2176" s="2">
+        <v>11684.73</v>
+      </c>
+    </row>
+    <row r="2177" spans="1:6">
+      <c r="A2177" s="2" t="s">
+        <v>2191</v>
+      </c>
+      <c r="B2177" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2177" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2177" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2177" s="2">
+        <v>5025.59</v>
+      </c>
+      <c r="F2177" s="2">
+        <v>8612.15</v>
+      </c>
+    </row>
+    <row r="2178" spans="1:6">
+      <c r="A2178" s="2" t="s">
+        <v>2192</v>
+      </c>
+      <c r="B2178" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2178" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2178" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2178" s="2">
+        <v>5620.05</v>
+      </c>
+      <c r="F2178" s="2">
+        <v>11710.18</v>
+      </c>
+    </row>
+    <row r="2179" spans="1:6">
+      <c r="A2179" s="2" t="s">
+        <v>2193</v>
+      </c>
+      <c r="B2179" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2179" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2179" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2179" s="2">
+        <v>8074.54</v>
+      </c>
+      <c r="F2179" s="2">
+        <v>13675.88</v>
+      </c>
+    </row>
+    <row r="2180" spans="1:6">
+      <c r="A2180" s="2" t="s">
+        <v>2194</v>
+      </c>
+      <c r="B2180" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2180" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2180" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2180" s="2">
+        <v>7036.22</v>
+      </c>
+      <c r="F2180" s="2">
+        <v>12872.9</v>
+      </c>
+    </row>
+    <row r="2181" spans="1:6">
+      <c r="A2181" s="2" t="s">
+        <v>2195</v>
+      </c>
+      <c r="B2181" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2181" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2181" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2181" s="2">
+        <v>5128.83</v>
+      </c>
+      <c r="F2181" s="2">
+        <v>10053.67</v>
+      </c>
+    </row>
+    <row r="2182" spans="1:6">
+      <c r="A2182" s="2" t="s">
+        <v>2196</v>
+      </c>
+      <c r="B2182" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2182" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2182" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2182" s="2">
+        <v>4321.1899999999996</v>
+      </c>
+      <c r="F2182" s="2">
+        <v>9507.6299999999992</v>
+      </c>
+    </row>
+    <row r="2183" spans="1:6">
+      <c r="A2183" s="2" t="s">
+        <v>2197</v>
+      </c>
+      <c r="B2183" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2183" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2183" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2183" s="2">
+        <v>5845.89</v>
+      </c>
+      <c r="F2183" s="2">
+        <v>11011.08</v>
+      </c>
+    </row>
+    <row r="2184" spans="1:6">
+      <c r="A2184" s="2" t="s">
+        <v>2198</v>
+      </c>
+      <c r="B2184" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2184" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2184" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2184" s="2">
+        <v>5982.16</v>
+      </c>
+      <c r="F2184" s="2">
+        <v>12293.47</v>
+      </c>
+    </row>
+    <row r="2185" spans="1:6">
+      <c r="A2185" s="2" t="s">
+        <v>2199</v>
+      </c>
+      <c r="B2185" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2185" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2185" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2185" s="2">
+        <v>6833.75</v>
+      </c>
+      <c r="F2185" s="2">
+        <v>12024.75</v>
+      </c>
+    </row>
+    <row r="2186" spans="1:6">
+      <c r="A2186" s="2" t="s">
+        <v>2200</v>
+      </c>
+      <c r="B2186" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2186" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2186" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2186" s="2">
+        <v>5595.93</v>
+      </c>
+      <c r="F2186" s="2">
+        <v>12756.07</v>
+      </c>
+    </row>
+    <row r="2187" spans="1:6">
+      <c r="A2187" s="2" t="s">
+        <v>2201</v>
+      </c>
+      <c r="B2187" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2187" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2187" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2187" s="2">
+        <v>6852.11</v>
+      </c>
+      <c r="F2187" s="2">
+        <v>12690.81</v>
+      </c>
+    </row>
+    <row r="2188" spans="1:6">
+      <c r="A2188" s="2" t="s">
+        <v>2202</v>
+      </c>
+      <c r="B2188" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2188" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2188" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2188" s="2">
+        <v>8560.49</v>
+      </c>
+      <c r="F2188" s="2">
+        <v>13033.95</v>
+      </c>
+    </row>
+    <row r="2189" spans="1:6">
+      <c r="A2189" s="2" t="s">
+        <v>2203</v>
+      </c>
+      <c r="B2189" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2189" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2189" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2189" s="2">
+        <v>7216.91</v>
+      </c>
+      <c r="F2189" s="2">
+        <v>12608.08</v>
+      </c>
+    </row>
+    <row r="2190" spans="1:6">
+      <c r="A2190" s="2" t="s">
+        <v>2204</v>
+      </c>
+      <c r="B2190" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2190" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2190" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2190" s="2">
+        <v>6180.6</v>
+      </c>
+      <c r="F2190" s="2">
+        <v>11153.27</v>
+      </c>
+    </row>
+    <row r="2191" spans="1:6">
+      <c r="A2191" s="2" t="s">
+        <v>2205</v>
+      </c>
+      <c r="B2191" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2191" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2191" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2191" s="2">
+        <v>6018.53</v>
+      </c>
+      <c r="F2191" s="2">
+        <v>9757.0300000000007</v>
+      </c>
+    </row>
+    <row r="2192" spans="1:6">
+      <c r="A2192" s="2" t="s">
+        <v>2206</v>
+      </c>
+      <c r="B2192" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2192" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2192" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2192" s="2">
+        <v>5810.3</v>
+      </c>
+      <c r="F2192" s="2">
+        <v>12583.89</v>
+      </c>
+    </row>
+    <row r="2193" spans="1:6">
+      <c r="A2193" s="2" t="s">
+        <v>2207</v>
+      </c>
+      <c r="B2193" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2193" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2193" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2193" s="2">
+        <v>7655.08</v>
+      </c>
+      <c r="F2193" s="2">
+        <v>13711.6</v>
+      </c>
+    </row>
+    <row r="2194" spans="1:6">
+      <c r="A2194" s="2" t="s">
+        <v>2208</v>
+      </c>
+      <c r="B2194" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2194" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2194" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2194" s="2">
+        <v>5485.53</v>
+      </c>
+      <c r="F2194" s="2">
+        <v>11406.11</v>
+      </c>
+    </row>
+    <row r="2195" spans="1:6">
+      <c r="A2195" s="2" t="s">
+        <v>2209</v>
+      </c>
+      <c r="B2195" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2195" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2195" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2195" s="2">
+        <v>6292.58</v>
+      </c>
+      <c r="F2195" s="2">
+        <v>11918.91</v>
+      </c>
+    </row>
+    <row r="2196" spans="1:6">
+      <c r="A2196" s="2" t="s">
+        <v>2210</v>
+      </c>
+      <c r="B2196" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2196" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2196" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2196" s="2">
+        <v>6299.75</v>
+      </c>
+      <c r="F2196" s="2">
+        <v>10688.15</v>
+      </c>
+    </row>
+    <row r="2197" spans="1:6">
+      <c r="A2197" s="2" t="s">
+        <v>2211</v>
+      </c>
+      <c r="B2197" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2197" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2197" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2197" s="2">
+        <v>5636.17</v>
+      </c>
+      <c r="F2197" s="2">
+        <v>10743.29</v>
+      </c>
+    </row>
+    <row r="2198" spans="1:6">
+      <c r="A2198" s="2" t="s">
+        <v>2212</v>
+      </c>
+      <c r="B2198" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2198" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2198" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2198" s="2">
+        <v>4591.3500000000004</v>
+      </c>
+      <c r="F2198" s="2">
+        <v>10758.78</v>
+      </c>
+    </row>
+    <row r="2199" spans="1:6">
+      <c r="A2199" s="2" t="s">
+        <v>2213</v>
+      </c>
+      <c r="B2199" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2199" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2199" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2199" s="2">
+        <v>6625.88</v>
+      </c>
+      <c r="F2199" s="2">
+        <v>11278.91</v>
+      </c>
+    </row>
+    <row r="2200" spans="1:6">
+      <c r="A2200" s="2" t="s">
+        <v>2214</v>
+      </c>
+      <c r="B2200" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2200" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2200" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2200" s="2">
+        <v>6165.11</v>
+      </c>
+      <c r="F2200" s="2">
+        <v>9633.7000000000007</v>
+      </c>
+    </row>
+    <row r="2201" spans="1:6">
+      <c r="A2201" s="2" t="s">
+        <v>2215</v>
+      </c>
+      <c r="B2201" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2201" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2201" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2201" s="2">
+        <v>6838.6</v>
+      </c>
+      <c r="F2201" s="2">
+        <v>12150.93</v>
+      </c>
+    </row>
+    <row r="2202" spans="1:6">
+      <c r="A2202" s="2" t="s">
+        <v>2216</v>
+      </c>
+      <c r="B2202" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2202" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2202" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2202" s="2">
+        <v>5597.99</v>
+      </c>
+      <c r="F2202" s="2">
+        <v>10978.59</v>
+      </c>
+    </row>
+    <row r="2203" spans="1:6">
+      <c r="A2203" s="2" t="s">
+        <v>2217</v>
+      </c>
+      <c r="B2203" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2203" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2203" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2203" s="2">
+        <v>7703.3</v>
+      </c>
+      <c r="F2203" s="2">
+        <v>13305.76</v>
+      </c>
+    </row>
+    <row r="2204" spans="1:6">
+      <c r="A2204" s="2" t="s">
+        <v>2218</v>
+      </c>
+      <c r="B2204" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2204" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2204" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2204" s="2">
+        <v>5186.18</v>
+      </c>
+      <c r="F2204" s="2">
+        <v>11263</v>
+      </c>
+    </row>
+    <row r="2205" spans="1:6">
+      <c r="A2205" s="2" t="s">
+        <v>2219</v>
+      </c>
+      <c r="B2205" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2205" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2205" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2205" s="2">
+        <v>8292.76</v>
+      </c>
+      <c r="F2205" s="2">
+        <v>14296.85</v>
+      </c>
+    </row>
+    <row r="2206" spans="1:6">
+      <c r="A2206" s="2" t="s">
+        <v>2220</v>
+      </c>
+      <c r="B2206" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2206" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2206" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2206" s="2">
+        <v>4141.1499999999996</v>
+      </c>
+      <c r="F2206" s="2">
+        <v>9842.18</v>
+      </c>
+    </row>
+    <row r="2207" spans="1:6">
+      <c r="A2207" s="2" t="s">
+        <v>2221</v>
+      </c>
+      <c r="B2207" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2207" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2207" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2207" s="2">
+        <v>6760.03</v>
+      </c>
+      <c r="F2207" s="2">
+        <v>13210.47</v>
+      </c>
+    </row>
+    <row r="2208" spans="1:6">
+      <c r="A2208" s="2" t="s">
+        <v>2222</v>
+      </c>
+      <c r="B2208" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2208" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2208" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2208" s="2">
+        <v>6808.83</v>
+      </c>
+      <c r="F2208" s="2">
+        <v>11087.66</v>
+      </c>
+    </row>
+    <row r="2209" spans="1:6">
+      <c r="A2209" s="2" t="s">
+        <v>2223</v>
+      </c>
+      <c r="B2209" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2209" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2209" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2209" s="2">
+        <v>5283.64</v>
+      </c>
+      <c r="F2209" s="2">
+        <v>11181.32</v>
+      </c>
+    </row>
+    <row r="2210" spans="1:6">
+      <c r="A2210" s="2" t="s">
+        <v>2224</v>
+      </c>
+      <c r="B2210" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2210" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2210" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2210" s="2">
+        <v>6747.58</v>
+      </c>
+      <c r="F2210" s="2">
+        <v>12742.82</v>
+      </c>
+    </row>
+    <row r="2211" spans="1:6">
+      <c r="A2211" s="2" t="s">
+        <v>2225</v>
+      </c>
+      <c r="B2211" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2211" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2211" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2211" s="2">
+        <v>7773.73</v>
+      </c>
+      <c r="F2211" s="2">
+        <v>12276.09</v>
+      </c>
+    </row>
+    <row r="2212" spans="1:6">
+      <c r="A2212" s="2" t="s">
+        <v>2226</v>
+      </c>
+      <c r="B2212" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2212" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2212" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2212" s="2">
+        <v>3578.13</v>
+      </c>
+      <c r="F2212" s="2">
+        <v>7869.84</v>
+      </c>
+    </row>
+    <row r="2213" spans="1:6">
+      <c r="A2213" s="2" t="s">
+        <v>2227</v>
+      </c>
+      <c r="B2213" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2213" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2213" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2213" s="2">
+        <v>6841.6</v>
+      </c>
+      <c r="F2213" s="2">
+        <v>11738.86</v>
+      </c>
+    </row>
+    <row r="2214" spans="1:6">
+      <c r="A2214" s="2" t="s">
+        <v>2228</v>
+      </c>
+      <c r="B2214" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2214" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2214" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2214" s="2">
+        <v>3500</v>
+      </c>
+      <c r="F2214" s="2">
+        <v>8464.7800000000007</v>
+      </c>
+    </row>
+    <row r="2215" spans="1:6">
+      <c r="A2215" s="2" t="s">
+        <v>2229</v>
+      </c>
+      <c r="B2215" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2215" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2215" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2215" s="2">
+        <v>5079.51</v>
+      </c>
+      <c r="F2215" s="2">
+        <v>11176.26</v>
+      </c>
+    </row>
+    <row r="2216" spans="1:6">
+      <c r="A2216" s="2" t="s">
+        <v>2230</v>
+      </c>
+      <c r="B2216" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2216" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2216" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2216" s="2">
+        <v>8193.31</v>
+      </c>
+      <c r="F2216" s="2">
+        <v>13195.69</v>
+      </c>
+    </row>
+    <row r="2217" spans="1:6">
+      <c r="A2217" s="2" t="s">
+        <v>2231</v>
+      </c>
+      <c r="B2217" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2217" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2217" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2217" s="2">
+        <v>5540.17</v>
+      </c>
+      <c r="F2217" s="2">
+        <v>10349.1</v>
+      </c>
+    </row>
+    <row r="2218" spans="1:6">
+      <c r="A2218" s="2" t="s">
+        <v>2232</v>
+      </c>
+      <c r="B2218" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2218" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2218" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2218" s="2">
+        <v>4829.6499999999996</v>
+      </c>
+      <c r="F2218" s="2">
+        <v>9834.35</v>
+      </c>
+    </row>
+    <row r="2219" spans="1:6">
+      <c r="A2219" s="2" t="s">
+        <v>2233</v>
+      </c>
+      <c r="B2219" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2219" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2219" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2219" s="2">
+        <v>6000.78</v>
+      </c>
+      <c r="F2219" s="2">
+        <v>12389.7</v>
+      </c>
+    </row>
+    <row r="2220" spans="1:6">
+      <c r="A2220" s="2" t="s">
+        <v>2234</v>
+      </c>
+      <c r="B2220" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2220" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2220" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2220" s="2">
+        <v>8719.7999999999993</v>
+      </c>
+      <c r="F2220" s="2">
+        <v>14224.24</v>
+      </c>
+    </row>
+    <row r="2221" spans="1:6">
+      <c r="A2221" s="2" t="s">
+        <v>2235</v>
+      </c>
+      <c r="B2221" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2221" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2221" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2221" s="2">
+        <v>4040.29</v>
+      </c>
+      <c r="F2221" s="2">
+        <v>9390.9</v>
+      </c>
+    </row>
+    <row r="2222" spans="1:6">
+      <c r="A2222" s="2" t="s">
+        <v>2236</v>
+      </c>
+      <c r="B2222" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2222" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2222" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2222" s="2">
+        <v>4976.74</v>
+      </c>
+      <c r="F2222" s="2">
+        <v>10382.75</v>
+      </c>
+    </row>
+    <row r="2223" spans="1:6">
+      <c r="A2223" s="2" t="s">
+        <v>2237</v>
+      </c>
+      <c r="B2223" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2223" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2223" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2223" s="2">
+        <v>8035.23</v>
+      </c>
+      <c r="F2223" s="2">
+        <v>14562.89</v>
+      </c>
+    </row>
+    <row r="2224" spans="1:6">
+      <c r="A2224" s="2" t="s">
+        <v>2238</v>
+      </c>
+      <c r="B2224" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2224" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2224" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2224" s="2">
+        <v>8467.5499999999993</v>
+      </c>
+      <c r="F2224" s="2">
+        <v>13362.22</v>
+      </c>
+    </row>
+    <row r="2225" spans="1:6">
+      <c r="A2225" s="2" t="s">
+        <v>2239</v>
+      </c>
+      <c r="B2225" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2225" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2225" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2225" s="2">
+        <v>6114.19</v>
+      </c>
+      <c r="F2225" s="2">
+        <v>12660.61</v>
+      </c>
+    </row>
+    <row r="2226" spans="1:6">
+      <c r="A2226" s="2" t="s">
+        <v>2240</v>
+      </c>
+      <c r="B2226" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2226" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2226" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2226" s="2">
+        <v>4751.45</v>
+      </c>
+      <c r="F2226" s="2">
+        <v>10413.86</v>
+      </c>
+    </row>
+    <row r="2227" spans="1:6">
+      <c r="A2227" s="2" t="s">
+        <v>2241</v>
+      </c>
+      <c r="B2227" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2227" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2227" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2227" s="2">
+        <v>8753.32</v>
+      </c>
+      <c r="F2227" s="2">
+        <v>14118.99</v>
+      </c>
+    </row>
+    <row r="2228" spans="1:6">
+      <c r="A2228" s="2" t="s">
+        <v>2242</v>
+      </c>
+      <c r="B2228" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2228" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2228" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2228" s="2">
+        <v>8151.64</v>
+      </c>
+      <c r="F2228" s="2">
+        <v>15646.37</v>
+      </c>
+    </row>
+    <row r="2229" spans="1:6">
+      <c r="A2229" s="2" t="s">
+        <v>2243</v>
+      </c>
+      <c r="B2229" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2229" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2229" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2229" s="2">
+        <v>7053.05</v>
+      </c>
+      <c r="F2229" s="2">
+        <v>11702.55</v>
+      </c>
+    </row>
+    <row r="2230" spans="1:6">
+      <c r="A2230" s="2" t="s">
+        <v>2244</v>
+      </c>
+      <c r="B2230" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2230" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2230" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2230" s="2">
+        <v>5263.43</v>
+      </c>
+      <c r="F2230" s="2">
+        <v>10474.49</v>
+      </c>
+    </row>
+    <row r="2231" spans="1:6">
+      <c r="A2231" s="2" t="s">
+        <v>2245</v>
+      </c>
+      <c r="B2231" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2231" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2231" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2231" s="2">
+        <v>6179.47</v>
+      </c>
+      <c r="F2231" s="2">
+        <v>10687.54</v>
+      </c>
+    </row>
+    <row r="2232" spans="1:6">
+      <c r="A2232" s="2" t="s">
+        <v>2246</v>
+      </c>
+      <c r="B2232" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2232" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2232" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2232" s="2">
+        <v>6045.88</v>
+      </c>
+      <c r="F2232" s="2">
+        <v>12301.86</v>
+      </c>
+    </row>
+    <row r="2233" spans="1:6">
+      <c r="A2233" s="2" t="s">
+        <v>2247</v>
+      </c>
+      <c r="B2233" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2233" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2233" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2233" s="2">
+        <v>6635.33</v>
+      </c>
+      <c r="F2233" s="2">
+        <v>13480.69</v>
+      </c>
+    </row>
+    <row r="2234" spans="1:6">
+      <c r="A2234" s="2" t="s">
+        <v>2248</v>
+      </c>
+      <c r="B2234" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2234" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2234" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2234" s="2">
+        <v>7979.51</v>
+      </c>
+      <c r="F2234" s="2">
+        <v>14809.46</v>
+      </c>
+    </row>
+    <row r="2235" spans="1:6">
+      <c r="A2235" s="2" t="s">
+        <v>2249</v>
+      </c>
+      <c r="B2235" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2235" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2235" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2235" s="2">
+        <v>7293.61</v>
+      </c>
+      <c r="F2235" s="2">
+        <v>13766.78</v>
+      </c>
+    </row>
+    <row r="2236" spans="1:6">
+      <c r="A2236" s="2" t="s">
+        <v>2250</v>
+      </c>
+      <c r="B2236" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2236" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2236" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2236" s="2">
+        <v>4945.46</v>
+      </c>
+      <c r="F2236" s="2">
+        <v>10281.370000000001</v>
+      </c>
+    </row>
+    <row r="2237" spans="1:6">
+      <c r="A2237" s="2" t="s">
+        <v>2251</v>
+      </c>
+      <c r="B2237" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2237" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2237" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2237" s="2">
+        <v>7890.11</v>
+      </c>
+      <c r="F2237" s="2">
+        <v>13091.93</v>
+      </c>
+    </row>
+    <row r="2238" spans="1:6">
+      <c r="A2238" s="2" t="s">
+        <v>2252</v>
+      </c>
+      <c r="B2238" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2238" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2238" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2238" s="2">
+        <v>6614.07</v>
+      </c>
+      <c r="F2238" s="2">
+        <v>10771.14</v>
+      </c>
+    </row>
+    <row r="2239" spans="1:6">
+      <c r="A2239" s="2" t="s">
+        <v>2253</v>
+      </c>
+      <c r="B2239" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2239" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2239" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2239" s="2">
+        <v>7062.79</v>
+      </c>
+      <c r="F2239" s="2">
+        <v>14185.5</v>
+      </c>
+    </row>
+    <row r="2240" spans="1:6">
+      <c r="A2240" s="2" t="s">
+        <v>2254</v>
+      </c>
+      <c r="B2240" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2240" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2240" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2240" s="2">
+        <v>7998.16</v>
+      </c>
+      <c r="F2240" s="2">
+        <v>13867.35</v>
+      </c>
+    </row>
+    <row r="2241" spans="1:6">
+      <c r="A2241" s="2" t="s">
+        <v>2255</v>
+      </c>
+      <c r="B2241" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2241" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2241" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2241" s="2">
+        <v>4904.41</v>
+      </c>
+      <c r="F2241" s="2">
+        <v>10004.85</v>
+      </c>
+    </row>
+    <row r="2242" spans="1:6">
+      <c r="A2242" s="2" t="s">
+        <v>2256</v>
+      </c>
+      <c r="B2242" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2242" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2242" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2242" s="2">
+        <v>6195.32</v>
+      </c>
+      <c r="F2242" s="2">
+        <v>12751.78</v>
+      </c>
+    </row>
+    <row r="2243" spans="1:6">
+      <c r="A2243" s="2" t="s">
+        <v>2257</v>
+      </c>
+      <c r="B2243" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2243" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2243" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2243" s="2">
+        <v>5600.56</v>
+      </c>
+      <c r="F2243" s="2">
+        <v>10316.36</v>
+      </c>
+    </row>
+    <row r="2244" spans="1:6">
+      <c r="A2244" s="2" t="s">
+        <v>2258</v>
+      </c>
+      <c r="B2244" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2244" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2244" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2244" s="2">
+        <v>4356.88</v>
+      </c>
+      <c r="F2244" s="2">
+        <v>10176.19</v>
+      </c>
+    </row>
+    <row r="2245" spans="1:6">
+      <c r="A2245" s="2" t="s">
+        <v>2259</v>
+      </c>
+      <c r="B2245" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2245" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2245" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2245" s="2">
+        <v>6654.36</v>
+      </c>
+      <c r="F2245" s="2">
+        <v>12010.27</v>
+      </c>
+    </row>
+    <row r="2246" spans="1:6">
+      <c r="A2246" s="2" t="s">
+        <v>2260</v>
+      </c>
+      <c r="B2246" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2246" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2246" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2246" s="2">
+        <v>9252.18</v>
+      </c>
+      <c r="F2246" s="2">
+        <v>15257.13</v>
+      </c>
+    </row>
+    <row r="2247" spans="1:6">
+      <c r="A2247" s="2" t="s">
+        <v>2261</v>
+      </c>
+      <c r="B2247" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2247" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2247" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2247" s="2">
+        <v>4030.22</v>
+      </c>
+      <c r="F2247" s="2">
+        <v>9473.3700000000008</v>
+      </c>
+    </row>
+    <row r="2248" spans="1:6">
+      <c r="A2248" s="2" t="s">
+        <v>2262</v>
+      </c>
+      <c r="B2248" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2248" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2248" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2248" s="2">
+        <v>6199.57</v>
+      </c>
+      <c r="F2248" s="2">
+        <v>10532.84</v>
+      </c>
+    </row>
+    <row r="2249" spans="1:6">
+      <c r="A2249" s="2" t="s">
+        <v>2263</v>
+      </c>
+      <c r="B2249" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2249" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2249" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2249" s="2">
+        <v>7006.96</v>
+      </c>
+      <c r="F2249" s="2">
+        <v>12561.43</v>
+      </c>
+    </row>
+    <row r="2250" spans="1:6">
+      <c r="A2250" s="2" t="s">
+        <v>2264</v>
+      </c>
+      <c r="B2250" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2250" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2250" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2250" s="2">
+        <v>6386</v>
+      </c>
+      <c r="F2250" s="2">
+        <v>12719.1</v>
+      </c>
+    </row>
+    <row r="2251" spans="1:6">
+      <c r="A2251" s="2" t="s">
+        <v>2265</v>
+      </c>
+      <c r="B2251" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2251" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2251" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2251" s="2">
+        <v>6102.56</v>
+      </c>
+      <c r="F2251" s="2">
+        <v>11573.2</v>
+      </c>
+    </row>
+    <row r="2252" spans="1:6">
+      <c r="A2252" s="2" t="s">
+        <v>2266</v>
+      </c>
+      <c r="B2252" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2252" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2252" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2252" s="2">
+        <v>4679.25</v>
+      </c>
+      <c r="F2252" s="2">
+        <v>10793.35</v>
+      </c>
+    </row>
+    <row r="2253" spans="1:6">
+      <c r="A2253" s="2" t="s">
+        <v>2267</v>
+      </c>
+      <c r="B2253" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2253" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2253" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2253" s="2">
+        <v>6517.65</v>
+      </c>
+      <c r="F2253" s="2">
+        <v>11175.24</v>
+      </c>
+    </row>
+    <row r="2254" spans="1:6">
+      <c r="A2254" s="2" t="s">
+        <v>2268</v>
+      </c>
+      <c r="B2254" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2254" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2254" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2254" s="2">
+        <v>5330.19</v>
+      </c>
+      <c r="F2254" s="2">
+        <v>10803.19</v>
+      </c>
+    </row>
+    <row r="2255" spans="1:6">
+      <c r="A2255" s="2" t="s">
+        <v>2269</v>
+      </c>
+      <c r="B2255" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2255" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2255" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2255" s="2">
+        <v>3610.4</v>
+      </c>
+      <c r="F2255" s="2">
+        <v>8604.7999999999993</v>
+      </c>
+    </row>
+    <row r="2256" spans="1:6">
+      <c r="A2256" s="2" t="s">
+        <v>2270</v>
+      </c>
+      <c r="B2256" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2256" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2256" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2256" s="2">
+        <v>7671.82</v>
+      </c>
+      <c r="F2256" s="2">
+        <v>13763.41</v>
+      </c>
+    </row>
+    <row r="2257" spans="1:6">
+      <c r="A2257" s="2" t="s">
+        <v>2271</v>
+      </c>
+      <c r="B2257" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2257" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2257" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2257" s="2">
+        <v>7388.37</v>
+      </c>
+      <c r="F2257" s="2">
+        <v>12907.57</v>
+      </c>
+    </row>
+    <row r="2258" spans="1:6">
+      <c r="A2258" s="2" t="s">
+        <v>2272</v>
+      </c>
+      <c r="B2258" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2258" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2258" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2258" s="2">
+        <v>6300.3</v>
+      </c>
+      <c r="F2258" s="2">
+        <v>12346.37</v>
+      </c>
+    </row>
+    <row r="2259" spans="1:6">
+      <c r="A2259" s="2" t="s">
+        <v>2273</v>
+      </c>
+      <c r="B2259" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2259" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2259" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2259" s="2">
+        <v>6513.2</v>
+      </c>
+      <c r="F2259" s="2">
+        <v>12877.38</v>
+      </c>
+    </row>
+    <row r="2260" spans="1:6">
+      <c r="A2260" s="2" t="s">
+        <v>2274</v>
+      </c>
+      <c r="B2260" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2260" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2260" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2260" s="2">
+        <v>7527.49</v>
+      </c>
+      <c r="F2260" s="2">
+        <v>13574.79</v>
+      </c>
+    </row>
+    <row r="2261" spans="1:6">
+      <c r="A2261" s="2" t="s">
+        <v>2275</v>
+      </c>
+      <c r="B2261" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2261" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2261" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2261" s="2">
+        <v>6507.52</v>
+      </c>
+      <c r="F2261" s="2">
+        <v>12220.02</v>
+      </c>
+    </row>
+    <row r="2262" spans="1:6">
+      <c r="A2262" s="2" t="s">
+        <v>2276</v>
+      </c>
+      <c r="B2262" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2262" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2262" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2262" s="2">
+        <v>7323.13</v>
+      </c>
+      <c r="F2262" s="2">
+        <v>12018.57</v>
+      </c>
+    </row>
+    <row r="2263" spans="1:6">
+      <c r="A2263" s="2" t="s">
+        <v>2277</v>
+      </c>
+      <c r="B2263" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2263" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2263" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2263" s="2">
+        <v>5881.33</v>
+      </c>
+      <c r="F2263" s="2">
+        <v>11373.11</v>
+      </c>
+    </row>
+    <row r="2264" spans="1:6">
+      <c r="A2264" s="2" t="s">
+        <v>2278</v>
+      </c>
+      <c r="B2264" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2264" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2264" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2264" s="2">
+        <v>7812.69</v>
+      </c>
+      <c r="F2264" s="2">
+        <v>12880.23</v>
+      </c>
+    </row>
+    <row r="2265" spans="1:6">
+      <c r="A2265" s="2" t="s">
+        <v>2279</v>
+      </c>
+      <c r="B2265" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2265" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2265" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2265" s="2">
+        <v>6623.25</v>
+      </c>
+      <c r="F2265" s="2">
+        <v>11842.01</v>
+      </c>
+    </row>
+    <row r="2266" spans="1:6">
+      <c r="A2266" s="2" t="s">
+        <v>2280</v>
+      </c>
+      <c r="B2266" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2266" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2266" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2266" s="2">
+        <v>6471.17</v>
+      </c>
+      <c r="F2266" s="2">
+        <v>11665.55</v>
+      </c>
+    </row>
+    <row r="2267" spans="1:6">
+      <c r="A2267" s="2" t="s">
+        <v>2281</v>
+      </c>
+      <c r="B2267" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2267" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2267" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2267" s="2">
+        <v>4714.24</v>
+      </c>
+      <c r="F2267" s="2">
+        <v>9424.31</v>
+      </c>
+    </row>
+    <row r="2268" spans="1:6">
+      <c r="A2268" s="2" t="s">
+        <v>2282</v>
+      </c>
+      <c r="B2268" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2268" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2268" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2268" s="2">
+        <v>6582.66</v>
+      </c>
+      <c r="F2268" s="2">
+        <v>10510.8</v>
+      </c>
+    </row>
+    <row r="2269" spans="1:6">
+      <c r="A2269" s="2" t="s">
+        <v>2283</v>
+      </c>
+      <c r="B2269" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2269" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2269" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2269" s="2">
+        <v>5239.96</v>
+      </c>
+      <c r="F2269" s="2">
+        <v>10199.459999999999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/NGO_Project_MNE_Dataset_2000.xlsx
+++ b/NGO_Project_MNE_Dataset_2000.xlsx
@@ -11,14 +11,14 @@
     <sheet name="Instructions" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AVCB Cases'!$A$1:$N$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AVCB Cases'!$A$1:$N$55</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="168">
   <si>
     <t>case_id</t>
   </si>
@@ -962,7 +962,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N55"/>
+  <dimension ref="A1:N56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3323,6 +3323,48 @@
         <v>32</v>
       </c>
     </row>
+    <row r="56" spans="1:14">
+      <c r="A56" s="2">
+        <v>4</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E56" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G56" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H56" s="4">
+        <v>26</v>
+      </c>
+      <c r="I56" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J56" s="6">
+        <v>19000</v>
+      </c>
+      <c r="K56" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L56" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="M56" s="8"/>
+      <c r="N56" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/NGO_Project_MNE_Dataset_2000.xlsx
+++ b/NGO_Project_MNE_Dataset_2000.xlsx
@@ -11,14 +11,14 @@
     <sheet name="Instructions" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AVCB Cases'!$A$1:$N$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AVCB Cases'!$A$1:$N$56</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="169">
   <si>
     <t>case_id</t>
   </si>
@@ -522,6 +522,9 @@
   </si>
   <si>
     <t>union-rump-004</t>
+  </si>
+  <si>
+    <t>male</t>
   </si>
 </sst>
 </file>
@@ -962,7 +965,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N56"/>
+  <dimension ref="A1:N66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1032,7 +1035,7 @@
       <c r="B2" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="13" t="s">
         <v>117</v>
       </c>
       <c r="D2" s="3" t="s">
@@ -1074,13 +1077,13 @@
       <c r="B3" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="13" t="s">
         <v>118</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="13" t="s">
         <v>115</v>
       </c>
       <c r="F3" s="3" t="s">
@@ -1118,13 +1121,13 @@
       <c r="B4" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="13" t="s">
         <v>119</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="13" t="s">
         <v>116</v>
       </c>
       <c r="F4" s="3" t="s">
@@ -1798,7 +1801,7 @@
       <c r="B20" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="13" t="s">
         <v>117</v>
       </c>
       <c r="D20" s="3" t="s">
@@ -1840,13 +1843,13 @@
       <c r="B21" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="13" t="s">
         <v>118</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" s="13" t="s">
         <v>115</v>
       </c>
       <c r="F21" s="3" t="s">
@@ -1884,13 +1887,13 @@
       <c r="B22" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="13" t="s">
         <v>119</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E22" s="13" t="s">
         <v>116</v>
       </c>
       <c r="F22" s="3" t="s">
@@ -2564,7 +2567,7 @@
       <c r="B38" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="13" t="s">
         <v>117</v>
       </c>
       <c r="D38" s="3" t="s">
@@ -2606,13 +2609,13 @@
       <c r="B39" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="13" t="s">
         <v>118</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E39" t="s">
+      <c r="E39" s="13" t="s">
         <v>115</v>
       </c>
       <c r="F39" s="3" t="s">
@@ -2650,13 +2653,13 @@
       <c r="B40" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="13" t="s">
         <v>119</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E40" t="s">
+      <c r="E40" s="13" t="s">
         <v>116</v>
       </c>
       <c r="F40" s="3" t="s">
@@ -3259,26 +3262,26 @@
         <v>61</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H54" s="4">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I54" s="5" t="s">
         <v>17</v>
       </c>
       <c r="J54" s="6">
-        <v>32000</v>
+        <v>23000</v>
       </c>
       <c r="K54" s="7" t="s">
         <v>18</v>
       </c>
       <c r="L54" s="8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="M54" s="8"/>
       <c r="N54" s="3" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="55" spans="1:14">
@@ -3304,23 +3307,23 @@
         <v>22</v>
       </c>
       <c r="H55" s="4">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="I55" s="5" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J55" s="6">
-        <v>19000</v>
+        <v>23000</v>
       </c>
       <c r="K55" s="7" t="s">
         <v>18</v>
       </c>
       <c r="L55" s="8" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="M55" s="8"/>
       <c r="N55" s="3" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
     </row>
     <row r="56" spans="1:14">
@@ -3343,26 +3346,454 @@
         <v>63</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H56" s="4">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="I56" s="5" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J56" s="6">
-        <v>19000</v>
+        <v>23000</v>
       </c>
       <c r="K56" s="7" t="s">
         <v>18</v>
       </c>
       <c r="L56" s="8" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="M56" s="8"/>
       <c r="N56" s="3" t="s">
-        <v>32</v>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14">
+      <c r="A57" s="2">
+        <v>4</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H57" s="4">
+        <v>34</v>
+      </c>
+      <c r="I57" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J57" s="6">
+        <v>23000</v>
+      </c>
+      <c r="K57" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L57" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="M57" s="8"/>
+      <c r="N57" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14">
+      <c r="A58" s="2">
+        <v>5</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G58" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H58" s="4">
+        <v>34</v>
+      </c>
+      <c r="I58" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J58" s="6">
+        <v>23000</v>
+      </c>
+      <c r="K58" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L58" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="M58" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="N58" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14">
+      <c r="A59" s="2">
+        <v>6</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G59" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="H59" s="4">
+        <v>34</v>
+      </c>
+      <c r="I59" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J59" s="6">
+        <v>23000</v>
+      </c>
+      <c r="K59" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L59" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="M59" s="8"/>
+      <c r="N59" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14">
+      <c r="A60" s="2">
+        <v>7</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G60" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H60" s="4">
+        <v>34</v>
+      </c>
+      <c r="I60" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J60" s="6">
+        <v>23000</v>
+      </c>
+      <c r="K60" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L60" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="M60" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="N60" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14">
+      <c r="A61" s="2">
+        <v>8</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="G61" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H61" s="4">
+        <v>34</v>
+      </c>
+      <c r="I61" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J61" s="6">
+        <v>23000</v>
+      </c>
+      <c r="K61" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L61" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="M61" s="8"/>
+      <c r="N61" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14">
+      <c r="A62" s="2">
+        <v>9</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G62" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H62" s="4">
+        <v>34</v>
+      </c>
+      <c r="I62" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J62" s="6">
+        <v>23000</v>
+      </c>
+      <c r="K62" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L62" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="M62" s="8"/>
+      <c r="N62" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14">
+      <c r="A63" s="2">
+        <v>10</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G63" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H63" s="4">
+        <v>34</v>
+      </c>
+      <c r="I63" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J63" s="6">
+        <v>23000</v>
+      </c>
+      <c r="K63" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L63" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="M63" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="N63" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14">
+      <c r="A64" s="2">
+        <v>11</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="G64" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H64" s="4">
+        <v>34</v>
+      </c>
+      <c r="I64" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J64" s="6">
+        <v>23000</v>
+      </c>
+      <c r="K64" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L64" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="M64" s="8"/>
+      <c r="N64" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14">
+      <c r="A65" s="2">
+        <v>12</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G65" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="H65" s="4">
+        <v>34</v>
+      </c>
+      <c r="I65" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J65" s="6">
+        <v>23000</v>
+      </c>
+      <c r="K65" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L65" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="M65" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="N65" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14">
+      <c r="A66" s="2">
+        <v>13</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="G66" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="H66" s="4">
+        <v>34</v>
+      </c>
+      <c r="I66" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J66" s="6">
+        <v>23000</v>
+      </c>
+      <c r="K66" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L66" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="M66" s="8"/>
+      <c r="N66" s="3" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/NGO_Project_MNE_Dataset_2000.xlsx
+++ b/NGO_Project_MNE_Dataset_2000.xlsx
@@ -11,14 +11,14 @@
     <sheet name="Instructions" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AVCB Cases'!$A$1:$N$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AVCB Cases'!$A$1:$N$66</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="168">
   <si>
     <t>case_id</t>
   </si>
@@ -522,9 +522,6 @@
   </si>
   <si>
     <t>union-rump-004</t>
-  </si>
-  <si>
-    <t>male</t>
   </si>
 </sst>
 </file>
@@ -3474,7 +3471,7 @@
         <v>47</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>168</v>
+        <v>16</v>
       </c>
       <c r="H59" s="4">
         <v>34</v>
@@ -3730,7 +3727,7 @@
         <v>59</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>168</v>
+        <v>16</v>
       </c>
       <c r="H65" s="4">
         <v>34</v>
@@ -3774,7 +3771,7 @@
         <v>61</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>168</v>
+        <v>16</v>
       </c>
       <c r="H66" s="4">
         <v>34</v>
